--- a/research/traditional_assets/database/data/netherlands/netherlands_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_construction_supplies.xlsx
@@ -590,94 +590,112 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.2148424543946932</v>
+        <v>-1.032325141776938</v>
       </c>
       <c r="H2">
-        <v>0.2134881149806523</v>
+        <v>-1.044423440453686</v>
       </c>
       <c r="I2">
-        <v>0.1309563294637922</v>
+        <v>-1.237240075614367</v>
       </c>
       <c r="J2">
-        <v>0.0930431616169593</v>
+        <v>-1.237240075614367</v>
       </c>
       <c r="K2">
-        <v>190.2</v>
+        <v>-158.8</v>
       </c>
       <c r="L2">
-        <v>0.1051409618573798</v>
+        <v>-1.500945179584121</v>
       </c>
       <c r="M2">
-        <v>48.516</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.02858759059572211</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.2550788643533123</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>48.516</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.02858759059572211</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.2550788643533123</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>0</v>
+        <v>8.77</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.1134540750323415</v>
+      </c>
+      <c r="W2">
+        <v>-0.6015151515151516</v>
       </c>
       <c r="X2">
-        <v>0.07680054732918393</v>
+        <v>0.0932853098474119</v>
+      </c>
+      <c r="Y2">
+        <v>-0.6948004613625635</v>
+      </c>
+      <c r="Z2">
+        <v>0.4687430774002038</v>
+      </c>
+      <c r="AA2">
+        <v>-0.5799477205263391</v>
       </c>
       <c r="AB2">
-        <v>0.07680054732918393</v>
+        <v>0.08220816604822997</v>
+      </c>
+      <c r="AC2">
+        <v>-0.6621558865745691</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>55.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>55.5</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>46.73</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.4179216867469879</v>
+      </c>
+      <c r="AI2">
+        <v>0.2969502407704655</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>0.3767636862049504</v>
+      </c>
+      <c r="AK2">
+        <v>0.2623364958176613</v>
       </c>
       <c r="AL2">
-        <v>14.6</v>
+        <v>6.46</v>
       </c>
       <c r="AM2">
-        <v>-5.1</v>
+        <v>6.433</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>-0.4422310756972112</v>
       </c>
       <c r="AO2">
-        <v>16.22602739726027</v>
+        <v>-20.26315789473684</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>-0.3723505976095618</v>
       </c>
       <c r="AQ2">
-        <v>-46.45098039215686</v>
+        <v>-20.34820457018499</v>
       </c>
     </row>
     <row r="3">
@@ -688,7 +706,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V. (BIT:CEM)</t>
+          <t>Ebusco Holding N.V. (ENXTAM:EBUS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -697,94 +715,112 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.2148424543946932</v>
+        <v>-1.032325141776938</v>
       </c>
       <c r="H3">
-        <v>0.2134881149806523</v>
+        <v>-1.044423440453686</v>
       </c>
       <c r="I3">
-        <v>0.1309563294637922</v>
+        <v>-1.237240075614367</v>
       </c>
       <c r="J3">
-        <v>0.0930431616169593</v>
+        <v>-1.237240075614367</v>
       </c>
       <c r="K3">
-        <v>190.2</v>
+        <v>-158.8</v>
       </c>
       <c r="L3">
-        <v>0.1051409618573798</v>
+        <v>-1.500945179584121</v>
       </c>
       <c r="M3">
-        <v>48.516</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.02858759059572211</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.2550788643533123</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>48.516</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.02858759059572211</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.2550788643533123</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0</v>
+        <v>8.77</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.1134540750323415</v>
+      </c>
+      <c r="W3">
+        <v>-0.6015151515151516</v>
       </c>
       <c r="X3">
-        <v>0.07680054732918393</v>
+        <v>0.0932853098474119</v>
+      </c>
+      <c r="Y3">
+        <v>-0.6948004613625635</v>
+      </c>
+      <c r="Z3">
+        <v>0.4687430774002038</v>
+      </c>
+      <c r="AA3">
+        <v>-0.5799477205263391</v>
       </c>
       <c r="AB3">
-        <v>0.07680054732918393</v>
+        <v>0.08220816604822997</v>
+      </c>
+      <c r="AC3">
+        <v>-0.6621558865745691</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>55.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>55.5</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>46.73</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.4179216867469879</v>
+      </c>
+      <c r="AI3">
+        <v>0.2969502407704655</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>0.3767636862049504</v>
+      </c>
+      <c r="AK3">
+        <v>0.2623364958176613</v>
       </c>
       <c r="AL3">
-        <v>14.6</v>
+        <v>6.46</v>
       </c>
       <c r="AM3">
-        <v>-5.1</v>
+        <v>6.433</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>-0.4422310756972112</v>
       </c>
       <c r="AO3">
-        <v>16.22602739726027</v>
+        <v>-20.26315789473684</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>-0.3723505976095618</v>
       </c>
       <c r="AQ3">
-        <v>-46.45098039215686</v>
+        <v>-20.34820457018499</v>
       </c>
     </row>
   </sheetData>
@@ -1079,49 +1115,49 @@
         <v>13.6095890410959</v>
       </c>
       <c r="F2">
-        <v>4.59577960422895</v>
+        <v>4.50471629399933</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>2.1225810119386</v>
+        <v>2.26730244457078</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="K2">
         <v>1697.1</v>
       </c>
       <c r="L2">
-        <v>1001.83983705669</v>
+        <v>964.707870999535</v>
       </c>
       <c r="M2">
         <v>1697.1</v>
       </c>
       <c r="N2">
-        <v>1748.56383705669</v>
+        <v>1762.34487099953</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>746.724</v>
+        <v>797.6369999999999</v>
       </c>
       <c r="Q2">
-        <v>0.0768005473291839</v>
+        <v>0.0767806167335264</v>
       </c>
       <c r="R2">
-        <v>0.072032557196375</v>
+        <v>0.070783229148419</v>
       </c>
       <c r="S2">
         <v>0.0443716</v>
       </c>
       <c r="T2">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1134,16 +1170,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0768005473291839</v>
+        <v>0.0767806167335264</v>
       </c>
       <c r="X2">
-        <v>0.0948738664220982</v>
+        <v>0.0971658625441867</v>
       </c>
       <c r="Y2">
         <v>0.715487684377053</v>
       </c>
       <c r="Z2">
-        <v>1.13261700436887</v>
+        <v>1.18627858069715</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -1176,7 +1212,7 @@
         <v>1697.1</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1361,7 +1397,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07680054732918393</v>
+        <v>0.07678061673352639</v>
       </c>
       <c r="C2">
         <v>1697.1</v>
@@ -1412,19 +1448,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07680054732918393</v>
+        <v>0.07678061673352639</v>
       </c>
       <c r="T2">
         <v>0.7154876843770529</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1443,13 +1479,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07664617991707463</v>
+        <v>0.07661591274235389</v>
       </c>
       <c r="C3">
-        <v>1681.747685254361</v>
+        <v>1681.856216168839</v>
       </c>
       <c r="D3">
-        <v>1698.718685254361</v>
+        <v>1698.827216168839</v>
       </c>
       <c r="E3">
         <v>16.971</v>
@@ -1476,37 +1512,37 @@
         <v>198.7</v>
       </c>
       <c r="M3">
-        <v>0.8774007</v>
+        <v>0.8536412999999999</v>
       </c>
       <c r="N3">
-        <v>197.8225993</v>
+        <v>197.8463587</v>
       </c>
       <c r="O3">
-        <v>51.0382306194</v>
+        <v>51.04436054460001</v>
       </c>
       <c r="P3">
-        <v>146.7843686806</v>
+        <v>146.8019981554</v>
       </c>
       <c r="Q3">
-        <v>299.8843686806</v>
+        <v>299.9019981554</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07703289486573195</v>
+        <v>0.07701281489126656</v>
       </c>
       <c r="T3">
         <v>0.7208502284357172</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1514,7 +1550,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>226.4643736892391</v>
+        <v>232.7675570523592</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1525,13 +1561,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07649181250496534</v>
+        <v>0.07645120875118139</v>
       </c>
       <c r="C4">
-        <v>1666.398461243996</v>
+        <v>1666.615951652984</v>
       </c>
       <c r="D4">
-        <v>1700.340461243996</v>
+        <v>1700.557951652984</v>
       </c>
       <c r="E4">
         <v>33.942</v>
@@ -1558,37 +1594,37 @@
         <v>198.7</v>
       </c>
       <c r="M4">
-        <v>1.7548014</v>
+        <v>1.7072826</v>
       </c>
       <c r="N4">
-        <v>196.9451986</v>
+        <v>196.9927174</v>
       </c>
       <c r="O4">
-        <v>50.81186123880001</v>
+        <v>50.82412108920001</v>
       </c>
       <c r="P4">
-        <v>146.1333373612</v>
+        <v>146.1685963108</v>
       </c>
       <c r="Q4">
-        <v>299.2333373612</v>
+        <v>299.2685963108</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07726998418874015</v>
+        <v>0.07724975178691978</v>
       </c>
       <c r="T4">
         <v>0.7263222121690482</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.258</v>
       </c>
       <c r="W4">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1596,7 +1632,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>113.2321868446196</v>
+        <v>116.3837785261796</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1607,13 +1643,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07633744509285603</v>
+        <v>0.07628650476000888</v>
       </c>
       <c r="C5">
-        <v>1651.052336829589</v>
+        <v>1651.379217219655</v>
       </c>
       <c r="D5">
-        <v>1701.965336829589</v>
+        <v>1702.292217219655</v>
       </c>
       <c r="E5">
         <v>50.913</v>
@@ -1640,37 +1676,37 @@
         <v>198.7</v>
       </c>
       <c r="M5">
-        <v>2.6322021</v>
+        <v>2.5609239</v>
       </c>
       <c r="N5">
-        <v>196.0677979</v>
+        <v>196.1390761</v>
       </c>
       <c r="O5">
-        <v>50.58549185820001</v>
+        <v>50.60388163380001</v>
       </c>
       <c r="P5">
-        <v>145.4823060418</v>
+        <v>145.5351944662</v>
       </c>
       <c r="Q5">
-        <v>298.5823060418</v>
+        <v>298.6351944662</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07751196195139798</v>
+        <v>0.0774915739793906</v>
       </c>
       <c r="T5">
         <v>0.731907020309252</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1678,7 +1714,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.48812456307972</v>
+        <v>77.58918568411971</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1689,13 +1725,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07618307768074677</v>
+        <v>0.0761218007688364</v>
       </c>
       <c r="C6">
-        <v>1635.709320905728</v>
+        <v>1636.146023680041</v>
       </c>
       <c r="D6">
-        <v>1703.593320905728</v>
+        <v>1704.030023680041</v>
       </c>
       <c r="E6">
         <v>67.884</v>
@@ -1722,37 +1758,37 @@
         <v>198.7</v>
       </c>
       <c r="M6">
-        <v>3.5096028</v>
+        <v>3.4145652</v>
       </c>
       <c r="N6">
-        <v>195.1903972</v>
+        <v>195.2854348</v>
       </c>
       <c r="O6">
-        <v>50.3591224776</v>
+        <v>50.38364217840001</v>
       </c>
       <c r="P6">
-        <v>144.8312747224</v>
+        <v>144.9017926216</v>
       </c>
       <c r="Q6">
-        <v>297.9312747224</v>
+        <v>298.0017926216</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07775898091744454</v>
+        <v>0.07773843413420459</v>
       </c>
       <c r="T6">
         <v>0.7376081786190435</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.258</v>
       </c>
       <c r="W6">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1760,7 +1796,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.61609342230978</v>
+        <v>58.19188926308978</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1771,13 +1807,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07602871026863746</v>
+        <v>0.07595709677766389</v>
       </c>
       <c r="C7">
-        <v>1620.369422401063</v>
+        <v>1620.91638188952</v>
       </c>
       <c r="D7">
-        <v>1705.224422401063</v>
+        <v>1705.77138188952</v>
       </c>
       <c r="E7">
         <v>84.855</v>
@@ -1804,37 +1840,37 @@
         <v>198.7</v>
       </c>
       <c r="M7">
-        <v>4.3870035</v>
+        <v>4.2682065</v>
       </c>
       <c r="N7">
-        <v>194.3129965</v>
+        <v>194.4317935</v>
       </c>
       <c r="O7">
-        <v>50.13275309700001</v>
+        <v>50.16340272300001</v>
       </c>
       <c r="P7">
-        <v>144.180243403</v>
+        <v>144.268390777</v>
       </c>
       <c r="Q7">
-        <v>297.280243403</v>
+        <v>297.368390777</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07801120028277628</v>
+        <v>0.07799049134490937</v>
       </c>
       <c r="T7">
         <v>0.7434293613143041</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1842,7 +1878,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.29287473784782</v>
+        <v>46.55351141047183</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1853,13 +1889,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07587434285652815</v>
+        <v>0.0757923927864914</v>
       </c>
       <c r="C8">
-        <v>1605.032650278474</v>
+        <v>1605.690302747892</v>
       </c>
       <c r="D8">
-        <v>1706.858650278474</v>
+        <v>1707.516302747892</v>
       </c>
       <c r="E8">
         <v>101.826</v>
@@ -1886,37 +1922,37 @@
         <v>198.7</v>
       </c>
       <c r="M8">
-        <v>5.2644042</v>
+        <v>5.121847799999999</v>
       </c>
       <c r="N8">
-        <v>193.4355958</v>
+        <v>193.5781522</v>
       </c>
       <c r="O8">
-        <v>49.90638371640001</v>
+        <v>49.9431632676</v>
       </c>
       <c r="P8">
-        <v>143.5292120836</v>
+        <v>143.6349889324</v>
       </c>
       <c r="Q8">
-        <v>296.6292120836</v>
+        <v>296.7349889324</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07826878601758315</v>
+        <v>0.07824791147499086</v>
       </c>
       <c r="T8">
         <v>0.7493743989605278</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1924,7 +1960,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.74406228153986</v>
+        <v>38.79459284205986</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1935,13 +1971,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07571997544441886</v>
+        <v>0.07562768879531889</v>
       </c>
       <c r="C9">
-        <v>1589.699013535232</v>
+        <v>1590.467797199598</v>
       </c>
       <c r="D9">
-        <v>1708.496013535232</v>
+        <v>1709.264797199598</v>
       </c>
       <c r="E9">
         <v>118.797</v>
@@ -1968,37 +2004,37 @@
         <v>198.7</v>
       </c>
       <c r="M9">
-        <v>6.141804900000001</v>
+        <v>5.9754891</v>
       </c>
       <c r="N9">
-        <v>192.5581951</v>
+        <v>192.7245109</v>
       </c>
       <c r="O9">
-        <v>49.6800143358</v>
+        <v>49.7229238122</v>
       </c>
       <c r="P9">
-        <v>142.8781807642</v>
+        <v>143.0015870878</v>
       </c>
       <c r="Q9">
-        <v>295.9781807642</v>
+        <v>296.1015870878</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07853191123055792</v>
+        <v>0.07851086752184827</v>
       </c>
       <c r="T9">
         <v>0.7554472868787132</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2006,7 +2042,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.35205338417701</v>
+        <v>33.25250815033702</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2017,13 +2053,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07556560803230958</v>
+        <v>0.07546298480414641</v>
       </c>
       <c r="C10">
-        <v>1574.368521203163</v>
+        <v>1575.248876233957</v>
       </c>
       <c r="D10">
-        <v>1710.136521203163</v>
+        <v>1711.016876233957</v>
       </c>
       <c r="E10">
         <v>135.768</v>
@@ -2050,37 +2086,37 @@
         <v>198.7</v>
       </c>
       <c r="M10">
-        <v>7.0192056</v>
+        <v>6.829130399999999</v>
       </c>
       <c r="N10">
-        <v>191.6807944</v>
+        <v>191.8708696</v>
       </c>
       <c r="O10">
-        <v>49.45364495520001</v>
+        <v>49.5026843568</v>
       </c>
       <c r="P10">
-        <v>142.2271494448</v>
+        <v>142.3681852432</v>
       </c>
       <c r="Q10">
-        <v>295.3271494448001</v>
+        <v>295.4681852432</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07880075655685823</v>
+        <v>0.07877954000450696</v>
       </c>
       <c r="T10">
         <v>0.7616521940994679</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2088,7 +2124,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.30804671115489</v>
+        <v>29.0959446315449</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2099,13 +2135,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07541124062020028</v>
+        <v>0.07529828081297392</v>
       </c>
       <c r="C11">
-        <v>1559.041182348819</v>
+        <v>1560.033550885391</v>
       </c>
       <c r="D11">
-        <v>1711.780182348819</v>
+        <v>1712.772550885391</v>
       </c>
       <c r="E11">
         <v>152.739</v>
@@ -2132,37 +2168,37 @@
         <v>198.7</v>
       </c>
       <c r="M11">
-        <v>7.896606299999999</v>
+        <v>7.682771699999998</v>
       </c>
       <c r="N11">
-        <v>190.8033937</v>
+        <v>191.0172283</v>
       </c>
       <c r="O11">
-        <v>49.22727557460001</v>
+        <v>49.28244490140001</v>
       </c>
       <c r="P11">
-        <v>141.5761181254</v>
+        <v>141.7347833986</v>
       </c>
       <c r="Q11">
-        <v>294.6761181254</v>
+        <v>294.8347833986001</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07907551057164866</v>
+        <v>0.07905411737689441</v>
       </c>
       <c r="T11">
         <v>0.767993472907492</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.258</v>
       </c>
       <c r="W11">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2170,7 +2206,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.16270818769324</v>
+        <v>25.86306189470658</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2181,13 +2217,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07525687320809098</v>
+        <v>0.07513357682180141</v>
       </c>
       <c r="C12">
-        <v>1543.717006073641</v>
+        <v>1544.821832233658</v>
       </c>
       <c r="D12">
-        <v>1713.427006073641</v>
+        <v>1714.531832233658</v>
       </c>
       <c r="E12">
         <v>169.71</v>
@@ -2214,37 +2250,37 @@
         <v>198.7</v>
       </c>
       <c r="M12">
-        <v>8.774007000000001</v>
+        <v>8.536413</v>
       </c>
       <c r="N12">
-        <v>189.925993</v>
+        <v>190.163587</v>
       </c>
       <c r="O12">
-        <v>49.000906194</v>
+        <v>49.062205446</v>
       </c>
       <c r="P12">
-        <v>140.925086806</v>
+        <v>141.101381554</v>
       </c>
       <c r="Q12">
-        <v>294.025086806</v>
+        <v>294.201381554</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.0793563702312122</v>
+        <v>0.07933479646866823</v>
       </c>
       <c r="T12">
         <v>0.7744756690223611</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2252,7 +2288,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.64643736892391</v>
+        <v>23.27675570523591</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2263,13 +2299,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07510250579598168</v>
+        <v>0.07496887283062892</v>
       </c>
       <c r="C13">
-        <v>1528.396001514127</v>
+        <v>1529.613731404087</v>
       </c>
       <c r="D13">
-        <v>1715.077001514127</v>
+        <v>1716.294731404087</v>
       </c>
       <c r="E13">
         <v>186.681</v>
@@ -2296,37 +2332,37 @@
         <v>198.7</v>
       </c>
       <c r="M13">
-        <v>9.6514077</v>
+        <v>9.390054299999999</v>
       </c>
       <c r="N13">
-        <v>189.0485923</v>
+        <v>189.3099457</v>
       </c>
       <c r="O13">
-        <v>48.7745368134</v>
+        <v>48.8419659906</v>
       </c>
       <c r="P13">
-        <v>140.2740554866</v>
+        <v>140.4679797094</v>
       </c>
       <c r="Q13">
-        <v>293.3740554866</v>
+        <v>293.5679797094</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07964354134379964</v>
+        <v>0.07962178295576282</v>
       </c>
       <c r="T13">
         <v>0.781103532465654</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2334,7 +2370,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.58767033538538</v>
+        <v>21.16068700475992</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2345,13 +2381,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07494813838387239</v>
+        <v>0.07480416883945641</v>
       </c>
       <c r="C14">
-        <v>1513.078177842002</v>
+        <v>1514.409259567809</v>
       </c>
       <c r="D14">
-        <v>1716.730177842002</v>
+        <v>1718.061259567809</v>
       </c>
       <c r="E14">
         <v>203.652</v>
@@ -2378,37 +2414,37 @@
         <v>198.7</v>
       </c>
       <c r="M14">
-        <v>10.5288084</v>
+        <v>10.2436956</v>
       </c>
       <c r="N14">
-        <v>188.1711916</v>
+        <v>188.4563044</v>
       </c>
       <c r="O14">
-        <v>48.54816743280001</v>
+        <v>48.6217265352</v>
       </c>
       <c r="P14">
-        <v>139.6230241672</v>
+        <v>139.8345778648</v>
       </c>
       <c r="Q14">
-        <v>292.7230241672</v>
+        <v>292.9345778648</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07993723907258227</v>
+        <v>0.07991529186301866</v>
       </c>
       <c r="T14">
         <v>0.7878820291690221</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.258</v>
       </c>
       <c r="W14">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2416,7 +2452,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.87203114076993</v>
+        <v>19.39729642102993</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2427,13 +2463,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.0747937709717631</v>
+        <v>0.07463946484828392</v>
       </c>
       <c r="C15">
-        <v>1497.76354426439</v>
+        <v>1499.208427941995</v>
       </c>
       <c r="D15">
-        <v>1718.38654426439</v>
+        <v>1719.831427941995</v>
       </c>
       <c r="E15">
         <v>220.623</v>
@@ -2460,37 +2496,37 @@
         <v>198.7</v>
       </c>
       <c r="M15">
-        <v>11.4062091</v>
+        <v>11.0973369</v>
       </c>
       <c r="N15">
-        <v>187.2937909</v>
+        <v>187.6026631</v>
       </c>
       <c r="O15">
-        <v>48.3217980522</v>
+        <v>48.40148707980001</v>
       </c>
       <c r="P15">
-        <v>138.9719928478</v>
+        <v>139.2011760202</v>
       </c>
       <c r="Q15">
-        <v>292.0719928478</v>
+        <v>292.3011760202</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08023768847329091</v>
+        <v>0.08021554810147577</v>
       </c>
       <c r="T15">
         <v>0.7948163533828121</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2498,7 +2534,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.42033643763378</v>
+        <v>17.90519669633532</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2509,13 +2545,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07463940355965382</v>
+        <v>0.07447476085711142</v>
       </c>
       <c r="C16">
-        <v>1482.45211002398</v>
+        <v>1484.011247790093</v>
       </c>
       <c r="D16">
-        <v>1720.04611002398</v>
+        <v>1721.605247790093</v>
       </c>
       <c r="E16">
         <v>237.594</v>
@@ -2542,37 +2578,37 @@
         <v>198.7</v>
       </c>
       <c r="M16">
-        <v>12.2836098</v>
+        <v>11.9509782</v>
       </c>
       <c r="N16">
-        <v>186.4163902</v>
+        <v>186.7490218</v>
       </c>
       <c r="O16">
-        <v>48.0954286716</v>
+        <v>48.1812476244</v>
       </c>
       <c r="P16">
-        <v>138.3209615284</v>
+        <v>138.5677741756</v>
       </c>
       <c r="Q16">
-        <v>291.4209615284</v>
+        <v>291.6677741756</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.0805451250693649</v>
+        <v>0.08052278704315281</v>
       </c>
       <c r="T16">
         <v>0.8019119409504114</v>
       </c>
       <c r="U16">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.258</v>
       </c>
       <c r="W16">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2580,7 +2616,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.17602669208851</v>
+        <v>16.62625407516851</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2591,13 +2627,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07448503614754449</v>
+        <v>0.0743100568659389</v>
       </c>
       <c r="C17">
-        <v>1467.143884399204</v>
+        <v>1468.817730422069</v>
       </c>
       <c r="D17">
-        <v>1721.708884399204</v>
+        <v>1723.382730422069</v>
       </c>
       <c r="E17">
         <v>254.565</v>
@@ -2624,37 +2660,37 @@
         <v>198.7</v>
       </c>
       <c r="M17">
-        <v>13.1610105</v>
+        <v>12.8046195</v>
       </c>
       <c r="N17">
-        <v>185.5389895</v>
+        <v>185.8953805</v>
       </c>
       <c r="O17">
-        <v>47.86905929100001</v>
+        <v>47.961008169</v>
       </c>
       <c r="P17">
-        <v>137.669930209</v>
+        <v>137.934372331</v>
       </c>
       <c r="Q17">
-        <v>290.769930209</v>
+        <v>291.034372331</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08085979546769942</v>
+        <v>0.08083725513639872</v>
       </c>
       <c r="T17">
         <v>0.8091744835196012</v>
       </c>
       <c r="U17">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.258</v>
       </c>
       <c r="W17">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2662,7 +2698,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.09762491261594</v>
+        <v>15.51783713682394</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2673,13 +2709,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07433066873543522</v>
+        <v>0.07414535287476642</v>
       </c>
       <c r="C18">
-        <v>1451.838876704404</v>
+        <v>1453.627887194642</v>
       </c>
       <c r="D18">
-        <v>1723.374876704404</v>
+        <v>1725.163887194642</v>
       </c>
       <c r="E18">
         <v>271.536</v>
@@ -2706,37 +2742,37 @@
         <v>198.7</v>
       </c>
       <c r="M18">
-        <v>14.0384112</v>
+        <v>13.6582608</v>
       </c>
       <c r="N18">
-        <v>184.6615888</v>
+        <v>185.0417392</v>
       </c>
       <c r="O18">
-        <v>47.6426899104</v>
+        <v>47.7407687136</v>
       </c>
       <c r="P18">
-        <v>137.0188988896</v>
+        <v>137.3009704864</v>
       </c>
       <c r="Q18">
-        <v>290.1188988896</v>
+        <v>290.4009704864</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08118195801837526</v>
+        <v>0.08115921056519812</v>
       </c>
       <c r="T18">
         <v>0.8166099437690097</v>
       </c>
       <c r="U18">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2744,7 +2780,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.15402335557745</v>
+        <v>14.54797231577245</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2755,13 +2791,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07417630132332592</v>
+        <v>0.07398064888359393</v>
       </c>
       <c r="C19">
-        <v>1436.537096290009</v>
+        <v>1438.441729511534</v>
       </c>
       <c r="D19">
-        <v>1725.044096290009</v>
+        <v>1726.948729511534</v>
       </c>
       <c r="E19">
         <v>288.507</v>
@@ -2788,37 +2824,37 @@
         <v>198.7</v>
       </c>
       <c r="M19">
-        <v>14.9158119</v>
+        <v>14.5119021</v>
       </c>
       <c r="N19">
-        <v>183.7841881</v>
+        <v>184.1880979</v>
       </c>
       <c r="O19">
-        <v>47.4163205298</v>
+        <v>47.5205292582</v>
       </c>
       <c r="P19">
-        <v>136.3678675702</v>
+        <v>136.6675686418</v>
       </c>
       <c r="Q19">
-        <v>289.4678675702</v>
+        <v>289.7675686418</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08151188352207941</v>
+        <v>0.08148892395613726</v>
       </c>
       <c r="T19">
         <v>0.8242245717352715</v>
       </c>
       <c r="U19">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2826,7 +2862,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.32143374642583</v>
+        <v>13.69220923837407</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2837,13 +2873,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07416884991121664</v>
+        <v>0.07381594489242142</v>
       </c>
       <c r="C20">
-        <v>1419.646752382958</v>
+        <v>1423.259268823704</v>
       </c>
       <c r="D20">
-        <v>1725.124752382958</v>
+        <v>1728.737268823704</v>
       </c>
       <c r="E20">
         <v>305.478</v>
@@ -2870,45 +2906,45 @@
         <v>198.7</v>
       </c>
       <c r="M20">
-        <v>16.1292384</v>
+        <v>15.3655434</v>
       </c>
       <c r="N20">
-        <v>182.5707616</v>
+        <v>183.3344566</v>
       </c>
       <c r="O20">
-        <v>47.10325649280001</v>
+        <v>47.3002898028</v>
       </c>
       <c r="P20">
-        <v>135.4675051072</v>
+        <v>136.0341667972</v>
       </c>
       <c r="Q20">
-        <v>288.5675051072</v>
+        <v>289.1341667972</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08184985598928857</v>
+        <v>0.08182667913709929</v>
       </c>
       <c r="T20">
         <v>0.8320249223348567</v>
       </c>
       <c r="U20">
-        <v>0.0528</v>
+        <v>0.0503</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.0391776</v>
+        <v>0.0373226</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>12.31924255022482</v>
+        <v>12.93153094735329</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2919,13 +2955,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07402264449910734</v>
+        <v>0.07386271090124893</v>
       </c>
       <c r="C21">
-        <v>1404.259846421102</v>
+        <v>1405.78005493158</v>
       </c>
       <c r="D21">
-        <v>1726.708846421102</v>
+        <v>1728.22905493158</v>
       </c>
       <c r="E21">
         <v>322.449</v>
@@ -2952,37 +2988,37 @@
         <v>198.7</v>
       </c>
       <c r="M21">
-        <v>17.0253072</v>
+        <v>16.7028582</v>
       </c>
       <c r="N21">
-        <v>181.6746928</v>
+        <v>181.9971418</v>
       </c>
       <c r="O21">
-        <v>46.87207074240001</v>
+        <v>46.9552625844</v>
       </c>
       <c r="P21">
-        <v>134.8026220576</v>
+        <v>135.0418792156</v>
       </c>
       <c r="Q21">
-        <v>287.9026220576</v>
+        <v>288.1418792156</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08219617345568807</v>
+        <v>0.08217277395215916</v>
       </c>
       <c r="T21">
         <v>0.8400178741838146</v>
       </c>
       <c r="U21">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.258</v>
       </c>
       <c r="W21">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -2990,7 +3026,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.67086136337088</v>
+        <v>11.89616756729695</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3001,13 +3037,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07387643908699804</v>
+        <v>0.07370913691007644</v>
       </c>
       <c r="C22">
-        <v>1388.875852318516</v>
+        <v>1390.479090311077</v>
       </c>
       <c r="D22">
-        <v>1728.295852318516</v>
+        <v>1729.899090311078</v>
       </c>
       <c r="E22">
         <v>339.42</v>
@@ -3034,37 +3070,37 @@
         <v>198.7</v>
       </c>
       <c r="M22">
-        <v>17.921376</v>
+        <v>17.581956</v>
       </c>
       <c r="N22">
-        <v>180.778624</v>
+        <v>181.118044</v>
       </c>
       <c r="O22">
-        <v>46.640884992</v>
+        <v>46.728455352</v>
       </c>
       <c r="P22">
-        <v>134.137739008</v>
+        <v>134.389588648</v>
       </c>
       <c r="Q22">
-        <v>287.237739008</v>
+        <v>287.489588648</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08255114885874754</v>
+        <v>0.08252752113759554</v>
       </c>
       <c r="T22">
         <v>0.8482106498289962</v>
       </c>
       <c r="U22">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3072,7 +3108,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.08731829520233</v>
+        <v>11.30135918893211</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3083,13 +3119,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07373023367488873</v>
+        <v>0.07355556291890392</v>
       </c>
       <c r="C23">
-        <v>1373.494778111395</v>
+        <v>1375.181356414967</v>
       </c>
       <c r="D23">
-        <v>1729.885778111395</v>
+        <v>1731.572356414968</v>
       </c>
       <c r="E23">
         <v>356.391</v>
@@ -3116,37 +3152,37 @@
         <v>198.7</v>
       </c>
       <c r="M23">
-        <v>18.8174448</v>
+        <v>18.4610538</v>
       </c>
       <c r="N23">
-        <v>179.8825552</v>
+        <v>180.2389462</v>
       </c>
       <c r="O23">
-        <v>46.4096992416</v>
+        <v>46.50164811960001</v>
       </c>
       <c r="P23">
-        <v>133.4728559584</v>
+        <v>133.7372980804</v>
       </c>
       <c r="Q23">
-        <v>286.5728559584</v>
+        <v>286.8372980804</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08291511098087181</v>
+        <v>0.08289124926443535</v>
       </c>
       <c r="T23">
         <v>0.856610837515828</v>
       </c>
       <c r="U23">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.258</v>
       </c>
       <c r="W23">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3154,7 +3190,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.55935075733556</v>
+        <v>10.76319922755439</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3165,13 +3201,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07358402826277946</v>
+        <v>0.07340198892773142</v>
       </c>
       <c r="C24">
-        <v>1358.116631865528</v>
+        <v>1359.886862627199</v>
       </c>
       <c r="D24">
-        <v>1731.478631865528</v>
+        <v>1733.248862627199</v>
       </c>
       <c r="E24">
         <v>373.362</v>
@@ -3198,37 +3234,37 @@
         <v>198.7</v>
       </c>
       <c r="M24">
-        <v>19.7135136</v>
+        <v>19.3401516</v>
       </c>
       <c r="N24">
-        <v>178.9864864</v>
+        <v>179.3598484</v>
       </c>
       <c r="O24">
-        <v>46.17851349120001</v>
+        <v>46.27484088720001</v>
       </c>
       <c r="P24">
-        <v>132.8079729088</v>
+        <v>133.0850075128</v>
       </c>
       <c r="Q24">
-        <v>285.9079729088</v>
+        <v>286.1850075128</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08328840546510186</v>
+        <v>0.08326430375350183</v>
       </c>
       <c r="T24">
         <v>0.8652264146305274</v>
       </c>
       <c r="U24">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3236,7 +3272,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.07938026836576</v>
+        <v>10.27396289902919</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3247,13 +3283,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07381327485067014</v>
+        <v>0.07324841493655893</v>
       </c>
       <c r="C25">
-        <v>1338.649379591051</v>
+        <v>1344.595618368098</v>
       </c>
       <c r="D25">
-        <v>1728.982379591051</v>
+        <v>1734.928618368098</v>
       </c>
       <c r="E25">
         <v>390.333</v>
@@ -3280,45 +3316,45 @@
         <v>198.7</v>
       </c>
       <c r="M25">
-        <v>21.468315</v>
+        <v>20.2192494</v>
       </c>
       <c r="N25">
-        <v>177.231685</v>
+        <v>178.4807506</v>
       </c>
       <c r="O25">
-        <v>45.72577473</v>
+        <v>46.04803365480001</v>
       </c>
       <c r="P25">
-        <v>131.50591027</v>
+        <v>132.4327169452</v>
       </c>
       <c r="Q25">
-        <v>284.60591027</v>
+        <v>285.5327169452</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08367139590996123</v>
+        <v>0.08364704796955705</v>
       </c>
       <c r="T25">
         <v>0.8740657729689851</v>
       </c>
       <c r="U25">
-        <v>0.055</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.04081</v>
+        <v>0.0384356</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>9.255500489908037</v>
+        <v>9.827268859940965</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3329,13 +3365,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07368339343856085</v>
+        <v>0.07339757694538644</v>
       </c>
       <c r="C26">
-        <v>1323.091765972769</v>
+        <v>1325.993074457792</v>
       </c>
       <c r="D26">
-        <v>1730.395765972769</v>
+        <v>1733.297074457792</v>
       </c>
       <c r="E26">
         <v>407.304</v>
@@ -3362,37 +3398,37 @@
         <v>198.7</v>
       </c>
       <c r="M26">
-        <v>22.40172</v>
+        <v>21.790764</v>
       </c>
       <c r="N26">
-        <v>176.29828</v>
+        <v>176.909236</v>
       </c>
       <c r="O26">
-        <v>45.48495624000001</v>
+        <v>45.64258288800001</v>
       </c>
       <c r="P26">
-        <v>130.81332376</v>
+        <v>131.266653112</v>
       </c>
       <c r="Q26">
-        <v>283.91332376</v>
+        <v>284.366653112</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08406446505073797</v>
+        <v>0.08403986440182426</v>
       </c>
       <c r="T26">
         <v>0.8831377460005603</v>
       </c>
       <c r="U26">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3400,7 +3436,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.869854636161868</v>
+        <v>9.118542149325284</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3411,13 +3447,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07355351202645156</v>
+        <v>0.07325661695421393</v>
       </c>
       <c r="C27">
-        <v>1307.536465039041</v>
+        <v>1310.56382435707</v>
       </c>
       <c r="D27">
-        <v>1731.811465039041</v>
+        <v>1734.83882435707</v>
       </c>
       <c r="E27">
         <v>424.275</v>
@@ -3444,37 +3480,37 @@
         <v>198.7</v>
       </c>
       <c r="M27">
-        <v>23.335125</v>
+        <v>22.6987125</v>
       </c>
       <c r="N27">
-        <v>175.364875</v>
+        <v>176.0012875</v>
       </c>
       <c r="O27">
-        <v>45.24413775000001</v>
+        <v>45.40833217500001</v>
       </c>
       <c r="P27">
-        <v>130.12073725</v>
+        <v>130.592955325</v>
       </c>
       <c r="Q27">
-        <v>283.22073725</v>
+        <v>283.692955325</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08446801603526875</v>
+        <v>0.08444315593895191</v>
       </c>
       <c r="T27">
         <v>0.8924516383129774</v>
       </c>
       <c r="U27">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3482,7 +3518,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.515060450715392</v>
+        <v>8.753800463352274</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3493,13 +3529,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07342363061434226</v>
+        <v>0.07311565696304145</v>
       </c>
       <c r="C28">
-        <v>1291.983482470787</v>
+        <v>1295.137319439478</v>
       </c>
       <c r="D28">
-        <v>1733.229482470787</v>
+        <v>1736.383319439478</v>
       </c>
       <c r="E28">
         <v>441.246</v>
@@ -3526,37 +3562,37 @@
         <v>198.7</v>
       </c>
       <c r="M28">
-        <v>24.26853</v>
+        <v>23.606661</v>
       </c>
       <c r="N28">
-        <v>174.43147</v>
+        <v>175.093339</v>
       </c>
       <c r="O28">
-        <v>45.00331926</v>
+        <v>45.174081462</v>
       </c>
       <c r="P28">
-        <v>129.42815074</v>
+        <v>129.919257538</v>
       </c>
       <c r="Q28">
-        <v>282.52815074</v>
+        <v>283.019257538</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08488247380316523</v>
+        <v>0.0848573472473533</v>
       </c>
       <c r="T28">
         <v>0.9020172574446489</v>
       </c>
       <c r="U28">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.258</v>
       </c>
       <c r="W28">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3564,7 +3600,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.187558125687879</v>
+        <v>8.417115830146416</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3575,13 +3611,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07329374920223297</v>
+        <v>0.07297469697186894</v>
       </c>
       <c r="C29">
-        <v>1276.432823967548</v>
+        <v>1279.713567043509</v>
       </c>
       <c r="D29">
-        <v>1734.649823967548</v>
+        <v>1737.930567043509</v>
       </c>
       <c r="E29">
         <v>458.217</v>
@@ -3608,37 +3644,37 @@
         <v>198.7</v>
       </c>
       <c r="M29">
-        <v>25.201935</v>
+        <v>24.5146095</v>
       </c>
       <c r="N29">
-        <v>173.498065</v>
+        <v>174.1853905</v>
       </c>
       <c r="O29">
-        <v>44.76250077000001</v>
+        <v>44.939830749</v>
       </c>
       <c r="P29">
-        <v>128.73556423</v>
+        <v>129.245559751</v>
       </c>
       <c r="Q29">
-        <v>281.83556423</v>
+        <v>282.345559751</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08530828657840134</v>
+        <v>0.08528288626283417</v>
       </c>
       <c r="T29">
         <v>0.9118449483333527</v>
       </c>
       <c r="U29">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.258</v>
       </c>
       <c r="W29">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3646,7 +3682,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.884315232143883</v>
+        <v>8.105370799400252</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3657,13 +3693,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07347550779012368</v>
+        <v>0.07283373698069645</v>
       </c>
       <c r="C30">
-        <v>1257.474820146513</v>
+        <v>1264.292574533832</v>
       </c>
       <c r="D30">
-        <v>1732.662820146513</v>
+        <v>1739.480574533832</v>
       </c>
       <c r="E30">
         <v>475.188</v>
@@ -3690,45 +3726,45 @@
         <v>198.7</v>
       </c>
       <c r="M30">
-        <v>26.848122</v>
+        <v>25.422558</v>
       </c>
       <c r="N30">
-        <v>171.851878</v>
+        <v>173.277442</v>
       </c>
       <c r="O30">
-        <v>44.337784524</v>
+        <v>44.705580036</v>
       </c>
       <c r="P30">
-        <v>127.514093476</v>
+        <v>128.571861964</v>
       </c>
       <c r="Q30">
-        <v>280.614093476</v>
+        <v>281.671861964</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.0857459274862829</v>
+        <v>0.08572024580652285</v>
       </c>
       <c r="T30">
         <v>0.9219456306356315</v>
       </c>
       <c r="U30">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.041923</v>
+        <v>0.039697</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.40089008832722</v>
+        <v>7.815893270850243</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3739,13 +3775,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07335675637801438</v>
+        <v>0.07286492098952395</v>
       </c>
       <c r="C31">
-        <v>1241.801507075778</v>
+        <v>1246.97843452409</v>
       </c>
       <c r="D31">
-        <v>1733.960507075778</v>
+        <v>1739.13743452409</v>
       </c>
       <c r="E31">
         <v>492.1589999999999</v>
@@ -3772,37 +3808,37 @@
         <v>198.7</v>
       </c>
       <c r="M31">
-        <v>27.8069835</v>
+        <v>26.7242337</v>
       </c>
       <c r="N31">
-        <v>170.8930165</v>
+        <v>171.9757663</v>
       </c>
       <c r="O31">
-        <v>44.090398257</v>
+        <v>44.36974770540001</v>
       </c>
       <c r="P31">
-        <v>126.802618243</v>
+        <v>127.6060185946</v>
       </c>
       <c r="Q31">
-        <v>279.902618243</v>
+        <v>280.7060185946</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08619589630706251</v>
+        <v>0.08616992533735768</v>
       </c>
       <c r="T31">
         <v>0.9323308391999462</v>
       </c>
       <c r="U31">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.258</v>
       </c>
       <c r="W31">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3810,7 +3846,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.14568698183318</v>
+        <v>7.435199161575961</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3821,13 +3857,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07323800496590509</v>
+        <v>0.07272989699835145</v>
       </c>
       <c r="C32">
-        <v>1226.130139280863</v>
+        <v>1231.494177118997</v>
       </c>
       <c r="D32">
-        <v>1735.260139280863</v>
+        <v>1740.624177118997</v>
       </c>
       <c r="E32">
         <v>509.1299999999999</v>
@@ -3854,37 +3890,37 @@
         <v>198.7</v>
       </c>
       <c r="M32">
-        <v>28.765845</v>
+        <v>27.645759</v>
       </c>
       <c r="N32">
-        <v>169.934155</v>
+        <v>171.054241</v>
       </c>
       <c r="O32">
-        <v>43.84301199000001</v>
+        <v>44.13199417800001</v>
       </c>
       <c r="P32">
-        <v>126.09114301</v>
+        <v>126.922246822</v>
       </c>
       <c r="Q32">
-        <v>279.19114301</v>
+        <v>280.022246822</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08665872137986441</v>
+        <v>0.08663245285478778</v>
       </c>
       <c r="T32">
         <v>0.9430127680089557</v>
       </c>
       <c r="U32">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.258</v>
       </c>
       <c r="W32">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3892,7 +3928,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.907497415772074</v>
+        <v>7.187359189523429</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3903,13 +3939,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.0731192535537958</v>
+        <v>0.07259487300717896</v>
       </c>
       <c r="C33">
-        <v>1210.460721139101</v>
+        <v>1216.012463842656</v>
       </c>
       <c r="D33">
-        <v>1736.561721139101</v>
+        <v>1742.113463842656</v>
       </c>
       <c r="E33">
         <v>526.101</v>
@@ -3936,37 +3972,37 @@
         <v>198.7</v>
       </c>
       <c r="M33">
-        <v>29.7247065</v>
+        <v>28.5672843</v>
       </c>
       <c r="N33">
-        <v>168.9752935</v>
+        <v>170.1327157</v>
       </c>
       <c r="O33">
-        <v>43.595625723</v>
+        <v>43.8942406506</v>
       </c>
       <c r="P33">
-        <v>125.379667777</v>
+        <v>126.2384750494</v>
       </c>
       <c r="Q33">
-        <v>278.479667777</v>
+        <v>279.3384750494</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08713496167216783</v>
+        <v>0.08710838696692602</v>
       </c>
       <c r="T33">
         <v>0.9540043179428642</v>
       </c>
       <c r="U33">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -3974,7 +4010,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.684674918489104</v>
+        <v>6.955508893087188</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -3985,13 +4021,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07300050214168649</v>
+        <v>0.07245984901600645</v>
       </c>
       <c r="C34">
-        <v>1194.793257040966</v>
+        <v>1200.533301230968</v>
       </c>
       <c r="D34">
-        <v>1737.865257040966</v>
+        <v>1743.605301230968</v>
       </c>
       <c r="E34">
         <v>543.072</v>
@@ -4018,37 +4054,37 @@
         <v>198.7</v>
       </c>
       <c r="M34">
-        <v>30.683568</v>
+        <v>29.4888096</v>
       </c>
       <c r="N34">
-        <v>168.016432</v>
+        <v>169.2111904</v>
       </c>
       <c r="O34">
-        <v>43.348239456</v>
+        <v>43.65648712320001</v>
       </c>
       <c r="P34">
-        <v>124.668192544</v>
+        <v>125.5547032768</v>
       </c>
       <c r="Q34">
-        <v>277.768192544</v>
+        <v>278.6547032768</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08762520903189192</v>
+        <v>0.08759831914118596</v>
       </c>
       <c r="T34">
         <v>0.9653191487571816</v>
       </c>
       <c r="U34">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.258</v>
       </c>
       <c r="W34">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4056,7 +4092,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.475778827286319</v>
+        <v>6.738149240178214</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4067,13 +4103,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.0728817507295772</v>
+        <v>0.07232482502483395</v>
       </c>
       <c r="C35">
-        <v>1179.127751390123</v>
+        <v>1185.056695842239</v>
       </c>
       <c r="D35">
-        <v>1739.170751390123</v>
+        <v>1745.099695842239</v>
       </c>
       <c r="E35">
         <v>560.043</v>
@@ -4100,37 +4136,37 @@
         <v>198.7</v>
       </c>
       <c r="M35">
-        <v>31.6424295</v>
+        <v>30.4103349</v>
       </c>
       <c r="N35">
-        <v>167.0575705</v>
+        <v>168.2896651</v>
       </c>
       <c r="O35">
-        <v>43.10085318900001</v>
+        <v>43.41873359580001</v>
       </c>
       <c r="P35">
-        <v>123.956717311</v>
+        <v>124.8709315042</v>
       </c>
       <c r="Q35">
-        <v>277.056717311</v>
+        <v>277.9709315042</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08813009064116001</v>
+        <v>0.08810287615646858</v>
       </c>
       <c r="T35">
         <v>0.9769717357152099</v>
       </c>
       <c r="U35">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V35">
         <v>0.258</v>
       </c>
       <c r="W35">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4138,7 +4174,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.279543105247339</v>
+        <v>6.533962899566752</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4149,13 +4185,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07311619131746791</v>
+        <v>0.07218980103366145</v>
       </c>
       <c r="C36">
-        <v>1159.581310786242</v>
+        <v>1169.582654257279</v>
       </c>
       <c r="D36">
-        <v>1736.595310786242</v>
+        <v>1746.596654257279</v>
       </c>
       <c r="E36">
         <v>577.014</v>
@@ -4182,45 +4218,45 @@
         <v>198.7</v>
       </c>
       <c r="M36">
-        <v>33.4091106</v>
+        <v>31.3318602</v>
       </c>
       <c r="N36">
-        <v>165.2908894</v>
+        <v>167.3681398</v>
       </c>
       <c r="O36">
-        <v>42.64504946520001</v>
+        <v>43.1809800684</v>
       </c>
       <c r="P36">
-        <v>122.6458399348</v>
+        <v>124.1871597316</v>
       </c>
       <c r="Q36">
-        <v>275.7458399348</v>
+        <v>277.2871597316</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08865027169313321</v>
+        <v>0.08862272277827493</v>
       </c>
       <c r="T36">
         <v>0.9889774313689361</v>
       </c>
       <c r="U36">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.258</v>
       </c>
       <c r="W36">
-        <v>0.0429618</v>
+        <v>0.0402906</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>5.947479487825696</v>
+        <v>6.34178752016773</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4231,13 +4267,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07300782790535862</v>
+        <v>0.07205477704248894</v>
       </c>
       <c r="C37">
-        <v>1143.799785394809</v>
+        <v>1154.111183079498</v>
       </c>
       <c r="D37">
-        <v>1737.784785394809</v>
+        <v>1748.096183079497</v>
       </c>
       <c r="E37">
         <v>593.985</v>
@@ -4264,45 +4300,45 @@
         <v>198.7</v>
       </c>
       <c r="M37">
-        <v>34.3917315</v>
+        <v>32.2533855</v>
       </c>
       <c r="N37">
-        <v>164.3082685</v>
+        <v>166.4466145</v>
       </c>
       <c r="O37">
-        <v>42.39153327300001</v>
+        <v>42.943226541</v>
       </c>
       <c r="P37">
-        <v>121.916735227</v>
+        <v>123.503387959</v>
       </c>
       <c r="Q37">
-        <v>275.016735227</v>
+        <v>276.603387959</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08918645831593634</v>
+        <v>0.08915856468075224</v>
       </c>
       <c r="T37">
         <v>1.001352533042777</v>
       </c>
       <c r="U37">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V37">
         <v>0.258</v>
       </c>
       <c r="W37">
-        <v>0.0429618</v>
+        <v>0.0402906</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y37">
-        <v>5.777551502459247</v>
+        <v>6.160593591020081</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4313,13 +4349,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07289946449324933</v>
+        <v>0.07218687305131646</v>
       </c>
       <c r="C38">
-        <v>1128.019890572797</v>
+        <v>1135.673144107421</v>
       </c>
       <c r="D38">
-        <v>1738.975890572797</v>
+        <v>1746.629144107421</v>
       </c>
       <c r="E38">
         <v>610.9559999999999</v>
@@ -4346,37 +4382,37 @@
         <v>198.7</v>
       </c>
       <c r="M38">
-        <v>35.37435239999999</v>
+        <v>33.78586679999999</v>
       </c>
       <c r="N38">
-        <v>163.3256476</v>
+        <v>164.9141332</v>
       </c>
       <c r="O38">
-        <v>42.1380170808</v>
+        <v>42.54784636560001</v>
       </c>
       <c r="P38">
-        <v>121.1876305192</v>
+        <v>122.3662868344</v>
       </c>
       <c r="Q38">
-        <v>274.2876305192</v>
+        <v>275.4662868344</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08973940077070208</v>
+        <v>0.08971115164268198</v>
       </c>
       <c r="T38">
         <v>1.014114356643925</v>
       </c>
       <c r="U38">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.258</v>
       </c>
       <c r="W38">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4384,7 +4420,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.617063960724269</v>
+        <v>5.881157383832463</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4395,13 +4431,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07279110108114004</v>
+        <v>0.07205926906014395</v>
       </c>
       <c r="C39">
-        <v>1112.241629675359</v>
+        <v>1120.119254911898</v>
       </c>
       <c r="D39">
-        <v>1740.168629675359</v>
+        <v>1748.046254911897</v>
       </c>
       <c r="E39">
         <v>627.9269999999999</v>
@@ -4428,37 +4464,37 @@
         <v>198.7</v>
       </c>
       <c r="M39">
-        <v>36.35697329999999</v>
+        <v>34.7243631</v>
       </c>
       <c r="N39">
-        <v>162.3430267</v>
+        <v>163.9756369</v>
       </c>
       <c r="O39">
-        <v>41.88450088860001</v>
+        <v>42.3057143202</v>
       </c>
       <c r="P39">
-        <v>120.4585258114</v>
+        <v>121.6699225798</v>
       </c>
       <c r="Q39">
-        <v>273.5585258114</v>
+        <v>274.7699225798</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09030989695419053</v>
+        <v>0.09028128104784755</v>
       </c>
       <c r="T39">
         <v>1.027281317502253</v>
       </c>
       <c r="U39">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.258</v>
       </c>
       <c r="W39">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4466,7 +4502,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.465251421245235</v>
+        <v>5.722207184269422</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4477,13 +4513,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07268273766903074</v>
+        <v>0.07193166506897146</v>
       </c>
       <c r="C40">
-        <v>1096.465006066861</v>
+        <v>1104.567667102101</v>
       </c>
       <c r="D40">
-        <v>1741.363006066861</v>
+        <v>1749.465667102101</v>
       </c>
       <c r="E40">
         <v>644.898</v>
@@ -4510,37 +4546,37 @@
         <v>198.7</v>
       </c>
       <c r="M40">
-        <v>37.3395942</v>
+        <v>35.6628594</v>
       </c>
       <c r="N40">
-        <v>161.3604058</v>
+        <v>163.0371406</v>
       </c>
       <c r="O40">
-        <v>41.63098469640001</v>
+        <v>42.06358227480001</v>
       </c>
       <c r="P40">
-        <v>119.7294211036</v>
+        <v>120.9735583252</v>
       </c>
       <c r="Q40">
-        <v>272.8294211036</v>
+        <v>274.0735583252</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09089879624037216</v>
+        <v>0.09086980172414752</v>
       </c>
       <c r="T40">
         <v>1.04087301903343</v>
       </c>
       <c r="U40">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.258</v>
       </c>
       <c r="W40">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4548,7 +4584,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.321429015422991</v>
+        <v>5.571622784683385</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4559,13 +4595,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07257437425692145</v>
+        <v>0.07180406107779896</v>
       </c>
       <c r="C41">
-        <v>1080.690023120911</v>
+        <v>1089.018386288758</v>
       </c>
       <c r="D41">
-        <v>1742.559023120911</v>
+        <v>1750.887386288758</v>
       </c>
       <c r="E41">
         <v>661.869</v>
@@ -4592,37 +4628,37 @@
         <v>198.7</v>
       </c>
       <c r="M41">
-        <v>38.3222151</v>
+        <v>36.60135570000001</v>
       </c>
       <c r="N41">
-        <v>160.3777849</v>
+        <v>162.0986443</v>
       </c>
       <c r="O41">
-        <v>41.37746850420001</v>
+        <v>41.82145022940001</v>
       </c>
       <c r="P41">
-        <v>119.0003163958</v>
+        <v>120.2771940706</v>
       </c>
       <c r="Q41">
-        <v>272.1003163958</v>
+        <v>273.3771940706</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09150700369987122</v>
+        <v>0.09147761816032618</v>
       </c>
       <c r="T41">
         <v>1.054910350123006</v>
       </c>
       <c r="U41">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V41">
         <v>0.258</v>
       </c>
       <c r="W41">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4630,7 +4666,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.184982117591632</v>
+        <v>5.428760661999195</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4641,13 +4677,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07246601084481215</v>
+        <v>0.07167645708662647</v>
       </c>
       <c r="C42">
-        <v>1064.916684220392</v>
+        <v>1073.471418100847</v>
       </c>
       <c r="D42">
-        <v>1743.756684220392</v>
+        <v>1752.311418100847</v>
       </c>
       <c r="E42">
         <v>678.84</v>
@@ -4674,37 +4710,37 @@
         <v>198.7</v>
       </c>
       <c r="M42">
-        <v>39.304836</v>
+        <v>37.539852</v>
       </c>
       <c r="N42">
-        <v>159.395164</v>
+        <v>161.160148</v>
       </c>
       <c r="O42">
-        <v>41.12395231200001</v>
+        <v>41.57931818400001</v>
       </c>
       <c r="P42">
-        <v>118.271211688</v>
+        <v>119.580829816</v>
       </c>
       <c r="Q42">
-        <v>271.371211688</v>
+        <v>272.680829816</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.09213548474135358</v>
+        <v>0.09210569514437744</v>
       </c>
       <c r="T42">
         <v>1.069415592248902</v>
       </c>
       <c r="U42">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V42">
         <v>0.258</v>
       </c>
       <c r="W42">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4712,7 +4748,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.055357564651842</v>
+        <v>5.293041645449215</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4723,13 +4759,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07235764743270284</v>
+        <v>0.07154885309545396</v>
       </c>
       <c r="C43">
-        <v>1049.144992757493</v>
+        <v>1057.926768185677</v>
       </c>
       <c r="D43">
-        <v>1744.955992757493</v>
+        <v>1753.737768185677</v>
       </c>
       <c r="E43">
         <v>695.811</v>
@@ -4756,37 +4792,37 @@
         <v>198.7</v>
       </c>
       <c r="M43">
-        <v>40.2874569</v>
+        <v>38.4783483</v>
       </c>
       <c r="N43">
-        <v>158.4125431</v>
+        <v>160.2216517</v>
       </c>
       <c r="O43">
-        <v>40.8704361198</v>
+        <v>41.33718613860001</v>
       </c>
       <c r="P43">
-        <v>117.5421069802</v>
+        <v>118.8844655614</v>
       </c>
       <c r="Q43">
-        <v>270.6421069802</v>
+        <v>271.9844655614</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.09278527022492009</v>
+        <v>0.09275506287365079</v>
       </c>
       <c r="T43">
         <v>1.084412537497709</v>
       </c>
       <c r="U43">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.258</v>
       </c>
       <c r="W43">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4794,7 +4830,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.932056160635943</v>
+        <v>5.163943068730942</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4805,13 +4841,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07224928402059355</v>
+        <v>0.07142124910428149</v>
       </c>
       <c r="C44">
-        <v>1033.374952133742</v>
+        <v>1042.384442208955</v>
       </c>
       <c r="D44">
-        <v>1746.156952133742</v>
+        <v>1755.166442208955</v>
       </c>
       <c r="E44">
         <v>712.7819999999999</v>
@@ -4838,37 +4874,37 @@
         <v>198.7</v>
       </c>
       <c r="M44">
-        <v>41.2700778</v>
+        <v>39.4168446</v>
       </c>
       <c r="N44">
-        <v>157.4299222</v>
+        <v>159.2831554</v>
       </c>
       <c r="O44">
-        <v>40.61691992760001</v>
+        <v>41.09505409320001</v>
       </c>
       <c r="P44">
-        <v>116.8130022724</v>
+        <v>118.1881013068</v>
       </c>
       <c r="Q44">
-        <v>269.9130022724</v>
+        <v>271.2881013068</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.09345746210447164</v>
+        <v>0.09342682259358875</v>
       </c>
       <c r="T44">
         <v>1.099926618789578</v>
       </c>
       <c r="U44">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.258</v>
       </c>
       <c r="W44">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4876,7 +4912,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.814626252049373</v>
+        <v>5.040992043284968</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4887,13 +4923,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07214092060848427</v>
+        <v>0.07129364511310898</v>
       </c>
       <c r="C45">
-        <v>1017.606565760039</v>
+        <v>1026.844445854868</v>
       </c>
       <c r="D45">
-        <v>1747.359565760039</v>
+        <v>1756.597445854868</v>
       </c>
       <c r="E45">
         <v>729.7529999999999</v>
@@ -4920,37 +4956,37 @@
         <v>198.7</v>
       </c>
       <c r="M45">
-        <v>42.2526987</v>
+        <v>40.35534089999999</v>
       </c>
       <c r="N45">
-        <v>156.4473013</v>
+        <v>158.3446591</v>
       </c>
       <c r="O45">
-        <v>40.36340373540001</v>
+        <v>40.85292204780001</v>
       </c>
       <c r="P45">
-        <v>116.0838975646</v>
+        <v>117.4917370522</v>
       </c>
       <c r="Q45">
-        <v>269.1838975646</v>
+        <v>270.5917370522</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.09415323966400749</v>
+        <v>0.09412215283001574</v>
       </c>
       <c r="T45">
         <v>1.115985053810987</v>
       </c>
       <c r="U45">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.258</v>
       </c>
       <c r="W45">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4958,7 +4994,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.702658199676131</v>
+        <v>4.923759670185317</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -4969,13 +5005,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07203255719637497</v>
+        <v>0.07116604112193647</v>
       </c>
       <c r="C46">
-        <v>1001.839837056686</v>
+        <v>1011.306784826155</v>
       </c>
       <c r="D46">
-        <v>1748.563837056686</v>
+        <v>1758.030784826155</v>
       </c>
       <c r="E46">
         <v>746.7239999999999</v>
@@ -5002,37 +5038,37 @@
         <v>198.7</v>
       </c>
       <c r="M46">
-        <v>43.2353196</v>
+        <v>41.2938372</v>
       </c>
       <c r="N46">
-        <v>155.4646804</v>
+        <v>157.4061628</v>
       </c>
       <c r="O46">
-        <v>40.1098875432</v>
+        <v>40.6107900024</v>
       </c>
       <c r="P46">
-        <v>115.3547928568</v>
+        <v>116.7953727976</v>
       </c>
       <c r="Q46">
-        <v>268.4547928568</v>
+        <v>269.8953727976</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.09487386642209816</v>
+        <v>0.09484231628917228</v>
       </c>
       <c r="T46">
         <v>1.132617004368875</v>
       </c>
       <c r="U46">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.258</v>
       </c>
       <c r="W46">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5040,7 +5076,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.595779604228946</v>
+        <v>4.811856041317468</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5051,13 +5087,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07279233378426569</v>
+        <v>0.07103843713076398</v>
       </c>
       <c r="C47">
-        <v>976.4600523048698</v>
+        <v>995.7714648441843</v>
       </c>
       <c r="D47">
-        <v>1740.15505230487</v>
+        <v>1759.466464844184</v>
       </c>
       <c r="E47">
         <v>763.6949999999999</v>
@@ -5084,45 +5120,45 @@
         <v>198.7</v>
       </c>
       <c r="M47">
-        <v>46.20354749999999</v>
+        <v>42.2323335</v>
       </c>
       <c r="N47">
-        <v>152.4964525</v>
+        <v>156.4676665</v>
       </c>
       <c r="O47">
-        <v>39.34408474500001</v>
+        <v>40.368657957</v>
       </c>
       <c r="P47">
-        <v>113.152367755</v>
+        <v>116.099008543</v>
       </c>
       <c r="Q47">
-        <v>266.252367755</v>
+        <v>269.199008543</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.09562069778957397</v>
+        <v>0.09558866751047995</v>
       </c>
       <c r="T47">
         <v>1.149853753128868</v>
       </c>
       <c r="U47">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V47">
         <v>0.258</v>
       </c>
       <c r="W47">
-        <v>0.044891</v>
+        <v>0.0410326</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.300535581169391</v>
+        <v>4.704925907065969</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5133,13 +5169,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07270326237215638</v>
+        <v>0.07091083313959148</v>
       </c>
       <c r="C48">
-        <v>960.4706579180611</v>
+        <v>980.2384916490264</v>
       </c>
       <c r="D48">
-        <v>1741.136657918061</v>
+        <v>1760.904491649026</v>
       </c>
       <c r="E48">
         <v>780.6659999999999</v>
@@ -5166,45 +5202,45 @@
         <v>198.7</v>
       </c>
       <c r="M48">
-        <v>47.230293</v>
+        <v>43.1708298</v>
       </c>
       <c r="N48">
-        <v>151.469707</v>
+        <v>155.5291702</v>
       </c>
       <c r="O48">
-        <v>39.07918440600001</v>
+        <v>40.12652591160001</v>
       </c>
       <c r="P48">
-        <v>112.390522594</v>
+        <v>115.4026442884</v>
       </c>
       <c r="Q48">
-        <v>265.490522594</v>
+        <v>268.5026442884</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.09639518957806736</v>
+        <v>0.09636266136961386</v>
       </c>
       <c r="T48">
         <v>1.167728899991082</v>
       </c>
       <c r="U48">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V48">
         <v>0.258</v>
       </c>
       <c r="W48">
-        <v>0.044891</v>
+        <v>0.0410326</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.207045677230925</v>
+        <v>4.602644909086274</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5215,13 +5251,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07261419096004709</v>
+        <v>0.07078322914841897</v>
       </c>
       <c r="C49">
-        <v>944.4823715858646</v>
+        <v>964.7078709995347</v>
       </c>
       <c r="D49">
-        <v>1742.119371585865</v>
+        <v>1762.344870999535</v>
       </c>
       <c r="E49">
         <v>797.6370000000001</v>
@@ -5248,45 +5284,45 @@
         <v>198.7</v>
       </c>
       <c r="M49">
-        <v>48.2570385</v>
+        <v>44.1093261</v>
       </c>
       <c r="N49">
-        <v>150.4429615</v>
+        <v>154.5906739</v>
       </c>
       <c r="O49">
-        <v>38.81428406700001</v>
+        <v>39.88439386620001</v>
       </c>
       <c r="P49">
-        <v>111.628677433</v>
+        <v>114.7062800338</v>
       </c>
       <c r="Q49">
-        <v>264.728677433</v>
+        <v>267.8062800338</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09719890747178694</v>
+        <v>0.09716586254418674</v>
       </c>
       <c r="T49">
         <v>1.186278580697154</v>
       </c>
       <c r="U49">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.258</v>
       </c>
       <c r="W49">
-        <v>0.044891</v>
+        <v>0.0410326</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.117534067077075</v>
+        <v>4.504716293999332</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5297,13 +5333,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07252511954793779</v>
+        <v>0.07154602515724648</v>
       </c>
       <c r="C50">
-        <v>928.4951951855294</v>
+        <v>939.1614050176602</v>
       </c>
       <c r="D50">
-        <v>1743.103195185529</v>
+        <v>1753.76940501766</v>
       </c>
       <c r="E50">
         <v>814.6079999999999</v>
@@ -5330,37 +5366,37 @@
         <v>198.7</v>
       </c>
       <c r="M50">
-        <v>49.283784</v>
+        <v>47.0843424</v>
       </c>
       <c r="N50">
-        <v>149.416216</v>
+        <v>151.6156576</v>
       </c>
       <c r="O50">
-        <v>38.54938372800001</v>
+        <v>39.1168396608</v>
       </c>
       <c r="P50">
-        <v>110.866832272</v>
+        <v>112.4988179392</v>
       </c>
       <c r="Q50">
-        <v>263.966832272</v>
+        <v>265.5988179392</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09803353759218805</v>
+        <v>0.09799995607162784</v>
       </c>
       <c r="T50">
         <v>1.205541710661151</v>
       </c>
       <c r="U50">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V50">
         <v>0.258</v>
       </c>
       <c r="W50">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5368,7 +5404,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.031752107346303</v>
+        <v>4.220086548346909</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5379,13 +5415,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.07341771413582851</v>
+        <v>0.07143697116607399</v>
       </c>
       <c r="C51">
-        <v>901.7151326176859</v>
+        <v>923.4112898547576</v>
       </c>
       <c r="D51">
-        <v>1733.294132617686</v>
+        <v>1754.990289854758</v>
       </c>
       <c r="E51">
         <v>831.579</v>
@@ -5412,45 +5448,45 @@
         <v>198.7</v>
       </c>
       <c r="M51">
-        <v>52.5557928</v>
+        <v>48.0652662</v>
       </c>
       <c r="N51">
-        <v>146.1442072</v>
+        <v>150.6347338</v>
       </c>
       <c r="O51">
-        <v>37.7052054576</v>
+        <v>38.86376132040001</v>
       </c>
       <c r="P51">
-        <v>108.4390017424</v>
+        <v>111.7709724796</v>
       </c>
       <c r="Q51">
-        <v>261.5390017424</v>
+        <v>264.8709724796</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09890089830554608</v>
+        <v>0.09886675914916468</v>
       </c>
       <c r="T51">
         <v>1.225560257486482</v>
       </c>
       <c r="U51">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V51">
         <v>0.258</v>
       </c>
       <c r="W51">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.780744032463725</v>
+        <v>4.133962333074523</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5461,13 +5497,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.0733486767237192</v>
+        <v>0.07132791717490149</v>
       </c>
       <c r="C52">
-        <v>885.4988702286</v>
+        <v>907.6628757115625</v>
       </c>
       <c r="D52">
-        <v>1734.0488702286</v>
+        <v>1756.212875711562</v>
       </c>
       <c r="E52">
         <v>848.55</v>
@@ -5494,45 +5530,45 @@
         <v>198.7</v>
       </c>
       <c r="M52">
-        <v>53.62836</v>
+        <v>49.04619</v>
       </c>
       <c r="N52">
-        <v>145.07164</v>
+        <v>149.65381</v>
       </c>
       <c r="O52">
-        <v>37.42848312</v>
+        <v>38.61068298000001</v>
       </c>
       <c r="P52">
-        <v>107.64315688</v>
+        <v>111.04312702</v>
       </c>
       <c r="Q52">
-        <v>260.74315688</v>
+        <v>264.14312702</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09980295344743841</v>
+        <v>0.09976823434980298</v>
       </c>
       <c r="T52">
         <v>1.246379546184826</v>
       </c>
       <c r="U52">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V52">
         <v>0.258</v>
       </c>
       <c r="W52">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.70512915181445</v>
+        <v>4.051283086413033</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5543,13 +5579,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.07327963931160991</v>
+        <v>0.07254333318372899</v>
       </c>
       <c r="C53">
-        <v>869.2832654047761</v>
+        <v>877.1616097132603</v>
       </c>
       <c r="D53">
-        <v>1734.804265404776</v>
+        <v>1742.68260971326</v>
       </c>
       <c r="E53">
         <v>865.521</v>
@@ -5576,37 +5612,37 @@
         <v>198.7</v>
       </c>
       <c r="M53">
-        <v>54.7009272</v>
+        <v>53.0564373</v>
       </c>
       <c r="N53">
-        <v>143.9990728</v>
+        <v>145.6435627</v>
       </c>
       <c r="O53">
-        <v>37.1517607824</v>
+        <v>37.57603917660001</v>
       </c>
       <c r="P53">
-        <v>106.8473120176</v>
+        <v>108.0675235234</v>
       </c>
       <c r="Q53">
-        <v>259.9473120176</v>
+        <v>261.1675235234</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1007418271665508</v>
+        <v>0.1007065044565898</v>
       </c>
       <c r="T53">
         <v>1.268048601768817</v>
       </c>
       <c r="U53">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V53">
         <v>0.258</v>
       </c>
       <c r="W53">
-        <v>0.0468944</v>
+        <v>0.0454846</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5614,7 +5650,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.632479560602403</v>
+        <v>3.745068649756474</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5625,13 +5661,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.07321060189950061</v>
+        <v>0.07246024919255649</v>
       </c>
       <c r="C54">
-        <v>853.068319005946</v>
+        <v>861.1088760317882</v>
       </c>
       <c r="D54">
-        <v>1735.560319005946</v>
+        <v>1743.600876031788</v>
       </c>
       <c r="E54">
         <v>882.492</v>
@@ -5658,37 +5694,37 @@
         <v>198.7</v>
       </c>
       <c r="M54">
-        <v>55.7734944</v>
+        <v>54.0967596</v>
       </c>
       <c r="N54">
-        <v>142.9265056</v>
+        <v>144.6032404</v>
       </c>
       <c r="O54">
-        <v>36.8750384448</v>
+        <v>37.3076360232</v>
       </c>
       <c r="P54">
-        <v>106.0514671552</v>
+        <v>107.2956043768</v>
       </c>
       <c r="Q54">
-        <v>259.1514671552</v>
+        <v>260.3956043768</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1017198206239596</v>
+        <v>0.1016838691511593</v>
       </c>
       <c r="T54">
         <v>1.290620534668807</v>
       </c>
       <c r="U54">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V54">
         <v>0.258</v>
       </c>
       <c r="W54">
-        <v>0.0468944</v>
+        <v>0.0454846</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5696,7 +5732,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.562624184436971</v>
+        <v>3.673048098799618</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5707,13 +5743,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.07498988648739133</v>
+        <v>0.07237716520138399</v>
       </c>
       <c r="C55">
-        <v>816.8197680087176</v>
+        <v>845.0571105789229</v>
       </c>
       <c r="D55">
-        <v>1716.282768008718</v>
+        <v>1744.520110578923</v>
       </c>
       <c r="E55">
         <v>899.463</v>
@@ -5740,45 +5776,45 @@
         <v>198.7</v>
       </c>
       <c r="M55">
-        <v>61.0735377</v>
+        <v>55.1370819</v>
       </c>
       <c r="N55">
-        <v>137.6264623</v>
+        <v>143.5629181</v>
       </c>
       <c r="O55">
-        <v>35.5076272734</v>
+        <v>37.0392328698</v>
       </c>
       <c r="P55">
-        <v>102.1188350266</v>
+        <v>106.5236852302</v>
       </c>
       <c r="Q55">
-        <v>255.2188350266</v>
+        <v>259.6236852302</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1027394308242369</v>
+        <v>0.1027028238327319</v>
       </c>
       <c r="T55">
         <v>1.314152975351776</v>
       </c>
       <c r="U55">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V55">
         <v>0.258</v>
       </c>
       <c r="W55">
-        <v>0.0503818</v>
+        <v>0.0454846</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.25345489197034</v>
+        <v>3.603745304482645</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5789,13 +5825,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.07495572307528202</v>
+        <v>0.0722940812102115</v>
       </c>
       <c r="C56">
-        <v>800.2148761993221</v>
+        <v>829.006314886836</v>
       </c>
       <c r="D56">
-        <v>1716.648876199322</v>
+        <v>1745.440314886836</v>
       </c>
       <c r="E56">
         <v>916.434</v>
@@ -5822,45 +5858,45 @@
         <v>198.7</v>
       </c>
       <c r="M56">
-        <v>62.2258686</v>
+        <v>56.1774042</v>
       </c>
       <c r="N56">
-        <v>136.4741314</v>
+        <v>142.5225958</v>
       </c>
       <c r="O56">
-        <v>35.21032590120001</v>
+        <v>36.77082971640001</v>
       </c>
       <c r="P56">
-        <v>101.2638054988</v>
+        <v>105.7517660836</v>
       </c>
       <c r="Q56">
-        <v>254.3638054988</v>
+        <v>258.8517660836</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.103803371902787</v>
+        <v>0.1037660808917641</v>
       </c>
       <c r="T56">
         <v>1.338708565629656</v>
       </c>
       <c r="U56">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V56">
         <v>0.258</v>
       </c>
       <c r="W56">
-        <v>0.0503818</v>
+        <v>0.0454846</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.193205727304223</v>
+        <v>3.537009280325559</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5871,13 +5907,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.07492155966317274</v>
+        <v>0.073353677219039</v>
       </c>
       <c r="C57">
-        <v>783.6101406157038</v>
+        <v>800.3719338128005</v>
       </c>
       <c r="D57">
-        <v>1717.015140615704</v>
+        <v>1733.776933812801</v>
       </c>
       <c r="E57">
         <v>933.405</v>
@@ -5904,37 +5940,37 @@
         <v>198.7</v>
       </c>
       <c r="M57">
-        <v>63.3781995</v>
+        <v>59.8312605</v>
       </c>
       <c r="N57">
-        <v>135.3218005</v>
+        <v>138.8687395</v>
       </c>
       <c r="O57">
-        <v>34.913024529</v>
+        <v>35.828134791</v>
       </c>
       <c r="P57">
-        <v>100.408775971</v>
+        <v>103.040604709</v>
       </c>
       <c r="Q57">
-        <v>253.508775971</v>
+        <v>256.140604709</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.104914599251495</v>
+        <v>0.1048765938200867</v>
       </c>
       <c r="T57">
         <v>1.364355515475443</v>
       </c>
       <c r="U57">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V57">
         <v>0.258</v>
       </c>
       <c r="W57">
-        <v>0.0503818</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5942,7 +5978,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.135147441353237</v>
+        <v>3.321006416035644</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5953,13 +5989,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07488739625106343</v>
+        <v>0.0732913692278665</v>
       </c>
       <c r="C58">
-        <v>767.0055613578819</v>
+        <v>784.0824666777777</v>
       </c>
       <c r="D58">
-        <v>1717.381561357882</v>
+        <v>1734.458466677778</v>
       </c>
       <c r="E58">
         <v>950.3760000000001</v>
@@ -5986,37 +6022,37 @@
         <v>198.7</v>
       </c>
       <c r="M58">
-        <v>64.5305304</v>
+        <v>60.91910160000001</v>
       </c>
       <c r="N58">
-        <v>134.1694696</v>
+        <v>137.7808984</v>
       </c>
       <c r="O58">
-        <v>34.6157231568</v>
+        <v>35.5474717872</v>
       </c>
       <c r="P58">
-        <v>99.55374644320001</v>
+        <v>102.2334266128</v>
       </c>
       <c r="Q58">
-        <v>252.6537464432</v>
+        <v>255.3334266128</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1060763369342351</v>
+        <v>0.1060375846087875</v>
       </c>
       <c r="T58">
         <v>1.391168235768764</v>
       </c>
       <c r="U58">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V58">
         <v>0.258</v>
       </c>
       <c r="W58">
-        <v>0.0503818</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6024,7 +6060,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.079162665614787</v>
+        <v>3.261702730035007</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6035,13 +6071,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07485323283895415</v>
+        <v>0.07322906123669401</v>
       </c>
       <c r="C59">
-        <v>750.4011385259593</v>
+        <v>767.7935355629251</v>
       </c>
       <c r="D59">
-        <v>1717.748138525959</v>
+        <v>1735.140535562925</v>
       </c>
       <c r="E59">
         <v>967.3470000000001</v>
@@ -6068,37 +6104,37 @@
         <v>198.7</v>
       </c>
       <c r="M59">
-        <v>65.68286130000001</v>
+        <v>62.00694270000001</v>
       </c>
       <c r="N59">
-        <v>133.0171387</v>
+        <v>136.6930573</v>
       </c>
       <c r="O59">
-        <v>34.31842178460001</v>
+        <v>35.26680878340001</v>
       </c>
       <c r="P59">
-        <v>98.6987169154</v>
+        <v>101.4262485166</v>
       </c>
       <c r="Q59">
-        <v>251.7987169154</v>
+        <v>254.5262485166</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1072921089278003</v>
+        <v>0.1072525749690558</v>
       </c>
       <c r="T59">
         <v>1.419228059331543</v>
       </c>
       <c r="U59">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V59">
         <v>0.258</v>
       </c>
       <c r="W59">
-        <v>0.0503818</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6106,7 +6142,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.025142267972421</v>
+        <v>3.204479875122113</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6117,13 +6153,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.07882141742684484</v>
+        <v>0.07316675324552149</v>
       </c>
       <c r="C60">
-        <v>691.8723360400162</v>
+        <v>751.5051411008554</v>
       </c>
       <c r="D60">
-        <v>1676.190336040016</v>
+        <v>1735.823141100855</v>
       </c>
       <c r="E60">
         <v>984.3179999999999</v>
@@ -6150,45 +6186,45 @@
         <v>198.7</v>
       </c>
       <c r="M60">
-        <v>75.98934959999998</v>
+        <v>63.09478379999999</v>
       </c>
       <c r="N60">
-        <v>122.7106504</v>
+        <v>135.6052162</v>
       </c>
       <c r="O60">
-        <v>31.65934780320001</v>
+        <v>34.98614577960001</v>
       </c>
       <c r="P60">
-        <v>91.05130259680003</v>
+        <v>100.6190704204</v>
       </c>
       <c r="Q60">
-        <v>244.1513025968</v>
+        <v>253.7190704204</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1085657748258211</v>
+        <v>0.1085254220131464</v>
       </c>
       <c r="T60">
         <v>1.44862406496874</v>
       </c>
       <c r="U60">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V60">
         <v>0.258</v>
       </c>
       <c r="W60">
-        <v>0.05728239999999999</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.614840119647504</v>
+        <v>3.149230222102767</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6199,13 +6235,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.07885626001473554</v>
+        <v>0.073104445254349</v>
       </c>
       <c r="C61">
-        <v>674.5453420122318</v>
+        <v>735.217283925176</v>
       </c>
       <c r="D61">
-        <v>1675.834342012232</v>
+        <v>1736.506283925176</v>
       </c>
       <c r="E61">
         <v>1001.289</v>
@@ -6232,45 +6268,45 @@
         <v>198.7</v>
       </c>
       <c r="M61">
-        <v>77.29951079999998</v>
+        <v>64.18262489999999</v>
       </c>
       <c r="N61">
-        <v>121.4004892</v>
+        <v>134.5173751</v>
       </c>
       <c r="O61">
-        <v>31.32132621360001</v>
+        <v>34.70548277580001</v>
       </c>
       <c r="P61">
-        <v>90.07916298640004</v>
+        <v>99.81189232420003</v>
       </c>
       <c r="Q61">
-        <v>243.1791629864</v>
+        <v>252.9118923242</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1099015707676477</v>
+        <v>0.1098603591569488</v>
       </c>
       <c r="T61">
         <v>1.479454022100434</v>
       </c>
       <c r="U61">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V61">
         <v>0.258</v>
       </c>
       <c r="W61">
-        <v>0.05728239999999999</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.570520795585683</v>
+        <v>3.095853438677296</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6281,13 +6317,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.07889110260262625</v>
+        <v>0.0730421372631765</v>
       </c>
       <c r="C62">
-        <v>657.2184991663688</v>
+        <v>718.929964670493</v>
       </c>
       <c r="D62">
-        <v>1675.478499166369</v>
+        <v>1737.189964670493</v>
       </c>
       <c r="E62">
         <v>1018.26</v>
@@ -6314,45 +6350,45 @@
         <v>198.7</v>
       </c>
       <c r="M62">
-        <v>78.60967199999997</v>
+        <v>65.270466</v>
       </c>
       <c r="N62">
-        <v>120.090328</v>
+        <v>133.429534</v>
       </c>
       <c r="O62">
-        <v>30.98330462400001</v>
+        <v>34.42481977200001</v>
       </c>
       <c r="P62">
-        <v>89.10702337600003</v>
+        <v>99.00471422800001</v>
       </c>
       <c r="Q62">
-        <v>242.207023376</v>
+        <v>252.104714228</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1113041565065656</v>
+        <v>0.1112620431579412</v>
       </c>
       <c r="T62">
         <v>1.511825477088713</v>
       </c>
       <c r="U62">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V62">
         <v>0.258</v>
       </c>
       <c r="W62">
-        <v>0.05728239999999999</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.527678782325921</v>
+        <v>3.044255881366007</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6363,13 +6399,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08105325919051695</v>
+        <v>0.076510265272004</v>
       </c>
       <c r="C63">
-        <v>618.4574809550345</v>
+        <v>664.7059710400335</v>
       </c>
       <c r="D63">
-        <v>1653.688480955034</v>
+        <v>1699.936971040034</v>
       </c>
       <c r="E63">
         <v>1035.231</v>
@@ -6396,45 +6432,45 @@
         <v>198.7</v>
       </c>
       <c r="M63">
-        <v>84.7854189</v>
+        <v>74.43310890000001</v>
       </c>
       <c r="N63">
-        <v>113.9145811</v>
+        <v>124.2668911</v>
       </c>
       <c r="O63">
-        <v>29.3899619238</v>
+        <v>32.06085790380001</v>
       </c>
       <c r="P63">
-        <v>84.52461917620002</v>
+        <v>92.2060331962</v>
       </c>
       <c r="Q63">
-        <v>237.6246191762</v>
+        <v>245.3060331962</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1127786697192742</v>
+        <v>0.1127356083897539</v>
       </c>
       <c r="T63">
         <v>1.545857006691775</v>
       </c>
       <c r="U63">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V63">
         <v>0.258</v>
       </c>
       <c r="W63">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.343563345890363</v>
+        <v>2.669510960061484</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6445,13 +6481,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08112297577840766</v>
+        <v>0.07650583328083152</v>
       </c>
       <c r="C64">
-        <v>600.7933116290383</v>
+        <v>647.7815577836873</v>
       </c>
       <c r="D64">
-        <v>1652.995311629038</v>
+        <v>1699.983557783687</v>
       </c>
       <c r="E64">
         <v>1052.202</v>
@@ -6478,45 +6514,45 @@
         <v>198.7</v>
       </c>
       <c r="M64">
-        <v>86.17534380000001</v>
+        <v>75.65332380000001</v>
       </c>
       <c r="N64">
-        <v>112.5246562</v>
+        <v>123.0466762</v>
       </c>
       <c r="O64">
-        <v>29.0313612996</v>
+        <v>31.7460424596</v>
       </c>
       <c r="P64">
-        <v>83.4932949004</v>
+        <v>91.3006337404</v>
       </c>
       <c r="Q64">
-        <v>236.5932949004</v>
+        <v>244.4006337404</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1143307888905465</v>
+        <v>0.1142867296863987</v>
       </c>
       <c r="T64">
         <v>1.581679669431841</v>
       </c>
       <c r="U64">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V64">
         <v>0.258</v>
       </c>
       <c r="W64">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.30576393708568</v>
+        <v>2.626454331673395</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6527,13 +6563,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08119269236629836</v>
+        <v>0.07650140128965902</v>
       </c>
       <c r="C65">
-        <v>583.129723165039</v>
+        <v>630.8571470808292</v>
       </c>
       <c r="D65">
-        <v>1652.302723165039</v>
+        <v>1700.030147080829</v>
       </c>
       <c r="E65">
         <v>1069.173</v>
@@ -6560,45 +6596,45 @@
         <v>198.7</v>
       </c>
       <c r="M65">
-        <v>87.5652687</v>
+        <v>76.87353870000001</v>
       </c>
       <c r="N65">
-        <v>111.1347313</v>
+        <v>121.8264613</v>
       </c>
       <c r="O65">
-        <v>28.6727606754</v>
+        <v>31.4312270154</v>
       </c>
       <c r="P65">
-        <v>82.46197062460001</v>
+        <v>90.39523428460001</v>
       </c>
       <c r="Q65">
-        <v>235.5619706246</v>
+        <v>243.4952342846</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.115966806395401</v>
+        <v>0.1159216953774568</v>
       </c>
       <c r="T65">
         <v>1.619438692320018</v>
       </c>
       <c r="U65">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V65">
         <v>0.258</v>
       </c>
       <c r="W65">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.269164509512891</v>
+        <v>2.584764580376993</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6609,13 +6645,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08126240895418907</v>
+        <v>0.07649696929848651</v>
       </c>
       <c r="C66">
-        <v>565.4667148332167</v>
+        <v>613.9327389316688</v>
       </c>
       <c r="D66">
-        <v>1651.610714833217</v>
+        <v>1700.076738931669</v>
       </c>
       <c r="E66">
         <v>1086.144</v>
@@ -6642,45 +6678,45 @@
         <v>198.7</v>
       </c>
       <c r="M66">
-        <v>88.9551936</v>
+        <v>78.0937536</v>
       </c>
       <c r="N66">
-        <v>109.7448064</v>
+        <v>120.6062464</v>
       </c>
       <c r="O66">
-        <v>28.31416005120001</v>
+        <v>31.1164115712</v>
       </c>
       <c r="P66">
-        <v>81.43064634880001</v>
+        <v>89.48983482880001</v>
       </c>
       <c r="Q66">
-        <v>234.5306463488</v>
+        <v>242.5898348288</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1176937137616363</v>
+        <v>0.1176474924957959</v>
       </c>
       <c r="T66">
         <v>1.659295438701983</v>
       </c>
       <c r="U66">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V66">
         <v>0.258</v>
       </c>
       <c r="W66">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.233708814051752</v>
+        <v>2.544377633808602</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6691,13 +6727,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08133212554207978</v>
+        <v>0.07649253730731402</v>
       </c>
       <c r="C67">
-        <v>547.8042859049724</v>
+        <v>597.0083333364159</v>
       </c>
       <c r="D67">
-        <v>1650.919285904972</v>
+        <v>1700.123333336416</v>
       </c>
       <c r="E67">
         <v>1103.115</v>
@@ -6724,45 +6760,45 @@
         <v>198.7</v>
       </c>
       <c r="M67">
-        <v>90.3451185</v>
+        <v>79.3139685</v>
       </c>
       <c r="N67">
-        <v>108.3548815</v>
+        <v>119.3860315</v>
       </c>
       <c r="O67">
-        <v>27.955559427</v>
+        <v>30.801596127</v>
       </c>
       <c r="P67">
-        <v>80.39932207300001</v>
+        <v>88.58443537300002</v>
       </c>
       <c r="Q67">
-        <v>233.499322073</v>
+        <v>241.684435373</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1195193015487994</v>
+        <v>0.1194719065923258</v>
       </c>
       <c r="T67">
         <v>1.701429713448632</v>
       </c>
       <c r="U67">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V67">
         <v>0.258</v>
       </c>
       <c r="W67">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.199344063066341</v>
+        <v>2.505233362519239</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6773,13 +6809,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08140184212997049</v>
+        <v>0.07839801331614152</v>
       </c>
       <c r="C68">
-        <v>530.142435652928</v>
+        <v>560.2374455835961</v>
       </c>
       <c r="D68">
-        <v>1650.228435652928</v>
+        <v>1680.323445583596</v>
       </c>
       <c r="E68">
         <v>1120.086</v>
@@ -6806,37 +6842,37 @@
         <v>198.7</v>
       </c>
       <c r="M68">
-        <v>91.7350434</v>
+        <v>84.90251880000001</v>
       </c>
       <c r="N68">
-        <v>106.9649566</v>
+        <v>113.7974812</v>
       </c>
       <c r="O68">
-        <v>27.59695880280001</v>
+        <v>29.3597501496</v>
       </c>
       <c r="P68">
-        <v>79.36799779720002</v>
+        <v>84.4377310504</v>
       </c>
       <c r="Q68">
-        <v>232.4679977972</v>
+        <v>237.5377310504</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1214522768528544</v>
+        <v>0.1214036391651221</v>
       </c>
       <c r="T68">
         <v>1.746042474945084</v>
       </c>
       <c r="U68">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V68">
         <v>0.258</v>
       </c>
       <c r="W68">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6844,7 +6880,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.166020668171396</v>
+        <v>2.340331038565136</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6855,13 +6891,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.0814715587178612</v>
+        <v>0.07842251932496902</v>
       </c>
       <c r="C69">
-        <v>512.4811633509223</v>
+        <v>543.0148058338443</v>
       </c>
       <c r="D69">
-        <v>1649.538163350922</v>
+        <v>1680.071805833844</v>
       </c>
       <c r="E69">
         <v>1137.057</v>
@@ -6888,37 +6924,37 @@
         <v>198.7</v>
       </c>
       <c r="M69">
-        <v>93.12496830000001</v>
+        <v>86.1889206</v>
       </c>
       <c r="N69">
-        <v>105.5750317</v>
+        <v>112.5110794</v>
       </c>
       <c r="O69">
-        <v>27.2383581786</v>
+        <v>29.0278584852</v>
       </c>
       <c r="P69">
-        <v>78.3366735214</v>
+        <v>83.48322091480001</v>
       </c>
       <c r="Q69">
-        <v>231.4366735214</v>
+        <v>236.5832209148</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.123502402175337</v>
+        <v>0.1234524464393001</v>
       </c>
       <c r="T69">
         <v>1.793359040168593</v>
       </c>
       <c r="U69">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V69">
         <v>0.258</v>
       </c>
       <c r="W69">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6926,7 +6962,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.133692001482271</v>
+        <v>2.305400724556701</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6937,13 +6973,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.08154127530575191</v>
+        <v>0.07844702533379652</v>
       </c>
       <c r="C70">
-        <v>494.8204682740077</v>
+        <v>525.7922414423008</v>
       </c>
       <c r="D70">
-        <v>1648.848468274008</v>
+        <v>1679.820241442301</v>
       </c>
       <c r="E70">
         <v>1154.028</v>
@@ -6970,37 +7006,37 @@
         <v>198.7</v>
       </c>
       <c r="M70">
-        <v>94.5148932</v>
+        <v>87.47532240000001</v>
       </c>
       <c r="N70">
-        <v>104.1851068</v>
+        <v>111.2246776</v>
       </c>
       <c r="O70">
-        <v>26.8797575544</v>
+        <v>28.6959668208</v>
       </c>
       <c r="P70">
-        <v>77.30534924560001</v>
+        <v>82.5287107792</v>
       </c>
       <c r="Q70">
-        <v>230.4053492456</v>
+        <v>235.6287107792</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1256806603304747</v>
+        <v>0.1256293041681141</v>
       </c>
       <c r="T70">
         <v>1.843632890718572</v>
       </c>
       <c r="U70">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V70">
         <v>0.258</v>
       </c>
       <c r="W70">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7008,7 +7044,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.102314177931061</v>
+        <v>2.271497772724985</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7019,13 +7055,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0816109918936426</v>
+        <v>0.07847153134262402</v>
       </c>
       <c r="C71">
-        <v>477.1603496984494</v>
+        <v>508.5697523751196</v>
       </c>
       <c r="D71">
-        <v>1648.159349698449</v>
+        <v>1679.56875237512</v>
       </c>
       <c r="E71">
         <v>1170.999</v>
@@ -7052,37 +7088,37 @@
         <v>198.7</v>
       </c>
       <c r="M71">
-        <v>95.9048181</v>
+        <v>88.7617242</v>
       </c>
       <c r="N71">
-        <v>102.7951819</v>
+        <v>109.9382758</v>
       </c>
       <c r="O71">
-        <v>26.5211569302</v>
+        <v>28.36407515640001</v>
       </c>
       <c r="P71">
-        <v>76.27402496980001</v>
+        <v>81.57420064360001</v>
       </c>
       <c r="Q71">
-        <v>229.3740249698</v>
+        <v>234.6742006436</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1279994512698149</v>
+        <v>0.1279466043310452</v>
       </c>
       <c r="T71">
         <v>1.897150215497581</v>
       </c>
       <c r="U71">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V71">
         <v>0.258</v>
       </c>
       <c r="W71">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7090,7 +7126,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.07184585651177</v>
+        <v>2.238577515149261</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7101,13 +7137,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0816807084815333</v>
+        <v>0.07849603735145153</v>
       </c>
       <c r="C72">
-        <v>459.500806901721</v>
+        <v>491.3473385984748</v>
       </c>
       <c r="D72">
-        <v>1647.470806901721</v>
+        <v>1679.317338598475</v>
       </c>
       <c r="E72">
         <v>1187.97</v>
@@ -7134,37 +7170,37 @@
         <v>198.7</v>
       </c>
       <c r="M72">
-        <v>97.294743</v>
+        <v>90.04812600000001</v>
       </c>
       <c r="N72">
-        <v>101.405257</v>
+        <v>108.651874</v>
       </c>
       <c r="O72">
-        <v>26.16255630600001</v>
+        <v>28.032183492</v>
       </c>
       <c r="P72">
-        <v>75.24270069400001</v>
+        <v>80.61969050800001</v>
       </c>
       <c r="Q72">
-        <v>228.342700694</v>
+        <v>233.719690508</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1304728282717777</v>
+        <v>0.1304183911715051</v>
       </c>
       <c r="T72">
         <v>1.954235361928524</v>
       </c>
       <c r="U72">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V72">
         <v>0.258</v>
       </c>
       <c r="W72">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7172,7 +7208,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.042248058561602</v>
+        <v>2.206597836361414</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7183,13 +7219,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.08175042506942401</v>
+        <v>0.07852054336027903</v>
       </c>
       <c r="C73">
-        <v>441.8418391625046</v>
+        <v>474.1250000785612</v>
       </c>
       <c r="D73">
-        <v>1646.782839162504</v>
+        <v>1679.066000078561</v>
       </c>
       <c r="E73">
         <v>1204.941</v>
@@ -7216,37 +7252,37 @@
         <v>198.7</v>
       </c>
       <c r="M73">
-        <v>98.68466789999998</v>
+        <v>91.33452779999999</v>
       </c>
       <c r="N73">
-        <v>100.0153321</v>
+        <v>107.3654722</v>
       </c>
       <c r="O73">
-        <v>25.80395568180001</v>
+        <v>27.70029182760001</v>
       </c>
       <c r="P73">
-        <v>74.21137641820003</v>
+        <v>79.66518037240002</v>
       </c>
       <c r="Q73">
-        <v>227.3113764182</v>
+        <v>232.7651803724</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1331167829980139</v>
+        <v>0.1330606460699277</v>
       </c>
       <c r="T73">
         <v>2.015257415009877</v>
       </c>
       <c r="U73">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V73">
         <v>0.258</v>
       </c>
       <c r="W73">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7254,7 +7290,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.013484001398763</v>
+        <v>2.175518993595761</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7265,13 +7301,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.09052825365731472</v>
+        <v>0.07854504936910653</v>
       </c>
       <c r="C74">
-        <v>342.6118252275926</v>
+        <v>456.9027367815929</v>
       </c>
       <c r="D74">
-        <v>1564.523825227592</v>
+        <v>1678.814736781593</v>
       </c>
       <c r="E74">
         <v>1221.912</v>
@@ -7298,45 +7334,45 @@
         <v>198.7</v>
       </c>
       <c r="M74">
-        <v>119.9917584</v>
+        <v>92.6209296</v>
       </c>
       <c r="N74">
-        <v>78.70824160000002</v>
+        <v>106.0790704</v>
       </c>
       <c r="O74">
-        <v>20.30672633280001</v>
+        <v>27.36840016320001</v>
       </c>
       <c r="P74">
-        <v>58.40151526720001</v>
+        <v>78.71067023680001</v>
       </c>
       <c r="Q74">
-        <v>211.5015152672</v>
+        <v>231.8106702368</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1359495916332668</v>
+        <v>0.1358916334610947</v>
       </c>
       <c r="T74">
         <v>2.08063818616847</v>
       </c>
       <c r="U74">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V74">
         <v>0.258</v>
       </c>
       <c r="W74">
-        <v>0.07286440000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.655947063777674</v>
+        <v>2.145303452018042</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7347,13 +7383,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.09071891624520544</v>
+        <v>0.07856955537793403</v>
       </c>
       <c r="C75">
-        <v>323.9451729956613</v>
+        <v>439.6805486738051</v>
       </c>
       <c r="D75">
-        <v>1562.828172995661</v>
+        <v>1678.563548673805</v>
       </c>
       <c r="E75">
         <v>1238.883</v>
@@ -7380,45 +7416,45 @@
         <v>198.7</v>
       </c>
       <c r="M75">
-        <v>121.6583106</v>
+        <v>93.90733139999999</v>
       </c>
       <c r="N75">
-        <v>77.04168940000002</v>
+        <v>104.7926686</v>
       </c>
       <c r="O75">
-        <v>19.87675586520001</v>
+        <v>27.03650849880001</v>
       </c>
       <c r="P75">
-        <v>57.16493353480001</v>
+        <v>77.75616010120002</v>
       </c>
       <c r="Q75">
-        <v>210.2649335348</v>
+        <v>230.8561601012</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1389922379452053</v>
+        <v>0.1389323236219779</v>
       </c>
       <c r="T75">
         <v>2.150861977412884</v>
       </c>
       <c r="U75">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V75">
         <v>0.258</v>
       </c>
       <c r="W75">
-        <v>0.07286440000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.633262857424555</v>
+        <v>2.115915733497247</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7429,13 +7465,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.09090957883309614</v>
+        <v>0.07859406138676153</v>
       </c>
       <c r="C76">
-        <v>305.2821923264114</v>
+        <v>422.4584357214528</v>
       </c>
       <c r="D76">
-        <v>1561.136192326411</v>
+        <v>1678.312435721453</v>
       </c>
       <c r="E76">
         <v>1255.854</v>
@@ -7462,45 +7498,45 @@
         <v>198.7</v>
       </c>
       <c r="M76">
-        <v>123.3248628</v>
+        <v>95.1937332</v>
       </c>
       <c r="N76">
-        <v>75.37513720000003</v>
+        <v>103.5062668</v>
       </c>
       <c r="O76">
-        <v>19.44678539760001</v>
+        <v>26.70461683440001</v>
       </c>
       <c r="P76">
-        <v>55.92835180240002</v>
+        <v>76.80164996560001</v>
       </c>
       <c r="Q76">
-        <v>209.0283518024</v>
+        <v>229.9016499656</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1422689339734467</v>
+        <v>0.1422069130260059</v>
       </c>
       <c r="T76">
         <v>2.226487598753023</v>
       </c>
       <c r="U76">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V76">
         <v>0.258</v>
       </c>
       <c r="W76">
-        <v>0.07286440000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.611191737729629</v>
+        <v>2.087322277639176</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7511,13 +7547,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.09110024142098685</v>
+        <v>0.07861856739558903</v>
       </c>
       <c r="C77">
-        <v>286.6228713077937</v>
+        <v>405.2363978908115</v>
       </c>
       <c r="D77">
-        <v>1559.447871307794</v>
+        <v>1678.061397890811</v>
       </c>
       <c r="E77">
         <v>1272.825</v>
@@ -7544,45 +7580,45 @@
         <v>198.7</v>
       </c>
       <c r="M77">
-        <v>124.991415</v>
+        <v>96.48013499999999</v>
       </c>
       <c r="N77">
-        <v>73.70858500000003</v>
+        <v>102.219865</v>
       </c>
       <c r="O77">
-        <v>19.01681493000001</v>
+        <v>26.37272517000001</v>
       </c>
       <c r="P77">
-        <v>54.69177007000002</v>
+        <v>75.84713983000002</v>
       </c>
       <c r="Q77">
-        <v>207.79177007</v>
+        <v>228.94713983</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1458077656839473</v>
+        <v>0.1457434695823561</v>
       </c>
       <c r="T77">
         <v>2.308163269800373</v>
       </c>
       <c r="U77">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V77">
         <v>0.258</v>
       </c>
       <c r="W77">
-        <v>0.07286440000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.589709181226567</v>
+        <v>2.05949131393732</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7593,13 +7629,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.09129090400887756</v>
+        <v>0.07864307340441654</v>
       </c>
       <c r="C78">
-        <v>267.9671980792352</v>
+        <v>388.0144351481763</v>
       </c>
       <c r="D78">
-        <v>1557.763198079235</v>
+        <v>1677.810435148176</v>
       </c>
       <c r="E78">
         <v>1289.796</v>
@@ -7626,45 +7662,45 @@
         <v>198.7</v>
       </c>
       <c r="M78">
-        <v>126.6579672</v>
+        <v>97.76653680000001</v>
       </c>
       <c r="N78">
-        <v>72.0420328</v>
+        <v>100.9334632</v>
       </c>
       <c r="O78">
-        <v>18.5868444624</v>
+        <v>26.0408335056</v>
       </c>
       <c r="P78">
-        <v>53.4551883376</v>
+        <v>74.8926296944</v>
       </c>
       <c r="Q78">
-        <v>206.5551883376</v>
+        <v>227.9926296944</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1496415000369898</v>
+        <v>0.1495747391850689</v>
       </c>
       <c r="T78">
         <v>2.396645246768335</v>
       </c>
       <c r="U78">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V78">
         <v>0.258</v>
       </c>
       <c r="W78">
-        <v>0.07286440000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.568791955157796</v>
+        <v>2.032392744017092</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7675,13 +7711,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.09148156659676826</v>
+        <v>0.07866757941324404</v>
       </c>
       <c r="C79">
-        <v>249.3151608313588</v>
+        <v>370.7925474598635</v>
       </c>
       <c r="D79">
-        <v>1556.082160831359</v>
+        <v>1677.559547459864</v>
       </c>
       <c r="E79">
         <v>1306.767</v>
@@ -7708,45 +7744,45 @@
         <v>198.7</v>
       </c>
       <c r="M79">
-        <v>128.3245194</v>
+        <v>99.05293860000002</v>
       </c>
       <c r="N79">
-        <v>70.3754806</v>
+        <v>99.6470614</v>
       </c>
       <c r="O79">
-        <v>18.1568739948</v>
+        <v>25.7089418412</v>
       </c>
       <c r="P79">
-        <v>52.2186066052</v>
+        <v>73.9381195588</v>
       </c>
       <c r="Q79">
-        <v>205.3186066052</v>
+        <v>227.0381195588</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1538086025946445</v>
+        <v>0.1537391626662784</v>
       </c>
       <c r="T79">
         <v>2.492821308690033</v>
       </c>
       <c r="U79">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V79">
         <v>0.258</v>
       </c>
       <c r="W79">
-        <v>0.07286440000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.54841803366224</v>
+        <v>2.005998033055831</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7757,13 +7793,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.09167222918465896</v>
+        <v>0.08691047742207153</v>
       </c>
       <c r="C80">
-        <v>230.6667478057084</v>
+        <v>273.4856708108143</v>
       </c>
       <c r="D80">
-        <v>1554.404747805708</v>
+        <v>1597.223670810814</v>
       </c>
       <c r="E80">
         <v>1323.738</v>
@@ -7790,37 +7826,37 @@
         <v>198.7</v>
       </c>
       <c r="M80">
-        <v>129.9910716</v>
+        <v>119.13642</v>
       </c>
       <c r="N80">
-        <v>68.70892839999999</v>
+        <v>79.56358000000002</v>
       </c>
       <c r="O80">
-        <v>17.7269035272</v>
+        <v>20.52740364000001</v>
       </c>
       <c r="P80">
-        <v>50.9820248728</v>
+        <v>59.03617636000001</v>
       </c>
       <c r="Q80">
-        <v>204.0820248728</v>
+        <v>212.13617636</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1583545326575407</v>
+        <v>0.1582821701003252</v>
       </c>
       <c r="T80">
         <v>2.597740648968249</v>
       </c>
       <c r="U80">
-        <v>0.09820000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V80">
         <v>0.258</v>
       </c>
       <c r="W80">
-        <v>0.07286440000000001</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7828,7 +7864,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.52856652041016</v>
+        <v>1.667835914491975</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7839,13 +7875,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.09186289177254967</v>
+        <v>0.08704034743089903</v>
       </c>
       <c r="C81">
-        <v>212.0219472944736</v>
+        <v>255.3104705383146</v>
       </c>
       <c r="D81">
-        <v>1552.730947294474</v>
+        <v>1596.019470538315</v>
       </c>
       <c r="E81">
         <v>1340.709</v>
@@ -7872,37 +7908,37 @@
         <v>198.7</v>
       </c>
       <c r="M81">
-        <v>131.6576238</v>
+        <v>120.66381</v>
       </c>
       <c r="N81">
-        <v>67.04237620000001</v>
+        <v>78.03619000000002</v>
       </c>
       <c r="O81">
-        <v>17.2969330596</v>
+        <v>20.13333702000001</v>
       </c>
       <c r="P81">
-        <v>49.74544314040001</v>
+        <v>57.90285298000001</v>
       </c>
       <c r="Q81">
-        <v>202.8454431404</v>
+        <v>211.00285298</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1633334084407127</v>
+        <v>0.1632578449090431</v>
       </c>
       <c r="T81">
         <v>2.712652307368201</v>
       </c>
       <c r="U81">
-        <v>0.09820000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V81">
         <v>0.258</v>
       </c>
       <c r="W81">
-        <v>0.07286440000000001</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7910,7 +7946,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.509217577113829</v>
+        <v>1.646724067473089</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7921,13 +7957,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1351094154983285</v>
+        <v>0.08717021743972653</v>
       </c>
       <c r="C82">
-        <v>-109.7495570949254</v>
+        <v>237.1370846714851</v>
       </c>
       <c r="D82">
-        <v>1247.930442905075</v>
+        <v>1594.817084671485</v>
       </c>
       <c r="E82">
         <v>1357.68</v>
@@ -7954,45 +7990,45 @@
         <v>198.7</v>
       </c>
       <c r="M82">
-        <v>222.116448</v>
+        <v>122.1912</v>
       </c>
       <c r="N82">
-        <v>-23.41644799999997</v>
+        <v>76.50880000000002</v>
       </c>
       <c r="O82">
-        <v>-6.041443583999993</v>
+        <v>19.73927040000001</v>
       </c>
       <c r="P82">
-        <v>-17.37500441599998</v>
+        <v>56.76952960000001</v>
       </c>
       <c r="Q82">
-        <v>135.724995584</v>
+        <v>209.8695296</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1721829622362067</v>
+        <v>0.1687310871986327</v>
       </c>
       <c r="T82">
-        <v>2.916898596495731</v>
+        <v>2.839055131608146</v>
       </c>
       <c r="U82">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V82">
-        <v>0.2308005573725004</v>
+        <v>0.258</v>
       </c>
       <c r="W82">
-        <v>0.1258410288138589</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.8945758037693815</v>
+        <v>1.626140016629676</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8003,13 +8039,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1362874154983285</v>
+        <v>0.08730008744855404</v>
       </c>
       <c r="C83">
-        <v>-133.3578034012585</v>
+        <v>218.9655091126808</v>
       </c>
       <c r="D83">
-        <v>1241.293196598742</v>
+        <v>1593.616509112681</v>
       </c>
       <c r="E83">
         <v>1374.651</v>
@@ -8036,45 +8072,45 @@
         <v>198.7</v>
       </c>
       <c r="M83">
-        <v>224.8929036</v>
+        <v>123.71859</v>
       </c>
       <c r="N83">
-        <v>-26.19290359999999</v>
+        <v>74.98141000000001</v>
       </c>
       <c r="O83">
-        <v>-6.757769128799999</v>
+        <v>19.34520378</v>
       </c>
       <c r="P83">
-        <v>-19.43513447119999</v>
+        <v>55.63620622000001</v>
       </c>
       <c r="Q83">
-        <v>133.6648655288</v>
+        <v>208.73620622</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.178834697090744</v>
+        <v>0.1747804602555476</v>
       </c>
       <c r="T83">
-        <v>3.070419575258665</v>
+        <v>2.978763516294403</v>
       </c>
       <c r="U83">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V83">
-        <v>0.227951167775309</v>
+        <v>0.258</v>
       </c>
       <c r="W83">
-        <v>0.1263071889519594</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.8835316580438335</v>
+        <v>1.606064213955235</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8085,13 +8121,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1374654154983285</v>
+        <v>0.08742995745738154</v>
       </c>
       <c r="C84">
-        <v>-156.8958214705503</v>
+        <v>200.7957397765879</v>
       </c>
       <c r="D84">
-        <v>1234.72617852945</v>
+        <v>1592.417739776588</v>
       </c>
       <c r="E84">
         <v>1391.622</v>
@@ -8118,45 +8154,45 @@
         <v>198.7</v>
       </c>
       <c r="M84">
-        <v>227.6693592</v>
+        <v>125.24598</v>
       </c>
       <c r="N84">
-        <v>-28.96935919999999</v>
+        <v>73.45402000000001</v>
       </c>
       <c r="O84">
-        <v>-7.474094673599996</v>
+        <v>18.95113716000001</v>
       </c>
       <c r="P84">
-        <v>-21.49526452639999</v>
+        <v>54.50288284000001</v>
       </c>
       <c r="Q84">
-        <v>131.6047354736</v>
+        <v>207.60288284</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1862255135957853</v>
+        <v>0.181501985874342</v>
       </c>
       <c r="T84">
-        <v>3.240998440550813</v>
+        <v>3.133995054834688</v>
       </c>
       <c r="U84">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V84">
-        <v>0.2251712754853663</v>
+        <v>0.258</v>
       </c>
       <c r="W84">
-        <v>0.1267619793305941</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.8727568817262258</v>
+        <v>1.586478065004562</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8167,13 +8203,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1386434154983285</v>
+        <v>0.08755982746620905</v>
       </c>
       <c r="C85">
-        <v>-180.3647200570422</v>
+        <v>182.6277725901737</v>
       </c>
       <c r="D85">
-        <v>1228.228279942958</v>
+        <v>1591.220772590174</v>
       </c>
       <c r="E85">
         <v>1408.593</v>
@@ -8200,45 +8236,45 @@
         <v>198.7</v>
       </c>
       <c r="M85">
-        <v>230.4458148</v>
+        <v>126.77337</v>
       </c>
       <c r="N85">
-        <v>-31.74581479999998</v>
+        <v>71.92663000000002</v>
       </c>
       <c r="O85">
-        <v>-8.190420218399995</v>
+        <v>18.55707054000001</v>
       </c>
       <c r="P85">
-        <v>-23.55539458159998</v>
+        <v>53.36955946000001</v>
       </c>
       <c r="Q85">
-        <v>129.5446054184</v>
+        <v>206.46955946</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1944858379249492</v>
+        <v>0.1890142792129945</v>
       </c>
       <c r="T85">
-        <v>3.431645407642038</v>
+        <v>3.307489127320888</v>
       </c>
       <c r="U85">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V85">
-        <v>0.2224583685518076</v>
+        <v>0.258</v>
       </c>
       <c r="W85">
-        <v>0.1272058109049243</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.8622417385728978</v>
+        <v>1.56736387145029</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8249,13 +8285,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1398214154983285</v>
+        <v>0.08768969747503655</v>
       </c>
       <c r="C86">
-        <v>-203.7655846973369</v>
+        <v>164.4616034926444</v>
       </c>
       <c r="D86">
-        <v>1221.798415302663</v>
+        <v>1590.025603492644</v>
       </c>
       <c r="E86">
         <v>1425.564</v>
@@ -8282,45 +8318,45 @@
         <v>198.7</v>
       </c>
       <c r="M86">
-        <v>233.2222704</v>
+        <v>128.30076</v>
       </c>
       <c r="N86">
-        <v>-34.52227039999994</v>
+        <v>70.39924000000005</v>
       </c>
       <c r="O86">
-        <v>-8.906745763199984</v>
+        <v>18.16300392000001</v>
       </c>
       <c r="P86">
-        <v>-25.61552463679995</v>
+        <v>52.23623608000004</v>
       </c>
       <c r="Q86">
-        <v>127.4844753632</v>
+        <v>205.33623608</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2037787027952584</v>
+        <v>0.1974656092189784</v>
       </c>
       <c r="T86">
-        <v>3.646123245619662</v>
+        <v>3.502669958867862</v>
       </c>
       <c r="U86">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V86">
-        <v>0.2198100546404766</v>
+        <v>0.258</v>
       </c>
       <c r="W86">
-        <v>0.127639075060818</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.8519769559708397</v>
+        <v>1.548704777742548</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8331,13 +8367,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1409994154983285</v>
+        <v>0.08781956748386405</v>
       </c>
       <c r="C87">
-        <v>-227.0994783149665</v>
+        <v>146.2972284353957</v>
       </c>
       <c r="D87">
-        <v>1215.435521685033</v>
+        <v>1588.832228435396</v>
       </c>
       <c r="E87">
         <v>1442.535</v>
@@ -8364,45 +8400,45 @@
         <v>198.7</v>
       </c>
       <c r="M87">
-        <v>235.998726</v>
+        <v>129.82815</v>
       </c>
       <c r="N87">
-        <v>-37.29872599999996</v>
+        <v>68.87185000000002</v>
       </c>
       <c r="O87">
-        <v>-9.623071307999989</v>
+        <v>17.76893730000001</v>
       </c>
       <c r="P87">
-        <v>-27.67565469199997</v>
+        <v>51.10291270000002</v>
       </c>
       <c r="Q87">
-        <v>125.424345308</v>
+        <v>204.2029127</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2143106163149423</v>
+        <v>0.2070437832257603</v>
       </c>
       <c r="T87">
-        <v>3.889198128660974</v>
+        <v>3.723874901287768</v>
       </c>
       <c r="U87">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V87">
-        <v>0.2172240539976475</v>
+        <v>0.258</v>
       </c>
       <c r="W87">
-        <v>0.1280621447659849</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8419536976653003</v>
+        <v>1.530484721533812</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8413,13 +8449,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1421774154983285</v>
+        <v>0.08794943749269155</v>
       </c>
       <c r="C88">
-        <v>-250.3674418061619</v>
+        <v>128.1346433819699</v>
       </c>
       <c r="D88">
-        <v>1209.138558193838</v>
+        <v>1587.64064338197</v>
       </c>
       <c r="E88">
         <v>1459.506</v>
@@ -8446,45 +8482,45 @@
         <v>198.7</v>
       </c>
       <c r="M88">
-        <v>238.7751816</v>
+        <v>131.35554</v>
       </c>
       <c r="N88">
-        <v>-40.07518159999995</v>
+        <v>67.34446000000003</v>
       </c>
       <c r="O88">
-        <v>-10.33939685279999</v>
+        <v>17.37487068000001</v>
       </c>
       <c r="P88">
-        <v>-29.73578474719996</v>
+        <v>49.96958932000002</v>
       </c>
       <c r="Q88">
-        <v>123.3642152528</v>
+        <v>203.06958932</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2263470889088667</v>
+        <v>0.2179902678049397</v>
       </c>
       <c r="T88">
-        <v>4.1669979949939</v>
+        <v>3.97668054976766</v>
       </c>
       <c r="U88">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V88">
-        <v>0.2146981929046516</v>
+        <v>0.258</v>
       </c>
       <c r="W88">
-        <v>0.128475375640799</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.8321635383901224</v>
+        <v>1.512688387562489</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8495,13 +8531,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1433554154983285</v>
+        <v>0.1280685285335503</v>
       </c>
       <c r="C89">
-        <v>-273.5704946075125</v>
+        <v>-187.4732181227787</v>
       </c>
       <c r="D89">
-        <v>1202.906505392487</v>
+        <v>1289.003781877221</v>
       </c>
       <c r="E89">
         <v>1476.477</v>
@@ -8528,37 +8564,37 @@
         <v>198.7</v>
       </c>
       <c r="M89">
-        <v>241.5516372</v>
+        <v>216.7468236</v>
       </c>
       <c r="N89">
-        <v>-42.85163719999994</v>
+        <v>-18.04682359999998</v>
       </c>
       <c r="O89">
-        <v>-11.05572239759999</v>
+        <v>-4.656080488799995</v>
       </c>
       <c r="P89">
-        <v>-31.79591480239996</v>
+        <v>-13.39074311119999</v>
       </c>
       <c r="Q89">
-        <v>121.3040851976</v>
+        <v>139.7092568888</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2402353265172411</v>
+        <v>0.2350746575574089</v>
       </c>
       <c r="T89">
-        <v>4.487536302301123</v>
+        <v>4.371239204559097</v>
       </c>
       <c r="U89">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2122303975839085</v>
+        <v>0.2365183449913312</v>
       </c>
       <c r="W89">
-        <v>0.1288791069552726</v>
+        <v>0.1120791069552726</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8566,7 +8602,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8225984402477072</v>
+        <v>0.9167377712842294</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8577,13 +8613,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1445334154983285</v>
+        <v>0.1290785285335503</v>
       </c>
       <c r="C90">
-        <v>-296.7096352461572</v>
+        <v>-210.5194653817982</v>
       </c>
       <c r="D90">
-        <v>1196.738364753843</v>
+        <v>1282.928534618202</v>
       </c>
       <c r="E90">
         <v>1493.448</v>
@@ -8610,37 +8646,37 @@
         <v>198.7</v>
       </c>
       <c r="M90">
-        <v>244.3280928</v>
+        <v>219.2381664</v>
       </c>
       <c r="N90">
-        <v>-45.62809279999996</v>
+        <v>-20.53816639999999</v>
       </c>
       <c r="O90">
-        <v>-11.77204794239999</v>
+        <v>-5.298846931199999</v>
       </c>
       <c r="P90">
-        <v>-33.85604485759997</v>
+        <v>-15.23931946879999</v>
       </c>
       <c r="Q90">
-        <v>119.2439551424</v>
+        <v>137.8606805312</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2564382703936778</v>
+        <v>0.250847545687193</v>
       </c>
       <c r="T90">
-        <v>4.861497660826218</v>
+        <v>4.735509138272356</v>
       </c>
       <c r="U90">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.209818688520455</v>
+        <v>0.2338306365255206</v>
       </c>
       <c r="W90">
-        <v>0.1292736625580536</v>
+        <v>0.1124736625580536</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8648,7 +8684,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8132507306994378</v>
+        <v>0.9063202966105449</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8659,13 +8695,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1457114154983285</v>
+        <v>0.1300885285335503</v>
       </c>
       <c r="C91">
-        <v>-319.785841873138</v>
+        <v>-233.5087143751862</v>
       </c>
       <c r="D91">
-        <v>1190.633158126862</v>
+        <v>1276.910285624814</v>
       </c>
       <c r="E91">
         <v>1510.419</v>
@@ -8692,37 +8728,37 @@
         <v>198.7</v>
       </c>
       <c r="M91">
-        <v>247.1045484</v>
+        <v>221.7295092</v>
       </c>
       <c r="N91">
-        <v>-48.40454839999995</v>
+        <v>-23.02950919999998</v>
       </c>
       <c r="O91">
-        <v>-12.48837348719999</v>
+        <v>-5.941613373599995</v>
       </c>
       <c r="P91">
-        <v>-35.91617491279997</v>
+        <v>-17.08789582639998</v>
       </c>
       <c r="Q91">
-        <v>117.1838250872</v>
+        <v>136.0121041736</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2755872040658304</v>
+        <v>0.269488231658756</v>
       </c>
       <c r="T91">
-        <v>5.303451993628602</v>
+        <v>5.166009969024389</v>
       </c>
       <c r="U91">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2074611751662925</v>
+        <v>0.2312033260027619</v>
       </c>
       <c r="W91">
-        <v>0.1296593517427946</v>
+        <v>0.1128593517427946</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8730,7 +8766,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8041130820398935</v>
+        <v>0.8961369224913254</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8741,13 +8777,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.195253986605082</v>
+        <v>0.1310985285335503</v>
       </c>
       <c r="C92">
-        <v>-547.0842835337822</v>
+        <v>-256.4417634984059</v>
       </c>
       <c r="D92">
-        <v>980.3057164662176</v>
+        <v>1270.948236501594</v>
       </c>
       <c r="E92">
         <v>1527.39</v>
@@ -8774,45 +8810,45 @@
         <v>198.7</v>
       </c>
       <c r="M92">
-        <v>329.610762</v>
+        <v>224.220852</v>
       </c>
       <c r="N92">
-        <v>-130.910762</v>
+        <v>-25.52085199999999</v>
       </c>
       <c r="O92">
-        <v>-33.774976596</v>
+        <v>-6.584379815999998</v>
       </c>
       <c r="P92">
-        <v>-97.135785404</v>
+        <v>-18.93647218399999</v>
       </c>
       <c r="Q92">
-        <v>55.96421459599999</v>
+        <v>134.163527816</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3124116355399484</v>
+        <v>0.2918570548246316</v>
       </c>
       <c r="T92">
-        <v>6.153353994523749</v>
+        <v>5.682610965926828</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1555307226285288</v>
+        <v>0.2286344001582868</v>
       </c>
       <c r="W92">
-        <v>0.1822364700567635</v>
+        <v>0.1132364700567635</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.6028322582501113</v>
+        <v>0.886179845574755</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8823,13 +8859,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.196953986605082</v>
+        <v>0.1321085285335503</v>
       </c>
       <c r="C93">
-        <v>-569.9617168069099</v>
+        <v>-279.319396304998</v>
       </c>
       <c r="D93">
-        <v>974.39928319309</v>
+        <v>1265.041603695002</v>
       </c>
       <c r="E93">
         <v>1544.361</v>
@@ -8856,45 +8892,45 @@
         <v>198.7</v>
       </c>
       <c r="M93">
-        <v>333.2731038</v>
+        <v>226.7121948</v>
       </c>
       <c r="N93">
-        <v>-134.5731038</v>
+        <v>-28.01219479999997</v>
       </c>
       <c r="O93">
-        <v>-34.7198607804</v>
+        <v>-7.227146258399993</v>
       </c>
       <c r="P93">
-        <v>-99.85324301959999</v>
+        <v>-20.78504854159998</v>
       </c>
       <c r="Q93">
-        <v>53.24675698040001</v>
+        <v>132.3149514584</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3420351505999427</v>
+        <v>0.3191967275829241</v>
       </c>
       <c r="T93">
-        <v>6.837059993915276</v>
+        <v>6.314012184363142</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.153821593808435</v>
+        <v>0.2261219342224815</v>
       </c>
       <c r="W93">
-        <v>0.1826053000561397</v>
+        <v>0.1136053000561397</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.5962077279396707</v>
+        <v>0.876441605513494</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8905,13 +8941,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.198653986605082</v>
+        <v>0.1331185285335503</v>
       </c>
       <c r="C94">
-        <v>-592.7684027179831</v>
+        <v>-302.1423818498681</v>
       </c>
       <c r="D94">
-        <v>968.5635972820168</v>
+        <v>1259.189618150132</v>
       </c>
       <c r="E94">
         <v>1561.332</v>
@@ -8938,45 +8974,45 @@
         <v>198.7</v>
       </c>
       <c r="M94">
-        <v>336.9354456</v>
+        <v>229.2035376</v>
       </c>
       <c r="N94">
-        <v>-138.2354456</v>
+        <v>-30.50353759999999</v>
       </c>
       <c r="O94">
-        <v>-35.66474496479999</v>
+        <v>-7.869912700799997</v>
       </c>
       <c r="P94">
-        <v>-102.5707006352</v>
+        <v>-22.63362489919999</v>
       </c>
       <c r="Q94">
-        <v>50.52929936480002</v>
+        <v>130.4663751008</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3790645444249356</v>
+        <v>0.3533713185307897</v>
       </c>
       <c r="T94">
-        <v>7.691692493154688</v>
+        <v>7.103263707408537</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1521496199626912</v>
+        <v>0.2236640871113675</v>
       </c>
       <c r="W94">
-        <v>0.1829661120120513</v>
+        <v>0.1139661120120513</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.5897272091577177</v>
+        <v>0.86691506632313</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -8987,13 +9023,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.200353986605082</v>
+        <v>0.1341285285335503</v>
       </c>
       <c r="C95">
-        <v>-615.5056048193049</v>
+        <v>-324.9114750230917</v>
       </c>
       <c r="D95">
-        <v>962.7973951806952</v>
+        <v>1253.391524976908</v>
       </c>
       <c r="E95">
         <v>1578.303</v>
@@ -9020,45 +9056,45 @@
         <v>198.7</v>
       </c>
       <c r="M95">
-        <v>340.5977874000001</v>
+        <v>231.6948804</v>
       </c>
       <c r="N95">
-        <v>-141.8977874000001</v>
+        <v>-32.99488040000003</v>
       </c>
       <c r="O95">
-        <v>-36.60962914920002</v>
+        <v>-8.512679143200007</v>
       </c>
       <c r="P95">
-        <v>-105.2881582508</v>
+        <v>-24.48220125680002</v>
       </c>
       <c r="Q95">
-        <v>47.81184174919996</v>
+        <v>128.6177987432</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4266737650570693</v>
+        <v>0.3973100783209025</v>
       </c>
       <c r="T95">
-        <v>8.790505706462502</v>
+        <v>8.118015665609757</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1505136025437375</v>
+        <v>0.2212590969273743</v>
       </c>
       <c r="W95">
-        <v>0.1833191645710615</v>
+        <v>0.1143191645710615</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.5833860563710754</v>
+        <v>0.8575933989433112</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9069,13 +9105,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.202053986605082</v>
+        <v>0.1351385285335503</v>
       </c>
       <c r="C96">
-        <v>-638.1745567517527</v>
+        <v>-347.6274168745363</v>
       </c>
       <c r="D96">
-        <v>957.0994432482474</v>
+        <v>1247.646583125464</v>
       </c>
       <c r="E96">
         <v>1595.274</v>
@@ -9102,45 +9138,45 @@
         <v>198.7</v>
       </c>
       <c r="M96">
-        <v>344.2601292000001</v>
+        <v>234.1862232</v>
       </c>
       <c r="N96">
-        <v>-145.5601292</v>
+        <v>-35.48622320000001</v>
       </c>
       <c r="O96">
-        <v>-37.55451333360001</v>
+        <v>-9.155445585600003</v>
       </c>
       <c r="P96">
-        <v>-108.0056158664</v>
+        <v>-26.33077761440001</v>
       </c>
       <c r="Q96">
-        <v>45.09438413359996</v>
+        <v>126.7692223856</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4901527258999143</v>
+        <v>0.4558950913743864</v>
       </c>
       <c r="T96">
-        <v>10.25558999087292</v>
+        <v>9.47101827654472</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1489123940060381</v>
+        <v>0.2189052767472959</v>
       </c>
       <c r="W96">
-        <v>0.183664705373497</v>
+        <v>0.114664705373497</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.57717982172883</v>
+        <v>0.8484700649119994</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9151,13 +9187,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.203753986605082</v>
+        <v>0.1361485285335503</v>
       </c>
       <c r="C97">
-        <v>-660.776463124671</v>
+        <v>-370.2909349296001</v>
       </c>
       <c r="D97">
-        <v>951.4685368753292</v>
+        <v>1241.9540650704</v>
       </c>
       <c r="E97">
         <v>1612.245</v>
@@ -9184,45 +9220,45 @@
         <v>198.7</v>
       </c>
       <c r="M97">
-        <v>347.922471</v>
+        <v>236.677566</v>
       </c>
       <c r="N97">
-        <v>-149.222471</v>
+        <v>-37.97756600000002</v>
       </c>
       <c r="O97">
-        <v>-38.499397518</v>
+        <v>-9.798212028000007</v>
       </c>
       <c r="P97">
-        <v>-110.723073482</v>
+        <v>-28.17935397200002</v>
       </c>
       <c r="Q97">
-        <v>42.37692651799998</v>
+        <v>124.920646028</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5790232710798974</v>
+        <v>0.5379141096492639</v>
       </c>
       <c r="T97">
-        <v>12.30670798904751</v>
+        <v>11.36522193185367</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1473448951217641</v>
+        <v>0.2166010106762717</v>
       </c>
       <c r="W97">
-        <v>0.1840029716327233</v>
+        <v>0.1150029716327233</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.5711042446580002</v>
+        <v>0.8395388010708205</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9233,13 +9269,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.205453986605082</v>
+        <v>0.1371585285335503</v>
       </c>
       <c r="C98">
-        <v>-683.312500364881</v>
+        <v>-392.9027434963425</v>
       </c>
       <c r="D98">
-        <v>945.9034996351189</v>
+        <v>1236.313256503657</v>
       </c>
       <c r="E98">
         <v>1629.216</v>
@@ -9266,45 +9302,45 @@
         <v>198.7</v>
       </c>
       <c r="M98">
-        <v>351.5848128</v>
+        <v>239.1689088</v>
       </c>
       <c r="N98">
-        <v>-152.8848128</v>
+        <v>-40.46890879999998</v>
       </c>
       <c r="O98">
-        <v>-39.4442817024</v>
+        <v>-10.4409784704</v>
       </c>
       <c r="P98">
-        <v>-113.4405310976</v>
+        <v>-30.02793032959998</v>
       </c>
       <c r="Q98">
-        <v>39.65946890239999</v>
+        <v>123.0720696704</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.7123290888498702</v>
+        <v>0.6609426370615784</v>
       </c>
       <c r="T98">
-        <v>15.38338498630936</v>
+        <v>14.20652741481705</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1458100524642457</v>
+        <v>0.2143447501483939</v>
       </c>
       <c r="W98">
-        <v>0.1843341906782158</v>
+        <v>0.1153341906782158</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.5651552421094794</v>
+        <v>0.8307936052263329</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9315,13 +9351,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.207153986605082</v>
+        <v>0.1381685285335503</v>
       </c>
       <c r="C99">
-        <v>-705.7838175360725</v>
+        <v>-415.4635439642882</v>
       </c>
       <c r="D99">
-        <v>940.4031824639274</v>
+        <v>1230.723456035712</v>
       </c>
       <c r="E99">
         <v>1646.187</v>
@@ -9348,45 +9384,45 @@
         <v>198.7</v>
       </c>
       <c r="M99">
-        <v>355.2471546</v>
+        <v>241.6602516</v>
       </c>
       <c r="N99">
-        <v>-156.5471546</v>
+        <v>-42.96025159999999</v>
       </c>
       <c r="O99">
-        <v>-40.38916588679999</v>
+        <v>-11.0837449128</v>
       </c>
       <c r="P99">
-        <v>-116.1579887132</v>
+        <v>-31.87650668719999</v>
       </c>
       <c r="Q99">
-        <v>36.94201128680001</v>
+        <v>121.2234933128</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.934505451799827</v>
+        <v>0.8659901827487713</v>
       </c>
       <c r="T99">
-        <v>20.51117998174581</v>
+        <v>18.94203655308941</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1443068560470885</v>
+        <v>0.2121350104561424</v>
       </c>
       <c r="W99">
-        <v>0.1846585804650383</v>
+        <v>0.1156585804650383</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.5593288994073199</v>
+        <v>0.8222287226982263</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9397,13 +9433,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.208853986605082</v>
+        <v>0.1391785285335503</v>
       </c>
       <c r="C100">
-        <v>-728.1915371297704</v>
+        <v>-437.9740250951552</v>
       </c>
       <c r="D100">
-        <v>934.9664628702295</v>
+        <v>1225.183974904845</v>
       </c>
       <c r="E100">
         <v>1663.158</v>
@@ -9430,45 +9466,45 @@
         <v>198.7</v>
       </c>
       <c r="M100">
-        <v>358.9094964</v>
+        <v>244.1515944</v>
       </c>
       <c r="N100">
-        <v>-160.2094964</v>
+        <v>-45.4515944</v>
       </c>
       <c r="O100">
-        <v>-41.3340500712</v>
+        <v>-11.7265113552</v>
       </c>
       <c r="P100">
-        <v>-118.8754463288</v>
+        <v>-33.7250830448</v>
       </c>
       <c r="Q100">
-        <v>34.2245536712</v>
+        <v>119.3749169552</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.378858177699741</v>
+        <v>1.276085274123157</v>
       </c>
       <c r="T100">
-        <v>30.76676997261871</v>
+        <v>28.41305482963411</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1428343371078325</v>
+        <v>0.2099703674923042</v>
       </c>
       <c r="W100">
-        <v>0.1849763500521298</v>
+        <v>0.1159763500521298</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.5536214616582655</v>
+        <v>0.8138386336911015</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9479,13 +9515,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.210553986605082</v>
+        <v>0.1401885285335503</v>
       </c>
       <c r="C101">
-        <v>-750.5367558290224</v>
+        <v>-460.4348633057714</v>
       </c>
       <c r="D101">
-        <v>929.5922441709776</v>
+        <v>1219.694136694229</v>
       </c>
       <c r="E101">
         <v>1680.129</v>
@@ -9512,45 +9548,45 @@
         <v>198.7</v>
       </c>
       <c r="M101">
-        <v>362.5718382</v>
+        <v>246.6429372</v>
       </c>
       <c r="N101">
-        <v>-163.8718382</v>
+        <v>-47.94293719999999</v>
       </c>
       <c r="O101">
-        <v>-42.2789342556</v>
+        <v>-12.3692777976</v>
       </c>
       <c r="P101">
-        <v>-121.5929039444</v>
+        <v>-35.57365940239999</v>
       </c>
       <c r="Q101">
-        <v>31.50709605560002</v>
+        <v>117.5263405976</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.711916355399481</v>
+        <v>2.506370548246314</v>
       </c>
       <c r="T101">
-        <v>61.53353994523741</v>
+        <v>56.82610965926822</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V101">
-        <v>0.1413915660259353</v>
+        <v>0.2078494546893516</v>
       </c>
       <c r="W101">
-        <v>0.1852877000516032</v>
+        <v>0.1162877000516032</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.5480293256819195</v>
+        <v>0.8056180414315955</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_construction_supplies.xlsx
@@ -1257,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1394,22 +1394,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07678061673352639</v>
+        <v>0.07661591274235389</v>
       </c>
       <c r="C2">
-        <v>1697.1</v>
+        <v>1681.856216168839</v>
       </c>
       <c r="D2">
-        <v>1697.1</v>
+        <v>1698.827216168839</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>16.971</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>16.971</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1430,28 +1430,28 @@
         <v>198.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.8536412999999999</v>
       </c>
       <c r="N2">
-        <v>198.7</v>
+        <v>197.8463587</v>
       </c>
       <c r="O2">
-        <v>51.26460000000001</v>
+        <v>51.04436054460001</v>
       </c>
       <c r="P2">
-        <v>147.4354</v>
+        <v>146.8019981554</v>
       </c>
       <c r="Q2">
-        <v>300.5354</v>
+        <v>299.9019981554</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07678061673352639</v>
+        <v>0.07701281489126656</v>
       </c>
       <c r="T2">
-        <v>0.7154876843770529</v>
+        <v>0.7208502284357172</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>232.7675570523592</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1476,22 +1476,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07661591274235389</v>
+        <v>0.07645120875118139</v>
       </c>
       <c r="C3">
-        <v>1681.856216168839</v>
+        <v>1666.615951652984</v>
       </c>
       <c r="D3">
-        <v>1698.827216168839</v>
+        <v>1700.557951652984</v>
       </c>
       <c r="E3">
-        <v>16.971</v>
+        <v>33.942</v>
       </c>
       <c r="F3">
-        <v>16.971</v>
+        <v>33.942</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1512,28 +1512,28 @@
         <v>198.7</v>
       </c>
       <c r="M3">
-        <v>0.8536412999999999</v>
+        <v>1.7072826</v>
       </c>
       <c r="N3">
-        <v>197.8463587</v>
+        <v>196.9927174</v>
       </c>
       <c r="O3">
-        <v>51.04436054460001</v>
+        <v>50.82412108920001</v>
       </c>
       <c r="P3">
-        <v>146.8019981554</v>
+        <v>146.1685963108</v>
       </c>
       <c r="Q3">
-        <v>299.9019981554</v>
+        <v>299.2685963108</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07701281489126656</v>
+        <v>0.07724975178691978</v>
       </c>
       <c r="T3">
-        <v>0.7208502284357172</v>
+        <v>0.7263222121690482</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>232.7675570523592</v>
+        <v>116.3837785261796</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1558,22 +1558,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07645120875118139</v>
+        <v>0.07628650476000888</v>
       </c>
       <c r="C4">
-        <v>1666.615951652984</v>
+        <v>1651.379217219655</v>
       </c>
       <c r="D4">
-        <v>1700.557951652984</v>
+        <v>1702.292217219655</v>
       </c>
       <c r="E4">
-        <v>33.942</v>
+        <v>50.913</v>
       </c>
       <c r="F4">
-        <v>33.942</v>
+        <v>50.913</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1594,28 +1594,28 @@
         <v>198.7</v>
       </c>
       <c r="M4">
-        <v>1.7072826</v>
+        <v>2.5609239</v>
       </c>
       <c r="N4">
-        <v>196.9927174</v>
+        <v>196.1390761</v>
       </c>
       <c r="O4">
-        <v>50.82412108920001</v>
+        <v>50.60388163380001</v>
       </c>
       <c r="P4">
-        <v>146.1685963108</v>
+        <v>145.5351944662</v>
       </c>
       <c r="Q4">
-        <v>299.2685963108</v>
+        <v>298.6351944662</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07724975178691978</v>
+        <v>0.0774915739793906</v>
       </c>
       <c r="T4">
-        <v>0.7263222121690482</v>
+        <v>0.731907020309252</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>116.3837785261796</v>
+        <v>77.58918568411971</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1640,22 +1640,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07628650476000888</v>
+        <v>0.0761218007688364</v>
       </c>
       <c r="C5">
-        <v>1651.379217219655</v>
+        <v>1636.146023680041</v>
       </c>
       <c r="D5">
-        <v>1702.292217219655</v>
+        <v>1704.030023680041</v>
       </c>
       <c r="E5">
-        <v>50.913</v>
+        <v>67.884</v>
       </c>
       <c r="F5">
-        <v>50.913</v>
+        <v>67.884</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1676,28 +1676,28 @@
         <v>198.7</v>
       </c>
       <c r="M5">
-        <v>2.5609239</v>
+        <v>3.4145652</v>
       </c>
       <c r="N5">
-        <v>196.1390761</v>
+        <v>195.2854348</v>
       </c>
       <c r="O5">
-        <v>50.60388163380001</v>
+        <v>50.38364217840001</v>
       </c>
       <c r="P5">
-        <v>145.5351944662</v>
+        <v>144.9017926216</v>
       </c>
       <c r="Q5">
-        <v>298.6351944662</v>
+        <v>298.0017926216</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0774915739793906</v>
+        <v>0.07773843413420459</v>
       </c>
       <c r="T5">
-        <v>0.731907020309252</v>
+        <v>0.7376081786190435</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>77.58918568411971</v>
+        <v>58.19188926308978</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1722,22 +1722,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0761218007688364</v>
+        <v>0.07595709677766389</v>
       </c>
       <c r="C6">
-        <v>1636.146023680041</v>
+        <v>1620.91638188952</v>
       </c>
       <c r="D6">
-        <v>1704.030023680041</v>
+        <v>1705.77138188952</v>
       </c>
       <c r="E6">
-        <v>67.884</v>
+        <v>84.855</v>
       </c>
       <c r="F6">
-        <v>67.884</v>
+        <v>84.855</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1758,28 +1758,28 @@
         <v>198.7</v>
       </c>
       <c r="M6">
-        <v>3.4145652</v>
+        <v>4.2682065</v>
       </c>
       <c r="N6">
-        <v>195.2854348</v>
+        <v>194.4317935</v>
       </c>
       <c r="O6">
-        <v>50.38364217840001</v>
+        <v>50.16340272300001</v>
       </c>
       <c r="P6">
-        <v>144.9017926216</v>
+        <v>144.268390777</v>
       </c>
       <c r="Q6">
-        <v>298.0017926216</v>
+        <v>297.368390777</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07773843413420459</v>
+        <v>0.07799049134490937</v>
       </c>
       <c r="T6">
-        <v>0.7376081786190435</v>
+        <v>0.7434293613143041</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>58.19188926308978</v>
+        <v>46.55351141047183</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1804,22 +1804,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07595709677766389</v>
+        <v>0.0757923927864914</v>
       </c>
       <c r="C7">
-        <v>1620.91638188952</v>
+        <v>1605.690302747892</v>
       </c>
       <c r="D7">
-        <v>1705.77138188952</v>
+        <v>1707.516302747892</v>
       </c>
       <c r="E7">
-        <v>84.855</v>
+        <v>101.826</v>
       </c>
       <c r="F7">
-        <v>84.855</v>
+        <v>101.826</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1840,28 +1840,28 @@
         <v>198.7</v>
       </c>
       <c r="M7">
-        <v>4.2682065</v>
+        <v>5.1218478</v>
       </c>
       <c r="N7">
-        <v>194.4317935</v>
+        <v>193.5781522</v>
       </c>
       <c r="O7">
-        <v>50.16340272300001</v>
+        <v>49.9431632676</v>
       </c>
       <c r="P7">
-        <v>144.268390777</v>
+        <v>143.6349889324</v>
       </c>
       <c r="Q7">
-        <v>297.368390777</v>
+        <v>296.7349889324</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07799049134490937</v>
+        <v>0.07824791147499086</v>
       </c>
       <c r="T7">
-        <v>0.7434293613143041</v>
+        <v>0.7493743989605278</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>46.55351141047183</v>
+        <v>38.79459284205985</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1886,22 +1886,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0757923927864914</v>
+        <v>0.07562768879531889</v>
       </c>
       <c r="C8">
-        <v>1605.690302747892</v>
+        <v>1590.467797199598</v>
       </c>
       <c r="D8">
-        <v>1707.516302747892</v>
+        <v>1709.264797199598</v>
       </c>
       <c r="E8">
-        <v>101.826</v>
+        <v>118.797</v>
       </c>
       <c r="F8">
-        <v>101.826</v>
+        <v>118.797</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1922,28 +1922,28 @@
         <v>198.7</v>
       </c>
       <c r="M8">
-        <v>5.121847799999999</v>
+        <v>5.975489099999999</v>
       </c>
       <c r="N8">
-        <v>193.5781522</v>
+        <v>192.7245109</v>
       </c>
       <c r="O8">
-        <v>49.9431632676</v>
+        <v>49.7229238122</v>
       </c>
       <c r="P8">
-        <v>143.6349889324</v>
+        <v>143.0015870878</v>
       </c>
       <c r="Q8">
-        <v>296.7349889324</v>
+        <v>296.1015870878</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07824791147499086</v>
+        <v>0.07851086752184827</v>
       </c>
       <c r="T8">
-        <v>0.7493743989605278</v>
+        <v>0.7554472868787132</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.79459284205986</v>
+        <v>33.25250815033702</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1968,22 +1968,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07562768879531889</v>
+        <v>0.07546298480414641</v>
       </c>
       <c r="C9">
-        <v>1590.467797199598</v>
+        <v>1575.248876233957</v>
       </c>
       <c r="D9">
-        <v>1709.264797199598</v>
+        <v>1711.016876233957</v>
       </c>
       <c r="E9">
-        <v>118.797</v>
+        <v>135.768</v>
       </c>
       <c r="F9">
-        <v>118.797</v>
+        <v>135.768</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2004,28 +2004,28 @@
         <v>198.7</v>
       </c>
       <c r="M9">
-        <v>5.9754891</v>
+        <v>6.829130399999999</v>
       </c>
       <c r="N9">
-        <v>192.7245109</v>
+        <v>191.8708696</v>
       </c>
       <c r="O9">
-        <v>49.7229238122</v>
+        <v>49.5026843568</v>
       </c>
       <c r="P9">
-        <v>143.0015870878</v>
+        <v>142.3681852432</v>
       </c>
       <c r="Q9">
-        <v>296.1015870878</v>
+        <v>295.4681852432</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07851086752184827</v>
+        <v>0.07877954000450696</v>
       </c>
       <c r="T9">
-        <v>0.7554472868787132</v>
+        <v>0.7616521940994679</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.25250815033702</v>
+        <v>29.0959446315449</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2050,22 +2050,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07546298480414641</v>
+        <v>0.07529828081297392</v>
       </c>
       <c r="C10">
-        <v>1575.248876233957</v>
+        <v>1560.033550885391</v>
       </c>
       <c r="D10">
-        <v>1711.016876233957</v>
+        <v>1712.772550885391</v>
       </c>
       <c r="E10">
-        <v>135.768</v>
+        <v>152.739</v>
       </c>
       <c r="F10">
-        <v>135.768</v>
+        <v>152.739</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2086,28 +2086,28 @@
         <v>198.7</v>
       </c>
       <c r="M10">
-        <v>6.829130399999999</v>
+        <v>7.682771699999998</v>
       </c>
       <c r="N10">
-        <v>191.8708696</v>
+        <v>191.0172283</v>
       </c>
       <c r="O10">
-        <v>49.5026843568</v>
+        <v>49.28244490140001</v>
       </c>
       <c r="P10">
-        <v>142.3681852432</v>
+        <v>141.7347833986</v>
       </c>
       <c r="Q10">
-        <v>295.4681852432</v>
+        <v>294.8347833986001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07877954000450696</v>
+        <v>0.07905411737689441</v>
       </c>
       <c r="T10">
-        <v>0.7616521940994679</v>
+        <v>0.767993472907492</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>29.0959446315449</v>
+        <v>25.86306189470658</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2132,22 +2132,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07529828081297392</v>
+        <v>0.07513357682180141</v>
       </c>
       <c r="C11">
-        <v>1560.033550885391</v>
+        <v>1544.821832233658</v>
       </c>
       <c r="D11">
-        <v>1712.772550885391</v>
+        <v>1714.531832233658</v>
       </c>
       <c r="E11">
-        <v>152.739</v>
+        <v>169.71</v>
       </c>
       <c r="F11">
-        <v>152.739</v>
+        <v>169.71</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2168,28 +2168,28 @@
         <v>198.7</v>
       </c>
       <c r="M11">
-        <v>7.682771699999998</v>
+        <v>8.536412999999998</v>
       </c>
       <c r="N11">
-        <v>191.0172283</v>
+        <v>190.163587</v>
       </c>
       <c r="O11">
-        <v>49.28244490140001</v>
+        <v>49.062205446</v>
       </c>
       <c r="P11">
-        <v>141.7347833986</v>
+        <v>141.101381554</v>
       </c>
       <c r="Q11">
-        <v>294.8347833986001</v>
+        <v>294.201381554</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07905411737689441</v>
+        <v>0.07933479646866823</v>
       </c>
       <c r="T11">
-        <v>0.767993472907492</v>
+        <v>0.7744756690223611</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.86306189470658</v>
+        <v>23.27675570523592</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2214,22 +2214,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07513357682180141</v>
+        <v>0.07496887283062892</v>
       </c>
       <c r="C12">
-        <v>1544.821832233658</v>
+        <v>1529.613731404087</v>
       </c>
       <c r="D12">
-        <v>1714.531832233658</v>
+        <v>1716.294731404087</v>
       </c>
       <c r="E12">
-        <v>169.71</v>
+        <v>186.681</v>
       </c>
       <c r="F12">
-        <v>169.71</v>
+        <v>186.681</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2250,28 +2250,28 @@
         <v>198.7</v>
       </c>
       <c r="M12">
-        <v>8.536413</v>
+        <v>9.390054299999999</v>
       </c>
       <c r="N12">
-        <v>190.163587</v>
+        <v>189.3099457</v>
       </c>
       <c r="O12">
-        <v>49.062205446</v>
+        <v>48.8419659906</v>
       </c>
       <c r="P12">
-        <v>141.101381554</v>
+        <v>140.4679797094</v>
       </c>
       <c r="Q12">
-        <v>294.201381554</v>
+        <v>293.5679797094</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07933479646866823</v>
+        <v>0.07962178295576282</v>
       </c>
       <c r="T12">
-        <v>0.7744756690223611</v>
+        <v>0.781103532465654</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.27675570523591</v>
+        <v>21.16068700475992</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2296,22 +2296,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07496887283062892</v>
+        <v>0.07480416883945641</v>
       </c>
       <c r="C13">
-        <v>1529.613731404087</v>
+        <v>1514.409259567809</v>
       </c>
       <c r="D13">
-        <v>1716.294731404087</v>
+        <v>1718.061259567809</v>
       </c>
       <c r="E13">
-        <v>186.681</v>
+        <v>203.652</v>
       </c>
       <c r="F13">
-        <v>186.681</v>
+        <v>203.652</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2332,28 +2332,28 @@
         <v>198.7</v>
       </c>
       <c r="M13">
-        <v>9.390054299999999</v>
+        <v>10.2436956</v>
       </c>
       <c r="N13">
-        <v>189.3099457</v>
+        <v>188.4563044</v>
       </c>
       <c r="O13">
-        <v>48.8419659906</v>
+        <v>48.6217265352</v>
       </c>
       <c r="P13">
-        <v>140.4679797094</v>
+        <v>139.8345778648</v>
       </c>
       <c r="Q13">
-        <v>293.5679797094</v>
+        <v>292.9345778648</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07962178295576282</v>
+        <v>0.07991529186301866</v>
       </c>
       <c r="T13">
-        <v>0.781103532465654</v>
+        <v>0.7878820291690221</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.16068700475992</v>
+        <v>19.39729642102993</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2378,22 +2378,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07480416883945641</v>
+        <v>0.07463946484828392</v>
       </c>
       <c r="C14">
-        <v>1514.409259567809</v>
+        <v>1499.208427941995</v>
       </c>
       <c r="D14">
-        <v>1718.061259567809</v>
+        <v>1719.831427941995</v>
       </c>
       <c r="E14">
-        <v>203.652</v>
+        <v>220.623</v>
       </c>
       <c r="F14">
-        <v>203.652</v>
+        <v>220.623</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2414,28 +2414,28 @@
         <v>198.7</v>
       </c>
       <c r="M14">
-        <v>10.2436956</v>
+        <v>11.0973369</v>
       </c>
       <c r="N14">
-        <v>188.4563044</v>
+        <v>187.6026631</v>
       </c>
       <c r="O14">
-        <v>48.6217265352</v>
+        <v>48.40148707980001</v>
       </c>
       <c r="P14">
-        <v>139.8345778648</v>
+        <v>139.2011760202</v>
       </c>
       <c r="Q14">
-        <v>292.9345778648</v>
+        <v>292.3011760202</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07991529186301866</v>
+        <v>0.08021554810147577</v>
       </c>
       <c r="T14">
-        <v>0.7878820291690221</v>
+        <v>0.7948163533828121</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.39729642102993</v>
+        <v>17.90519669633532</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2460,22 +2460,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07463946484828392</v>
+        <v>0.07447476085711142</v>
       </c>
       <c r="C15">
-        <v>1499.208427941995</v>
+        <v>1484.011247790093</v>
       </c>
       <c r="D15">
-        <v>1719.831427941995</v>
+        <v>1721.605247790093</v>
       </c>
       <c r="E15">
-        <v>220.623</v>
+        <v>237.594</v>
       </c>
       <c r="F15">
-        <v>220.623</v>
+        <v>237.594</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2496,28 +2496,28 @@
         <v>198.7</v>
       </c>
       <c r="M15">
-        <v>11.0973369</v>
+        <v>11.9509782</v>
       </c>
       <c r="N15">
-        <v>187.6026631</v>
+        <v>186.7490218</v>
       </c>
       <c r="O15">
-        <v>48.40148707980001</v>
+        <v>48.1812476244</v>
       </c>
       <c r="P15">
-        <v>139.2011760202</v>
+        <v>138.5677741756</v>
       </c>
       <c r="Q15">
-        <v>292.3011760202</v>
+        <v>291.6677741756</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08021554810147577</v>
+        <v>0.08052278704315281</v>
       </c>
       <c r="T15">
-        <v>0.7948163533828121</v>
+        <v>0.8019119409504114</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.90519669633532</v>
+        <v>16.62625407516851</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2542,22 +2542,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07447476085711142</v>
+        <v>0.0743100568659389</v>
       </c>
       <c r="C16">
-        <v>1484.011247790093</v>
+        <v>1468.817730422069</v>
       </c>
       <c r="D16">
-        <v>1721.605247790093</v>
+        <v>1723.382730422069</v>
       </c>
       <c r="E16">
-        <v>237.594</v>
+        <v>254.565</v>
       </c>
       <c r="F16">
-        <v>237.594</v>
+        <v>254.565</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2578,28 +2578,28 @@
         <v>198.7</v>
       </c>
       <c r="M16">
-        <v>11.9509782</v>
+        <v>12.8046195</v>
       </c>
       <c r="N16">
-        <v>186.7490218</v>
+        <v>185.8953805</v>
       </c>
       <c r="O16">
-        <v>48.1812476244</v>
+        <v>47.961008169</v>
       </c>
       <c r="P16">
-        <v>138.5677741756</v>
+        <v>137.934372331</v>
       </c>
       <c r="Q16">
-        <v>291.6677741756</v>
+        <v>291.034372331</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08052278704315281</v>
+        <v>0.08083725513639872</v>
       </c>
       <c r="T16">
-        <v>0.8019119409504114</v>
+        <v>0.8091744835196012</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.62625407516851</v>
+        <v>15.51783713682394</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2624,22 +2624,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0743100568659389</v>
+        <v>0.07414535287476642</v>
       </c>
       <c r="C17">
-        <v>1468.817730422069</v>
+        <v>1453.627887194642</v>
       </c>
       <c r="D17">
-        <v>1723.382730422069</v>
+        <v>1725.163887194642</v>
       </c>
       <c r="E17">
-        <v>254.565</v>
+        <v>271.536</v>
       </c>
       <c r="F17">
-        <v>254.565</v>
+        <v>271.536</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2660,28 +2660,28 @@
         <v>198.7</v>
       </c>
       <c r="M17">
-        <v>12.8046195</v>
+        <v>13.6582608</v>
       </c>
       <c r="N17">
-        <v>185.8953805</v>
+        <v>185.0417392</v>
       </c>
       <c r="O17">
-        <v>47.961008169</v>
+        <v>47.7407687136</v>
       </c>
       <c r="P17">
-        <v>137.934372331</v>
+        <v>137.3009704864</v>
       </c>
       <c r="Q17">
-        <v>291.034372331</v>
+        <v>290.4009704864</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08083725513639872</v>
+        <v>0.08115921056519812</v>
       </c>
       <c r="T17">
-        <v>0.8091744835196012</v>
+        <v>0.8166099437690097</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.51783713682394</v>
+        <v>14.54797231577245</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2706,22 +2706,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07414535287476642</v>
+        <v>0.07398064888359393</v>
       </c>
       <c r="C18">
-        <v>1453.627887194642</v>
+        <v>1438.441729511534</v>
       </c>
       <c r="D18">
-        <v>1725.163887194642</v>
+        <v>1726.948729511534</v>
       </c>
       <c r="E18">
-        <v>271.536</v>
+        <v>288.507</v>
       </c>
       <c r="F18">
-        <v>271.536</v>
+        <v>288.507</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2742,28 +2742,28 @@
         <v>198.7</v>
       </c>
       <c r="M18">
-        <v>13.6582608</v>
+        <v>14.5119021</v>
       </c>
       <c r="N18">
-        <v>185.0417392</v>
+        <v>184.1880979</v>
       </c>
       <c r="O18">
-        <v>47.7407687136</v>
+        <v>47.5205292582</v>
       </c>
       <c r="P18">
-        <v>137.3009704864</v>
+        <v>136.6675686418</v>
       </c>
       <c r="Q18">
-        <v>290.4009704864</v>
+        <v>289.7675686418</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08115921056519812</v>
+        <v>0.08148892395613726</v>
       </c>
       <c r="T18">
-        <v>0.8166099437690097</v>
+        <v>0.8242245717352715</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2780,7 +2780,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.54797231577245</v>
+        <v>13.69220923837407</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2788,22 +2788,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07398064888359393</v>
+        <v>0.07381594489242141</v>
       </c>
       <c r="C19">
-        <v>1438.441729511534</v>
+        <v>1423.259268823704</v>
       </c>
       <c r="D19">
-        <v>1726.948729511534</v>
+        <v>1728.737268823704</v>
       </c>
       <c r="E19">
-        <v>288.507</v>
+        <v>305.478</v>
       </c>
       <c r="F19">
-        <v>288.507</v>
+        <v>305.478</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2824,28 +2824,28 @@
         <v>198.7</v>
       </c>
       <c r="M19">
-        <v>14.5119021</v>
+        <v>15.3655434</v>
       </c>
       <c r="N19">
-        <v>184.1880979</v>
+        <v>183.3344566</v>
       </c>
       <c r="O19">
-        <v>47.5205292582</v>
+        <v>47.3002898028</v>
       </c>
       <c r="P19">
-        <v>136.6675686418</v>
+        <v>136.0341667972</v>
       </c>
       <c r="Q19">
-        <v>289.7675686418</v>
+        <v>289.1341667972</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08148892395613726</v>
+        <v>0.08182667913709929</v>
       </c>
       <c r="T19">
-        <v>0.8242245717352715</v>
+        <v>0.8320249223348567</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.69220923837407</v>
+        <v>12.93153094735328</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2870,22 +2870,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07381594489242142</v>
+        <v>0.07386271090124893</v>
       </c>
       <c r="C20">
-        <v>1423.259268823704</v>
+        <v>1405.78005493158</v>
       </c>
       <c r="D20">
-        <v>1728.737268823704</v>
+        <v>1728.22905493158</v>
       </c>
       <c r="E20">
-        <v>305.478</v>
+        <v>322.449</v>
       </c>
       <c r="F20">
-        <v>305.478</v>
+        <v>322.449</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2906,45 +2906,45 @@
         <v>198.7</v>
       </c>
       <c r="M20">
-        <v>15.3655434</v>
+        <v>16.7028582</v>
       </c>
       <c r="N20">
-        <v>183.3344566</v>
+        <v>181.9971418</v>
       </c>
       <c r="O20">
-        <v>47.3002898028</v>
+        <v>46.9552625844</v>
       </c>
       <c r="P20">
-        <v>136.0341667972</v>
+        <v>135.0418792156</v>
       </c>
       <c r="Q20">
-        <v>289.1341667972</v>
+        <v>288.1418792156</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08182667913709929</v>
+        <v>0.08217277395215916</v>
       </c>
       <c r="T20">
-        <v>0.8320249223348567</v>
+        <v>0.8400178741838146</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>12.93153094735329</v>
+        <v>11.89616756729695</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2952,22 +2952,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07386271090124893</v>
+        <v>0.07370913691007644</v>
       </c>
       <c r="C21">
-        <v>1405.78005493158</v>
+        <v>1390.479090311077</v>
       </c>
       <c r="D21">
-        <v>1728.22905493158</v>
+        <v>1729.899090311078</v>
       </c>
       <c r="E21">
-        <v>322.449</v>
+        <v>339.42</v>
       </c>
       <c r="F21">
-        <v>322.449</v>
+        <v>339.42</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2988,28 +2988,28 @@
         <v>198.7</v>
       </c>
       <c r="M21">
-        <v>16.7028582</v>
+        <v>17.581956</v>
       </c>
       <c r="N21">
-        <v>181.9971418</v>
+        <v>181.118044</v>
       </c>
       <c r="O21">
-        <v>46.9552625844</v>
+        <v>46.728455352</v>
       </c>
       <c r="P21">
-        <v>135.0418792156</v>
+        <v>134.389588648</v>
       </c>
       <c r="Q21">
-        <v>288.1418792156</v>
+        <v>287.489588648</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08217277395215916</v>
+        <v>0.08252752113759554</v>
       </c>
       <c r="T21">
-        <v>0.8400178741838146</v>
+        <v>0.8482106498289962</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.89616756729695</v>
+        <v>11.30135918893211</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3034,22 +3034,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07370913691007644</v>
+        <v>0.07355556291890394</v>
       </c>
       <c r="C22">
-        <v>1390.479090311077</v>
+        <v>1375.181356414967</v>
       </c>
       <c r="D22">
-        <v>1729.899090311078</v>
+        <v>1731.572356414967</v>
       </c>
       <c r="E22">
-        <v>339.42</v>
+        <v>356.391</v>
       </c>
       <c r="F22">
-        <v>339.42</v>
+        <v>356.391</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3070,28 +3070,28 @@
         <v>198.7</v>
       </c>
       <c r="M22">
-        <v>17.581956</v>
+        <v>18.4610538</v>
       </c>
       <c r="N22">
-        <v>181.118044</v>
+        <v>180.2389462</v>
       </c>
       <c r="O22">
-        <v>46.728455352</v>
+        <v>46.50164811960001</v>
       </c>
       <c r="P22">
-        <v>134.389588648</v>
+        <v>133.7372980804</v>
       </c>
       <c r="Q22">
-        <v>287.489588648</v>
+        <v>286.8372980804</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08252752113759554</v>
+        <v>0.08289124926443536</v>
       </c>
       <c r="T22">
-        <v>0.8482106498289962</v>
+        <v>0.8566108375158281</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.30135918893211</v>
+        <v>10.76319922755439</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3116,22 +3116,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07355556291890392</v>
+        <v>0.07340198892773142</v>
       </c>
       <c r="C23">
-        <v>1375.181356414967</v>
+        <v>1359.886862627199</v>
       </c>
       <c r="D23">
-        <v>1731.572356414968</v>
+        <v>1733.248862627199</v>
       </c>
       <c r="E23">
-        <v>356.391</v>
+        <v>373.362</v>
       </c>
       <c r="F23">
-        <v>356.391</v>
+        <v>373.362</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3152,28 +3152,28 @@
         <v>198.7</v>
       </c>
       <c r="M23">
-        <v>18.4610538</v>
+        <v>19.3401516</v>
       </c>
       <c r="N23">
-        <v>180.2389462</v>
+        <v>179.3598484</v>
       </c>
       <c r="O23">
-        <v>46.50164811960001</v>
+        <v>46.27484088720001</v>
       </c>
       <c r="P23">
-        <v>133.7372980804</v>
+        <v>133.0850075128</v>
       </c>
       <c r="Q23">
-        <v>286.8372980804</v>
+        <v>286.1850075128</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08289124926443535</v>
+        <v>0.08326430375350183</v>
       </c>
       <c r="T23">
-        <v>0.856610837515828</v>
+        <v>0.8652264146305274</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.76319922755439</v>
+        <v>10.27396289902919</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3198,22 +3198,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07340198892773142</v>
+        <v>0.07324841493655893</v>
       </c>
       <c r="C24">
-        <v>1359.886862627199</v>
+        <v>1344.595618368098</v>
       </c>
       <c r="D24">
-        <v>1733.248862627199</v>
+        <v>1734.928618368098</v>
       </c>
       <c r="E24">
-        <v>373.362</v>
+        <v>390.333</v>
       </c>
       <c r="F24">
-        <v>373.362</v>
+        <v>390.333</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3234,28 +3234,28 @@
         <v>198.7</v>
       </c>
       <c r="M24">
-        <v>19.3401516</v>
+        <v>20.2192494</v>
       </c>
       <c r="N24">
-        <v>179.3598484</v>
+        <v>178.4807506</v>
       </c>
       <c r="O24">
-        <v>46.27484088720001</v>
+        <v>46.04803365480001</v>
       </c>
       <c r="P24">
-        <v>133.0850075128</v>
+        <v>132.4327169452</v>
       </c>
       <c r="Q24">
-        <v>286.1850075128</v>
+        <v>285.5327169452</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08326430375350183</v>
+        <v>0.08364704796955705</v>
       </c>
       <c r="T24">
-        <v>0.8652264146305274</v>
+        <v>0.8740657729689851</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.27396289902919</v>
+        <v>9.827268859940965</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3280,22 +3280,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07324841493655893</v>
+        <v>0.07339757694538644</v>
       </c>
       <c r="C25">
-        <v>1344.595618368098</v>
+        <v>1325.993074457792</v>
       </c>
       <c r="D25">
-        <v>1734.928618368098</v>
+        <v>1733.297074457792</v>
       </c>
       <c r="E25">
-        <v>390.333</v>
+        <v>407.304</v>
       </c>
       <c r="F25">
-        <v>390.333</v>
+        <v>407.304</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3316,45 +3316,45 @@
         <v>198.7</v>
       </c>
       <c r="M25">
-        <v>20.2192494</v>
+        <v>21.790764</v>
       </c>
       <c r="N25">
-        <v>178.4807506</v>
+        <v>176.909236</v>
       </c>
       <c r="O25">
-        <v>46.04803365480001</v>
+        <v>45.64258288800001</v>
       </c>
       <c r="P25">
-        <v>132.4327169452</v>
+        <v>131.266653112</v>
       </c>
       <c r="Q25">
-        <v>285.5327169452</v>
+        <v>284.366653112</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08364704796955705</v>
+        <v>0.08403986440182426</v>
       </c>
       <c r="T25">
-        <v>0.8740657729689851</v>
+        <v>0.8831377460005603</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>9.827268859940965</v>
+        <v>9.118542149325283</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3362,22 +3362,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07339757694538644</v>
+        <v>0.07325661695421393</v>
       </c>
       <c r="C26">
-        <v>1325.993074457792</v>
+        <v>1310.56382435707</v>
       </c>
       <c r="D26">
-        <v>1733.297074457792</v>
+        <v>1734.83882435707</v>
       </c>
       <c r="E26">
-        <v>407.304</v>
+        <v>424.275</v>
       </c>
       <c r="F26">
-        <v>407.304</v>
+        <v>424.275</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3398,28 +3398,28 @@
         <v>198.7</v>
       </c>
       <c r="M26">
-        <v>21.790764</v>
+        <v>22.6987125</v>
       </c>
       <c r="N26">
-        <v>176.909236</v>
+        <v>176.0012875</v>
       </c>
       <c r="O26">
-        <v>45.64258288800001</v>
+        <v>45.40833217500001</v>
       </c>
       <c r="P26">
-        <v>131.266653112</v>
+        <v>130.592955325</v>
       </c>
       <c r="Q26">
-        <v>284.366653112</v>
+        <v>283.692955325</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08403986440182426</v>
+        <v>0.08444315593895191</v>
       </c>
       <c r="T26">
-        <v>0.8831377460005603</v>
+        <v>0.8924516383129774</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.118542149325284</v>
+        <v>8.753800463352274</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3444,22 +3444,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07325661695421393</v>
+        <v>0.07311565696304145</v>
       </c>
       <c r="C27">
-        <v>1310.56382435707</v>
+        <v>1295.137319439478</v>
       </c>
       <c r="D27">
-        <v>1734.83882435707</v>
+        <v>1736.383319439478</v>
       </c>
       <c r="E27">
-        <v>424.275</v>
+        <v>441.246</v>
       </c>
       <c r="F27">
-        <v>424.275</v>
+        <v>441.246</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3480,28 +3480,28 @@
         <v>198.7</v>
       </c>
       <c r="M27">
-        <v>22.6987125</v>
+        <v>23.606661</v>
       </c>
       <c r="N27">
-        <v>176.0012875</v>
+        <v>175.093339</v>
       </c>
       <c r="O27">
-        <v>45.40833217500001</v>
+        <v>45.174081462</v>
       </c>
       <c r="P27">
-        <v>130.592955325</v>
+        <v>129.919257538</v>
       </c>
       <c r="Q27">
-        <v>283.692955325</v>
+        <v>283.019257538</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08444315593895191</v>
+        <v>0.0848573472473533</v>
       </c>
       <c r="T27">
-        <v>0.8924516383129774</v>
+        <v>0.9020172574446489</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.753800463352274</v>
+        <v>8.417115830146416</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3526,22 +3526,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07311565696304145</v>
+        <v>0.07297469697186894</v>
       </c>
       <c r="C28">
-        <v>1295.137319439478</v>
+        <v>1279.713567043509</v>
       </c>
       <c r="D28">
-        <v>1736.383319439478</v>
+        <v>1737.930567043509</v>
       </c>
       <c r="E28">
-        <v>441.246</v>
+        <v>458.217</v>
       </c>
       <c r="F28">
-        <v>441.246</v>
+        <v>458.217</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3562,28 +3562,28 @@
         <v>198.7</v>
       </c>
       <c r="M28">
-        <v>23.606661</v>
+        <v>24.5146095</v>
       </c>
       <c r="N28">
-        <v>175.093339</v>
+        <v>174.1853905</v>
       </c>
       <c r="O28">
-        <v>45.174081462</v>
+        <v>44.939830749</v>
       </c>
       <c r="P28">
-        <v>129.919257538</v>
+        <v>129.245559751</v>
       </c>
       <c r="Q28">
-        <v>283.019257538</v>
+        <v>282.345559751</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0848573472473533</v>
+        <v>0.08528288626283417</v>
       </c>
       <c r="T28">
-        <v>0.9020172574446489</v>
+        <v>0.9118449483333527</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.417115830146416</v>
+        <v>8.105370799400252</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3608,22 +3608,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07297469697186894</v>
+        <v>0.07283373698069645</v>
       </c>
       <c r="C29">
-        <v>1279.713567043509</v>
+        <v>1264.292574533832</v>
       </c>
       <c r="D29">
-        <v>1737.930567043509</v>
+        <v>1739.480574533832</v>
       </c>
       <c r="E29">
-        <v>458.217</v>
+        <v>475.188</v>
       </c>
       <c r="F29">
-        <v>458.217</v>
+        <v>475.188</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3644,28 +3644,28 @@
         <v>198.7</v>
       </c>
       <c r="M29">
-        <v>24.5146095</v>
+        <v>25.422558</v>
       </c>
       <c r="N29">
-        <v>174.1853905</v>
+        <v>173.277442</v>
       </c>
       <c r="O29">
-        <v>44.939830749</v>
+        <v>44.705580036</v>
       </c>
       <c r="P29">
-        <v>129.245559751</v>
+        <v>128.571861964</v>
       </c>
       <c r="Q29">
-        <v>282.345559751</v>
+        <v>281.671861964</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08528288626283417</v>
+        <v>0.08572024580652285</v>
       </c>
       <c r="T29">
-        <v>0.9118449483333527</v>
+        <v>0.9219456306356315</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.105370799400252</v>
+        <v>7.815893270850243</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3690,22 +3690,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07283373698069645</v>
+        <v>0.07286492098952395</v>
       </c>
       <c r="C30">
-        <v>1264.292574533832</v>
+        <v>1246.97843452409</v>
       </c>
       <c r="D30">
-        <v>1739.480574533832</v>
+        <v>1739.13743452409</v>
       </c>
       <c r="E30">
-        <v>475.188</v>
+        <v>492.159</v>
       </c>
       <c r="F30">
-        <v>475.188</v>
+        <v>492.159</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3726,45 +3726,45 @@
         <v>198.7</v>
       </c>
       <c r="M30">
-        <v>25.422558</v>
+        <v>26.7242337</v>
       </c>
       <c r="N30">
-        <v>173.277442</v>
+        <v>171.9757663</v>
       </c>
       <c r="O30">
-        <v>44.705580036</v>
+        <v>44.3697477054</v>
       </c>
       <c r="P30">
-        <v>128.571861964</v>
+        <v>127.6060185946</v>
       </c>
       <c r="Q30">
-        <v>281.671861964</v>
+        <v>280.7060185946</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08572024580652285</v>
+        <v>0.08616992533735768</v>
       </c>
       <c r="T30">
-        <v>0.9219456306356315</v>
+        <v>0.9323308391999462</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.815893270850243</v>
+        <v>7.435199161575959</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3772,22 +3772,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07286492098952395</v>
+        <v>0.07272989699835145</v>
       </c>
       <c r="C31">
-        <v>1246.97843452409</v>
+        <v>1231.494177118997</v>
       </c>
       <c r="D31">
-        <v>1739.13743452409</v>
+        <v>1740.624177118997</v>
       </c>
       <c r="E31">
-        <v>492.1589999999999</v>
+        <v>509.1299999999999</v>
       </c>
       <c r="F31">
-        <v>492.1589999999999</v>
+        <v>509.1299999999999</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3808,28 +3808,28 @@
         <v>198.7</v>
       </c>
       <c r="M31">
-        <v>26.7242337</v>
+        <v>27.645759</v>
       </c>
       <c r="N31">
-        <v>171.9757663</v>
+        <v>171.054241</v>
       </c>
       <c r="O31">
-        <v>44.36974770540001</v>
+        <v>44.13199417800001</v>
       </c>
       <c r="P31">
-        <v>127.6060185946</v>
+        <v>126.922246822</v>
       </c>
       <c r="Q31">
-        <v>280.7060185946</v>
+        <v>280.022246822</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08616992533735768</v>
+        <v>0.08663245285478778</v>
       </c>
       <c r="T31">
-        <v>0.9323308391999462</v>
+        <v>0.9430127680089557</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.435199161575961</v>
+        <v>7.187359189523429</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3854,22 +3854,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07272989699835145</v>
+        <v>0.07259487300717896</v>
       </c>
       <c r="C32">
-        <v>1231.494177118997</v>
+        <v>1216.012463842656</v>
       </c>
       <c r="D32">
-        <v>1740.624177118997</v>
+        <v>1742.113463842656</v>
       </c>
       <c r="E32">
-        <v>509.1299999999999</v>
+        <v>526.101</v>
       </c>
       <c r="F32">
-        <v>509.1299999999999</v>
+        <v>526.101</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3890,28 +3890,28 @@
         <v>198.7</v>
       </c>
       <c r="M32">
-        <v>27.645759</v>
+        <v>28.5672843</v>
       </c>
       <c r="N32">
-        <v>171.054241</v>
+        <v>170.1327157</v>
       </c>
       <c r="O32">
-        <v>44.13199417800001</v>
+        <v>43.8942406506</v>
       </c>
       <c r="P32">
-        <v>126.922246822</v>
+        <v>126.2384750494</v>
       </c>
       <c r="Q32">
-        <v>280.022246822</v>
+        <v>279.3384750494</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08663245285478778</v>
+        <v>0.08710838696692602</v>
       </c>
       <c r="T32">
-        <v>0.9430127680089557</v>
+        <v>0.9540043179428642</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.187359189523429</v>
+        <v>6.955508893087188</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3936,22 +3936,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07259487300717896</v>
+        <v>0.07245984901600645</v>
       </c>
       <c r="C33">
-        <v>1216.012463842656</v>
+        <v>1200.533301230968</v>
       </c>
       <c r="D33">
-        <v>1742.113463842656</v>
+        <v>1743.605301230968</v>
       </c>
       <c r="E33">
-        <v>526.101</v>
+        <v>543.072</v>
       </c>
       <c r="F33">
-        <v>526.101</v>
+        <v>543.072</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3972,28 +3972,28 @@
         <v>198.7</v>
       </c>
       <c r="M33">
-        <v>28.5672843</v>
+        <v>29.4888096</v>
       </c>
       <c r="N33">
-        <v>170.1327157</v>
+        <v>169.2111904</v>
       </c>
       <c r="O33">
-        <v>43.8942406506</v>
+        <v>43.65648712320001</v>
       </c>
       <c r="P33">
-        <v>126.2384750494</v>
+        <v>125.5547032768</v>
       </c>
       <c r="Q33">
-        <v>279.3384750494</v>
+        <v>278.6547032768</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08710838696692602</v>
+        <v>0.08759831914118596</v>
       </c>
       <c r="T33">
-        <v>0.9540043179428642</v>
+        <v>0.9653191487571816</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.955508893087188</v>
+        <v>6.738149240178214</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4018,22 +4018,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07245984901600645</v>
+        <v>0.07232482502483395</v>
       </c>
       <c r="C34">
-        <v>1200.533301230968</v>
+        <v>1185.056695842239</v>
       </c>
       <c r="D34">
-        <v>1743.605301230968</v>
+        <v>1745.099695842239</v>
       </c>
       <c r="E34">
-        <v>543.072</v>
+        <v>560.043</v>
       </c>
       <c r="F34">
-        <v>543.072</v>
+        <v>560.043</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4054,28 +4054,28 @@
         <v>198.7</v>
       </c>
       <c r="M34">
-        <v>29.4888096</v>
+        <v>30.4103349</v>
       </c>
       <c r="N34">
-        <v>169.2111904</v>
+        <v>168.2896651</v>
       </c>
       <c r="O34">
-        <v>43.65648712320001</v>
+        <v>43.41873359580001</v>
       </c>
       <c r="P34">
-        <v>125.5547032768</v>
+        <v>124.8709315042</v>
       </c>
       <c r="Q34">
-        <v>278.6547032768</v>
+        <v>277.9709315042</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08759831914118596</v>
+        <v>0.08810287615646858</v>
       </c>
       <c r="T34">
-        <v>0.9653191487571816</v>
+        <v>0.9769717357152099</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.738149240178214</v>
+        <v>6.533962899566752</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4100,22 +4100,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07232482502483395</v>
+        <v>0.07218980103366145</v>
       </c>
       <c r="C35">
-        <v>1185.056695842239</v>
+        <v>1169.582654257279</v>
       </c>
       <c r="D35">
-        <v>1745.099695842239</v>
+        <v>1746.596654257279</v>
       </c>
       <c r="E35">
-        <v>560.043</v>
+        <v>577.014</v>
       </c>
       <c r="F35">
-        <v>560.043</v>
+        <v>577.014</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4136,28 +4136,28 @@
         <v>198.7</v>
       </c>
       <c r="M35">
-        <v>30.4103349</v>
+        <v>31.3318602</v>
       </c>
       <c r="N35">
-        <v>168.2896651</v>
+        <v>167.3681398</v>
       </c>
       <c r="O35">
-        <v>43.41873359580001</v>
+        <v>43.1809800684</v>
       </c>
       <c r="P35">
-        <v>124.8709315042</v>
+        <v>124.1871597316</v>
       </c>
       <c r="Q35">
-        <v>277.9709315042</v>
+        <v>277.2871597316</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08810287615646858</v>
+        <v>0.08862272277827493</v>
       </c>
       <c r="T35">
-        <v>0.9769717357152099</v>
+        <v>0.9889774313689361</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.533962899566752</v>
+        <v>6.34178752016773</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4182,22 +4182,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07218980103366145</v>
+        <v>0.07205477704248894</v>
       </c>
       <c r="C36">
-        <v>1169.582654257279</v>
+        <v>1154.111183079498</v>
       </c>
       <c r="D36">
-        <v>1746.596654257279</v>
+        <v>1748.096183079497</v>
       </c>
       <c r="E36">
-        <v>577.014</v>
+        <v>593.985</v>
       </c>
       <c r="F36">
-        <v>577.014</v>
+        <v>593.985</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4218,28 +4218,28 @@
         <v>198.7</v>
       </c>
       <c r="M36">
-        <v>31.3318602</v>
+        <v>32.2533855</v>
       </c>
       <c r="N36">
-        <v>167.3681398</v>
+        <v>166.4466145</v>
       </c>
       <c r="O36">
-        <v>43.1809800684</v>
+        <v>42.943226541</v>
       </c>
       <c r="P36">
-        <v>124.1871597316</v>
+        <v>123.503387959</v>
       </c>
       <c r="Q36">
-        <v>277.2871597316</v>
+        <v>276.603387959</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08862272277827493</v>
+        <v>0.08915856468075224</v>
       </c>
       <c r="T36">
-        <v>0.9889774313689361</v>
+        <v>1.001352533042777</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.34178752016773</v>
+        <v>6.160593591020081</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4264,22 +4264,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07205477704248894</v>
+        <v>0.07218687305131646</v>
       </c>
       <c r="C37">
-        <v>1154.111183079498</v>
+        <v>1135.673144107421</v>
       </c>
       <c r="D37">
-        <v>1748.096183079497</v>
+        <v>1746.629144107421</v>
       </c>
       <c r="E37">
-        <v>593.985</v>
+        <v>610.956</v>
       </c>
       <c r="F37">
-        <v>593.985</v>
+        <v>610.956</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4300,45 +4300,45 @@
         <v>198.7</v>
       </c>
       <c r="M37">
-        <v>32.2533855</v>
+        <v>33.7858668</v>
       </c>
       <c r="N37">
-        <v>166.4466145</v>
+        <v>164.9141332</v>
       </c>
       <c r="O37">
-        <v>42.943226541</v>
+        <v>42.5478463656</v>
       </c>
       <c r="P37">
-        <v>123.503387959</v>
+        <v>122.3662868344</v>
       </c>
       <c r="Q37">
-        <v>276.603387959</v>
+        <v>275.4662868344</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08915856468075224</v>
+        <v>0.08971115164268198</v>
       </c>
       <c r="T37">
-        <v>1.001352533042777</v>
+        <v>1.014114356643925</v>
       </c>
       <c r="U37">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.258</v>
       </c>
       <c r="W37">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>6.160593591020081</v>
+        <v>5.881157383832461</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4346,22 +4346,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07218687305131646</v>
+        <v>0.07205926906014395</v>
       </c>
       <c r="C38">
-        <v>1135.673144107421</v>
+        <v>1120.119254911898</v>
       </c>
       <c r="D38">
-        <v>1746.629144107421</v>
+        <v>1748.046254911897</v>
       </c>
       <c r="E38">
-        <v>610.9559999999999</v>
+        <v>627.9269999999999</v>
       </c>
       <c r="F38">
-        <v>610.9559999999999</v>
+        <v>627.9269999999999</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4382,28 +4382,28 @@
         <v>198.7</v>
       </c>
       <c r="M38">
-        <v>33.78586679999999</v>
+        <v>34.7243631</v>
       </c>
       <c r="N38">
-        <v>164.9141332</v>
+        <v>163.9756369</v>
       </c>
       <c r="O38">
-        <v>42.54784636560001</v>
+        <v>42.3057143202</v>
       </c>
       <c r="P38">
-        <v>122.3662868344</v>
+        <v>121.6699225798</v>
       </c>
       <c r="Q38">
-        <v>275.4662868344</v>
+        <v>274.7699225798</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08971115164268198</v>
+        <v>0.09028128104784755</v>
       </c>
       <c r="T38">
-        <v>1.014114356643925</v>
+        <v>1.027281317502253</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.881157383832463</v>
+        <v>5.722207184269422</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4428,22 +4428,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07205926906014395</v>
+        <v>0.07193166506897146</v>
       </c>
       <c r="C39">
-        <v>1120.119254911898</v>
+        <v>1104.567667102101</v>
       </c>
       <c r="D39">
-        <v>1748.046254911897</v>
+        <v>1749.465667102101</v>
       </c>
       <c r="E39">
-        <v>627.9269999999999</v>
+        <v>644.898</v>
       </c>
       <c r="F39">
-        <v>627.9269999999999</v>
+        <v>644.898</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4464,28 +4464,28 @@
         <v>198.7</v>
       </c>
       <c r="M39">
-        <v>34.7243631</v>
+        <v>35.6628594</v>
       </c>
       <c r="N39">
-        <v>163.9756369</v>
+        <v>163.0371406</v>
       </c>
       <c r="O39">
-        <v>42.3057143202</v>
+        <v>42.06358227480001</v>
       </c>
       <c r="P39">
-        <v>121.6699225798</v>
+        <v>120.9735583252</v>
       </c>
       <c r="Q39">
-        <v>274.7699225798</v>
+        <v>274.0735583252</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09028128104784755</v>
+        <v>0.09086980172414752</v>
       </c>
       <c r="T39">
-        <v>1.027281317502253</v>
+        <v>1.04087301903343</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.722207184269422</v>
+        <v>5.571622784683385</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4510,22 +4510,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07193166506897146</v>
+        <v>0.07180406107779896</v>
       </c>
       <c r="C40">
-        <v>1104.567667102101</v>
+        <v>1089.018386288758</v>
       </c>
       <c r="D40">
-        <v>1749.465667102101</v>
+        <v>1750.887386288758</v>
       </c>
       <c r="E40">
-        <v>644.898</v>
+        <v>661.869</v>
       </c>
       <c r="F40">
-        <v>644.898</v>
+        <v>661.869</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4546,28 +4546,28 @@
         <v>198.7</v>
       </c>
       <c r="M40">
-        <v>35.6628594</v>
+        <v>36.60135570000001</v>
       </c>
       <c r="N40">
-        <v>163.0371406</v>
+        <v>162.0986443</v>
       </c>
       <c r="O40">
-        <v>42.06358227480001</v>
+        <v>41.82145022940001</v>
       </c>
       <c r="P40">
-        <v>120.9735583252</v>
+        <v>120.2771940706</v>
       </c>
       <c r="Q40">
-        <v>274.0735583252</v>
+        <v>273.3771940706</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09086980172414752</v>
+        <v>0.09147761816032618</v>
       </c>
       <c r="T40">
-        <v>1.04087301903343</v>
+        <v>1.054910350123006</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.571622784683385</v>
+        <v>5.428760661999195</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4592,22 +4592,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07180406107779896</v>
+        <v>0.07167645708662647</v>
       </c>
       <c r="C41">
-        <v>1089.018386288758</v>
+        <v>1073.471418100847</v>
       </c>
       <c r="D41">
-        <v>1750.887386288758</v>
+        <v>1752.311418100847</v>
       </c>
       <c r="E41">
-        <v>661.869</v>
+        <v>678.84</v>
       </c>
       <c r="F41">
-        <v>661.869</v>
+        <v>678.84</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4628,28 +4628,28 @@
         <v>198.7</v>
       </c>
       <c r="M41">
-        <v>36.60135570000001</v>
+        <v>37.539852</v>
       </c>
       <c r="N41">
-        <v>162.0986443</v>
+        <v>161.160148</v>
       </c>
       <c r="O41">
-        <v>41.82145022940001</v>
+        <v>41.57931818400001</v>
       </c>
       <c r="P41">
-        <v>120.2771940706</v>
+        <v>119.580829816</v>
       </c>
       <c r="Q41">
-        <v>273.3771940706</v>
+        <v>272.680829816</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09147761816032618</v>
+        <v>0.09210569514437744</v>
       </c>
       <c r="T41">
-        <v>1.054910350123006</v>
+        <v>1.069415592248902</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.428760661999195</v>
+        <v>5.293041645449215</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4674,22 +4674,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07167645708662647</v>
+        <v>0.07154885309545396</v>
       </c>
       <c r="C42">
-        <v>1073.471418100847</v>
+        <v>1057.926768185677</v>
       </c>
       <c r="D42">
-        <v>1752.311418100847</v>
+        <v>1753.737768185677</v>
       </c>
       <c r="E42">
-        <v>678.84</v>
+        <v>695.811</v>
       </c>
       <c r="F42">
-        <v>678.84</v>
+        <v>695.811</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4710,28 +4710,28 @@
         <v>198.7</v>
       </c>
       <c r="M42">
-        <v>37.539852</v>
+        <v>38.4783483</v>
       </c>
       <c r="N42">
-        <v>161.160148</v>
+        <v>160.2216517</v>
       </c>
       <c r="O42">
-        <v>41.57931818400001</v>
+        <v>41.33718613860001</v>
       </c>
       <c r="P42">
-        <v>119.580829816</v>
+        <v>118.8844655614</v>
       </c>
       <c r="Q42">
-        <v>272.680829816</v>
+        <v>271.9844655614</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09210569514437744</v>
+        <v>0.09275506287365079</v>
       </c>
       <c r="T42">
-        <v>1.069415592248902</v>
+        <v>1.084412537497709</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4748,7 +4748,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.293041645449215</v>
+        <v>5.163943068730942</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4756,22 +4756,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07154885309545396</v>
+        <v>0.07142124910428148</v>
       </c>
       <c r="C43">
-        <v>1057.926768185677</v>
+        <v>1042.384442208955</v>
       </c>
       <c r="D43">
-        <v>1753.737768185677</v>
+        <v>1755.166442208955</v>
       </c>
       <c r="E43">
-        <v>695.811</v>
+        <v>712.782</v>
       </c>
       <c r="F43">
-        <v>695.811</v>
+        <v>712.782</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4792,28 +4792,28 @@
         <v>198.7</v>
       </c>
       <c r="M43">
-        <v>38.4783483</v>
+        <v>39.4168446</v>
       </c>
       <c r="N43">
-        <v>160.2216517</v>
+        <v>159.2831554</v>
       </c>
       <c r="O43">
-        <v>41.33718613860001</v>
+        <v>41.0950540932</v>
       </c>
       <c r="P43">
-        <v>118.8844655614</v>
+        <v>118.1881013068</v>
       </c>
       <c r="Q43">
-        <v>271.9844655614</v>
+        <v>271.2881013068</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09275506287365079</v>
+        <v>0.09342682259358875</v>
       </c>
       <c r="T43">
-        <v>1.084412537497709</v>
+        <v>1.099926618789578</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.163943068730942</v>
+        <v>5.040992043284966</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4838,22 +4838,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07142124910428149</v>
+        <v>0.07129364511310898</v>
       </c>
       <c r="C44">
-        <v>1042.384442208955</v>
+        <v>1026.844445854868</v>
       </c>
       <c r="D44">
-        <v>1755.166442208955</v>
+        <v>1756.597445854868</v>
       </c>
       <c r="E44">
-        <v>712.7819999999999</v>
+        <v>729.7529999999999</v>
       </c>
       <c r="F44">
-        <v>712.7819999999999</v>
+        <v>729.7529999999999</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4874,28 +4874,28 @@
         <v>198.7</v>
       </c>
       <c r="M44">
-        <v>39.4168446</v>
+        <v>40.35534089999999</v>
       </c>
       <c r="N44">
-        <v>159.2831554</v>
+        <v>158.3446591</v>
       </c>
       <c r="O44">
-        <v>41.09505409320001</v>
+        <v>40.85292204780001</v>
       </c>
       <c r="P44">
-        <v>118.1881013068</v>
+        <v>117.4917370522</v>
       </c>
       <c r="Q44">
-        <v>271.2881013068</v>
+        <v>270.5917370522</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09342682259358875</v>
+        <v>0.09412215283001574</v>
       </c>
       <c r="T44">
-        <v>1.099926618789578</v>
+        <v>1.115985053810987</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.040992043284968</v>
+        <v>4.923759670185317</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4920,22 +4920,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07129364511310898</v>
+        <v>0.07116604112193647</v>
       </c>
       <c r="C45">
-        <v>1026.844445854868</v>
+        <v>1011.306784826155</v>
       </c>
       <c r="D45">
-        <v>1756.597445854868</v>
+        <v>1758.030784826155</v>
       </c>
       <c r="E45">
-        <v>729.7529999999999</v>
+        <v>746.7239999999999</v>
       </c>
       <c r="F45">
-        <v>729.7529999999999</v>
+        <v>746.7239999999999</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4956,28 +4956,28 @@
         <v>198.7</v>
       </c>
       <c r="M45">
-        <v>40.35534089999999</v>
+        <v>41.2938372</v>
       </c>
       <c r="N45">
-        <v>158.3446591</v>
+        <v>157.4061628</v>
       </c>
       <c r="O45">
-        <v>40.85292204780001</v>
+        <v>40.6107900024</v>
       </c>
       <c r="P45">
-        <v>117.4917370522</v>
+        <v>116.7953727976</v>
       </c>
       <c r="Q45">
-        <v>270.5917370522</v>
+        <v>269.8953727976</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09412215283001574</v>
+        <v>0.09484231628917228</v>
       </c>
       <c r="T45">
-        <v>1.115985053810987</v>
+        <v>1.132617004368875</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.923759670185317</v>
+        <v>4.811856041317468</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5002,22 +5002,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07116604112193647</v>
+        <v>0.07103843713076398</v>
       </c>
       <c r="C46">
-        <v>1011.306784826155</v>
+        <v>995.7714648441843</v>
       </c>
       <c r="D46">
-        <v>1758.030784826155</v>
+        <v>1759.466464844184</v>
       </c>
       <c r="E46">
-        <v>746.7239999999999</v>
+        <v>763.6949999999999</v>
       </c>
       <c r="F46">
-        <v>746.7239999999999</v>
+        <v>763.6949999999999</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5038,28 +5038,28 @@
         <v>198.7</v>
       </c>
       <c r="M46">
-        <v>41.2938372</v>
+        <v>42.2323335</v>
       </c>
       <c r="N46">
-        <v>157.4061628</v>
+        <v>156.4676665</v>
       </c>
       <c r="O46">
-        <v>40.6107900024</v>
+        <v>40.368657957</v>
       </c>
       <c r="P46">
-        <v>116.7953727976</v>
+        <v>116.099008543</v>
       </c>
       <c r="Q46">
-        <v>269.8953727976</v>
+        <v>269.199008543</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09484231628917228</v>
+        <v>0.09558866751047995</v>
       </c>
       <c r="T46">
-        <v>1.132617004368875</v>
+        <v>1.149853753128868</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.811856041317468</v>
+        <v>4.704925907065969</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5084,22 +5084,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07103843713076398</v>
+        <v>0.07091083313959148</v>
       </c>
       <c r="C47">
-        <v>995.7714648441843</v>
+        <v>980.2384916490264</v>
       </c>
       <c r="D47">
-        <v>1759.466464844184</v>
+        <v>1760.904491649026</v>
       </c>
       <c r="E47">
-        <v>763.6949999999999</v>
+        <v>780.6659999999999</v>
       </c>
       <c r="F47">
-        <v>763.6949999999999</v>
+        <v>780.6659999999999</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5120,28 +5120,28 @@
         <v>198.7</v>
       </c>
       <c r="M47">
-        <v>42.2323335</v>
+        <v>43.1708298</v>
       </c>
       <c r="N47">
-        <v>156.4676665</v>
+        <v>155.5291702</v>
       </c>
       <c r="O47">
-        <v>40.368657957</v>
+        <v>40.12652591160001</v>
       </c>
       <c r="P47">
-        <v>116.099008543</v>
+        <v>115.4026442884</v>
       </c>
       <c r="Q47">
-        <v>269.199008543</v>
+        <v>268.5026442884</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09558866751047995</v>
+        <v>0.09636266136961386</v>
       </c>
       <c r="T47">
-        <v>1.149853753128868</v>
+        <v>1.167728899991082</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.704925907065969</v>
+        <v>4.602644909086274</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5166,22 +5166,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07091083313959148</v>
+        <v>0.07078322914841897</v>
       </c>
       <c r="C48">
-        <v>980.2384916490264</v>
+        <v>964.7078709995347</v>
       </c>
       <c r="D48">
-        <v>1760.904491649026</v>
+        <v>1762.344870999535</v>
       </c>
       <c r="E48">
-        <v>780.6659999999999</v>
+        <v>797.6370000000001</v>
       </c>
       <c r="F48">
-        <v>780.6659999999999</v>
+        <v>797.6370000000001</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5202,28 +5202,28 @@
         <v>198.7</v>
       </c>
       <c r="M48">
-        <v>43.1708298</v>
+        <v>44.1093261</v>
       </c>
       <c r="N48">
-        <v>155.5291702</v>
+        <v>154.5906739</v>
       </c>
       <c r="O48">
-        <v>40.12652591160001</v>
+        <v>39.88439386620001</v>
       </c>
       <c r="P48">
-        <v>115.4026442884</v>
+        <v>114.7062800338</v>
       </c>
       <c r="Q48">
-        <v>268.5026442884</v>
+        <v>267.8062800338</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09636266136961386</v>
+        <v>0.09716586254418674</v>
       </c>
       <c r="T48">
-        <v>1.167728899991082</v>
+        <v>1.186278580697154</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.602644909086274</v>
+        <v>4.504716293999332</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5248,22 +5248,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07078322914841897</v>
+        <v>0.07154602515724648</v>
       </c>
       <c r="C49">
-        <v>964.7078709995347</v>
+        <v>939.1614050176601</v>
       </c>
       <c r="D49">
-        <v>1762.344870999535</v>
+        <v>1753.76940501766</v>
       </c>
       <c r="E49">
-        <v>797.6370000000001</v>
+        <v>814.6080000000001</v>
       </c>
       <c r="F49">
-        <v>797.6370000000001</v>
+        <v>814.6080000000001</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5284,45 +5284,45 @@
         <v>198.7</v>
       </c>
       <c r="M49">
-        <v>44.1093261</v>
+        <v>47.0843424</v>
       </c>
       <c r="N49">
-        <v>154.5906739</v>
+        <v>151.6156576</v>
       </c>
       <c r="O49">
-        <v>39.88439386620001</v>
+        <v>39.1168396608</v>
       </c>
       <c r="P49">
-        <v>114.7062800338</v>
+        <v>112.4988179392</v>
       </c>
       <c r="Q49">
-        <v>267.8062800338</v>
+        <v>265.5988179392</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09716586254418674</v>
+        <v>0.09799995607162784</v>
       </c>
       <c r="T49">
-        <v>1.186278580697154</v>
+        <v>1.205541710661151</v>
       </c>
       <c r="U49">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V49">
         <v>0.258</v>
       </c>
       <c r="W49">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.504716293999332</v>
+        <v>4.220086548346909</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5330,22 +5330,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07154602515724648</v>
+        <v>0.07143697116607399</v>
       </c>
       <c r="C50">
-        <v>939.1614050176602</v>
+        <v>923.4112898547576</v>
       </c>
       <c r="D50">
-        <v>1753.76940501766</v>
+        <v>1754.990289854758</v>
       </c>
       <c r="E50">
-        <v>814.6079999999999</v>
+        <v>831.579</v>
       </c>
       <c r="F50">
-        <v>814.6079999999999</v>
+        <v>831.579</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5366,28 +5366,28 @@
         <v>198.7</v>
       </c>
       <c r="M50">
-        <v>47.0843424</v>
+        <v>48.0652662</v>
       </c>
       <c r="N50">
-        <v>151.6156576</v>
+        <v>150.6347338</v>
       </c>
       <c r="O50">
-        <v>39.1168396608</v>
+        <v>38.86376132040001</v>
       </c>
       <c r="P50">
-        <v>112.4988179392</v>
+        <v>111.7709724796</v>
       </c>
       <c r="Q50">
-        <v>265.5988179392</v>
+        <v>264.8709724796</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09799995607162784</v>
+        <v>0.09886675914916468</v>
       </c>
       <c r="T50">
-        <v>1.205541710661151</v>
+        <v>1.225560257486482</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.220086548346909</v>
+        <v>4.133962333074523</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5412,22 +5412,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07143697116607399</v>
+        <v>0.07132791717490149</v>
       </c>
       <c r="C51">
-        <v>923.4112898547576</v>
+        <v>907.6628757115625</v>
       </c>
       <c r="D51">
-        <v>1754.990289854758</v>
+        <v>1756.212875711562</v>
       </c>
       <c r="E51">
-        <v>831.579</v>
+        <v>848.55</v>
       </c>
       <c r="F51">
-        <v>831.579</v>
+        <v>848.55</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5448,28 +5448,28 @@
         <v>198.7</v>
       </c>
       <c r="M51">
-        <v>48.0652662</v>
+        <v>49.04619</v>
       </c>
       <c r="N51">
-        <v>150.6347338</v>
+        <v>149.65381</v>
       </c>
       <c r="O51">
-        <v>38.86376132040001</v>
+        <v>38.61068298000001</v>
       </c>
       <c r="P51">
-        <v>111.7709724796</v>
+        <v>111.04312702</v>
       </c>
       <c r="Q51">
-        <v>264.8709724796</v>
+        <v>264.14312702</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09886675914916468</v>
+        <v>0.09976823434980298</v>
       </c>
       <c r="T51">
-        <v>1.225560257486482</v>
+        <v>1.246379546184826</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5486,7 +5486,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.133962333074523</v>
+        <v>4.051283086413033</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5494,22 +5494,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07132791717490149</v>
+        <v>0.07254333318372899</v>
       </c>
       <c r="C52">
-        <v>907.6628757115625</v>
+        <v>877.1616097132603</v>
       </c>
       <c r="D52">
-        <v>1756.212875711562</v>
+        <v>1742.68260971326</v>
       </c>
       <c r="E52">
-        <v>848.55</v>
+        <v>865.521</v>
       </c>
       <c r="F52">
-        <v>848.55</v>
+        <v>865.521</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5530,45 +5530,45 @@
         <v>198.7</v>
       </c>
       <c r="M52">
-        <v>49.04619</v>
+        <v>53.0564373</v>
       </c>
       <c r="N52">
-        <v>149.65381</v>
+        <v>145.6435627</v>
       </c>
       <c r="O52">
-        <v>38.61068298000001</v>
+        <v>37.57603917660001</v>
       </c>
       <c r="P52">
-        <v>111.04312702</v>
+        <v>108.0675235234</v>
       </c>
       <c r="Q52">
-        <v>264.14312702</v>
+        <v>261.1675235234</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09976823434980298</v>
+        <v>0.1007065044565898</v>
       </c>
       <c r="T52">
-        <v>1.246379546184826</v>
+        <v>1.268048601768817</v>
       </c>
       <c r="U52">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V52">
         <v>0.258</v>
       </c>
       <c r="W52">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.051283086413033</v>
+        <v>3.745068649756474</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5576,22 +5576,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07254333318372899</v>
+        <v>0.07246024919255649</v>
       </c>
       <c r="C53">
-        <v>877.1616097132603</v>
+        <v>861.1088760317882</v>
       </c>
       <c r="D53">
-        <v>1742.68260971326</v>
+        <v>1743.600876031788</v>
       </c>
       <c r="E53">
-        <v>865.521</v>
+        <v>882.492</v>
       </c>
       <c r="F53">
-        <v>865.521</v>
+        <v>882.492</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5612,28 +5612,28 @@
         <v>198.7</v>
       </c>
       <c r="M53">
-        <v>53.0564373</v>
+        <v>54.0967596</v>
       </c>
       <c r="N53">
-        <v>145.6435627</v>
+        <v>144.6032404</v>
       </c>
       <c r="O53">
-        <v>37.57603917660001</v>
+        <v>37.3076360232</v>
       </c>
       <c r="P53">
-        <v>108.0675235234</v>
+        <v>107.2956043768</v>
       </c>
       <c r="Q53">
-        <v>261.1675235234</v>
+        <v>260.3956043768</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1007065044565898</v>
+        <v>0.1016838691511593</v>
       </c>
       <c r="T53">
-        <v>1.268048601768817</v>
+        <v>1.290620534668807</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5650,7 +5650,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.745068649756474</v>
+        <v>3.673048098799618</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5658,22 +5658,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07246024919255649</v>
+        <v>0.07237716520138399</v>
       </c>
       <c r="C54">
-        <v>861.1088760317882</v>
+        <v>845.0571105789229</v>
       </c>
       <c r="D54">
-        <v>1743.600876031788</v>
+        <v>1744.520110578923</v>
       </c>
       <c r="E54">
-        <v>882.492</v>
+        <v>899.463</v>
       </c>
       <c r="F54">
-        <v>882.492</v>
+        <v>899.463</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5694,28 +5694,28 @@
         <v>198.7</v>
       </c>
       <c r="M54">
-        <v>54.0967596</v>
+        <v>55.1370819</v>
       </c>
       <c r="N54">
-        <v>144.6032404</v>
+        <v>143.5629181</v>
       </c>
       <c r="O54">
-        <v>37.3076360232</v>
+        <v>37.0392328698</v>
       </c>
       <c r="P54">
-        <v>107.2956043768</v>
+        <v>106.5236852302</v>
       </c>
       <c r="Q54">
-        <v>260.3956043768</v>
+        <v>259.6236852302</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1016838691511593</v>
+        <v>0.1027028238327319</v>
       </c>
       <c r="T54">
-        <v>1.290620534668807</v>
+        <v>1.314152975351776</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.673048098799618</v>
+        <v>3.603745304482645</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5740,22 +5740,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07237716520138399</v>
+        <v>0.0722940812102115</v>
       </c>
       <c r="C55">
-        <v>845.0571105789229</v>
+        <v>829.006314886836</v>
       </c>
       <c r="D55">
-        <v>1744.520110578923</v>
+        <v>1745.440314886836</v>
       </c>
       <c r="E55">
-        <v>899.463</v>
+        <v>916.434</v>
       </c>
       <c r="F55">
-        <v>899.463</v>
+        <v>916.434</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5776,28 +5776,28 @@
         <v>198.7</v>
       </c>
       <c r="M55">
-        <v>55.1370819</v>
+        <v>56.1774042</v>
       </c>
       <c r="N55">
-        <v>143.5629181</v>
+        <v>142.5225958</v>
       </c>
       <c r="O55">
-        <v>37.0392328698</v>
+        <v>36.77082971640001</v>
       </c>
       <c r="P55">
-        <v>106.5236852302</v>
+        <v>105.7517660836</v>
       </c>
       <c r="Q55">
-        <v>259.6236852302</v>
+        <v>258.8517660836</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1027028238327319</v>
+        <v>0.1037660808917641</v>
       </c>
       <c r="T55">
-        <v>1.314152975351776</v>
+        <v>1.338708565629656</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.603745304482645</v>
+        <v>3.537009280325559</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5822,22 +5822,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0722940812102115</v>
+        <v>0.073353677219039</v>
       </c>
       <c r="C56">
-        <v>829.006314886836</v>
+        <v>800.3719338128005</v>
       </c>
       <c r="D56">
-        <v>1745.440314886836</v>
+        <v>1733.776933812801</v>
       </c>
       <c r="E56">
-        <v>916.434</v>
+        <v>933.405</v>
       </c>
       <c r="F56">
-        <v>916.434</v>
+        <v>933.405</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5858,45 +5858,45 @@
         <v>198.7</v>
       </c>
       <c r="M56">
-        <v>56.1774042</v>
+        <v>59.8312605</v>
       </c>
       <c r="N56">
-        <v>142.5225958</v>
+        <v>138.8687395</v>
       </c>
       <c r="O56">
-        <v>36.77082971640001</v>
+        <v>35.828134791</v>
       </c>
       <c r="P56">
-        <v>105.7517660836</v>
+        <v>103.040604709</v>
       </c>
       <c r="Q56">
-        <v>258.8517660836</v>
+        <v>256.140604709</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1037660808917641</v>
+        <v>0.1048765938200867</v>
       </c>
       <c r="T56">
-        <v>1.338708565629656</v>
+        <v>1.364355515475443</v>
       </c>
       <c r="U56">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V56">
         <v>0.258</v>
       </c>
       <c r="W56">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.537009280325559</v>
+        <v>3.321006416035644</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5904,22 +5904,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.073353677219039</v>
+        <v>0.0732913692278665</v>
       </c>
       <c r="C57">
-        <v>800.3719338128005</v>
+        <v>784.0824666777777</v>
       </c>
       <c r="D57">
-        <v>1733.776933812801</v>
+        <v>1734.458466677778</v>
       </c>
       <c r="E57">
-        <v>933.405</v>
+        <v>950.3760000000001</v>
       </c>
       <c r="F57">
-        <v>933.405</v>
+        <v>950.3760000000001</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5940,28 +5940,28 @@
         <v>198.7</v>
       </c>
       <c r="M57">
-        <v>59.8312605</v>
+        <v>60.91910160000001</v>
       </c>
       <c r="N57">
-        <v>138.8687395</v>
+        <v>137.7808984</v>
       </c>
       <c r="O57">
-        <v>35.828134791</v>
+        <v>35.5474717872</v>
       </c>
       <c r="P57">
-        <v>103.040604709</v>
+        <v>102.2334266128</v>
       </c>
       <c r="Q57">
-        <v>256.140604709</v>
+        <v>255.3334266128</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1048765938200867</v>
+        <v>0.1060375846087875</v>
       </c>
       <c r="T57">
-        <v>1.364355515475443</v>
+        <v>1.391168235768764</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.321006416035644</v>
+        <v>3.261702730035007</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5986,22 +5986,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0732913692278665</v>
+        <v>0.07322906123669401</v>
       </c>
       <c r="C58">
-        <v>784.0824666777777</v>
+        <v>767.7935355629251</v>
       </c>
       <c r="D58">
-        <v>1734.458466677778</v>
+        <v>1735.140535562925</v>
       </c>
       <c r="E58">
-        <v>950.3760000000001</v>
+        <v>967.3470000000001</v>
       </c>
       <c r="F58">
-        <v>950.3760000000001</v>
+        <v>967.3470000000001</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6022,28 +6022,28 @@
         <v>198.7</v>
       </c>
       <c r="M58">
-        <v>60.91910160000001</v>
+        <v>62.00694270000001</v>
       </c>
       <c r="N58">
-        <v>137.7808984</v>
+        <v>136.6930573</v>
       </c>
       <c r="O58">
-        <v>35.5474717872</v>
+        <v>35.26680878340001</v>
       </c>
       <c r="P58">
-        <v>102.2334266128</v>
+        <v>101.4262485166</v>
       </c>
       <c r="Q58">
-        <v>255.3334266128</v>
+        <v>254.5262485166</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1060375846087875</v>
+        <v>0.1072525749690558</v>
       </c>
       <c r="T58">
-        <v>1.391168235768764</v>
+        <v>1.419228059331543</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.261702730035007</v>
+        <v>3.204479875122113</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6068,22 +6068,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07322906123669401</v>
+        <v>0.07316675324552151</v>
       </c>
       <c r="C59">
-        <v>767.7935355629251</v>
+        <v>751.5051411008552</v>
       </c>
       <c r="D59">
-        <v>1735.140535562925</v>
+        <v>1735.823141100855</v>
       </c>
       <c r="E59">
-        <v>967.3470000000001</v>
+        <v>984.3180000000001</v>
       </c>
       <c r="F59">
-        <v>967.3470000000001</v>
+        <v>984.3180000000001</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6104,28 +6104,28 @@
         <v>198.7</v>
       </c>
       <c r="M59">
-        <v>62.00694270000001</v>
+        <v>63.09478380000001</v>
       </c>
       <c r="N59">
-        <v>136.6930573</v>
+        <v>135.6052162</v>
       </c>
       <c r="O59">
-        <v>35.26680878340001</v>
+        <v>34.9861457796</v>
       </c>
       <c r="P59">
-        <v>101.4262485166</v>
+        <v>100.6190704204</v>
       </c>
       <c r="Q59">
-        <v>254.5262485166</v>
+        <v>253.7190704204</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1072525749690558</v>
+        <v>0.1085254220131464</v>
       </c>
       <c r="T59">
-        <v>1.419228059331543</v>
+        <v>1.44862406496874</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.204479875122113</v>
+        <v>3.149230222102766</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6150,22 +6150,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07316675324552149</v>
+        <v>0.073104445254349</v>
       </c>
       <c r="C60">
-        <v>751.5051411008554</v>
+        <v>735.217283925176</v>
       </c>
       <c r="D60">
-        <v>1735.823141100855</v>
+        <v>1736.506283925176</v>
       </c>
       <c r="E60">
-        <v>984.3179999999999</v>
+        <v>1001.289</v>
       </c>
       <c r="F60">
-        <v>984.3179999999999</v>
+        <v>1001.289</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6186,28 +6186,28 @@
         <v>198.7</v>
       </c>
       <c r="M60">
-        <v>63.09478379999999</v>
+        <v>64.18262489999999</v>
       </c>
       <c r="N60">
-        <v>135.6052162</v>
+        <v>134.5173751</v>
       </c>
       <c r="O60">
-        <v>34.98614577960001</v>
+        <v>34.70548277580001</v>
       </c>
       <c r="P60">
-        <v>100.6190704204</v>
+        <v>99.81189232420003</v>
       </c>
       <c r="Q60">
-        <v>253.7190704204</v>
+        <v>252.9118923242</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1085254220131464</v>
+        <v>0.1098603591569488</v>
       </c>
       <c r="T60">
-        <v>1.44862406496874</v>
+        <v>1.479454022100434</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.149230222102767</v>
+        <v>3.095853438677296</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6232,22 +6232,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.073104445254349</v>
+        <v>0.0730421372631765</v>
       </c>
       <c r="C61">
-        <v>735.217283925176</v>
+        <v>718.929964670493</v>
       </c>
       <c r="D61">
-        <v>1736.506283925176</v>
+        <v>1737.189964670493</v>
       </c>
       <c r="E61">
-        <v>1001.289</v>
+        <v>1018.26</v>
       </c>
       <c r="F61">
-        <v>1001.289</v>
+        <v>1018.26</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6268,28 +6268,28 @@
         <v>198.7</v>
       </c>
       <c r="M61">
-        <v>64.18262489999999</v>
+        <v>65.270466</v>
       </c>
       <c r="N61">
-        <v>134.5173751</v>
+        <v>133.429534</v>
       </c>
       <c r="O61">
-        <v>34.70548277580001</v>
+        <v>34.42481977200001</v>
       </c>
       <c r="P61">
-        <v>99.81189232420003</v>
+        <v>99.00471422800001</v>
       </c>
       <c r="Q61">
-        <v>252.9118923242</v>
+        <v>252.104714228</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1098603591569488</v>
+        <v>0.1112620431579412</v>
       </c>
       <c r="T61">
-        <v>1.479454022100434</v>
+        <v>1.511825477088713</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.095853438677296</v>
+        <v>3.044255881366007</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6314,22 +6314,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0730421372631765</v>
+        <v>0.076510265272004</v>
       </c>
       <c r="C62">
-        <v>718.929964670493</v>
+        <v>664.7059710400335</v>
       </c>
       <c r="D62">
-        <v>1737.189964670493</v>
+        <v>1699.936971040034</v>
       </c>
       <c r="E62">
-        <v>1018.26</v>
+        <v>1035.231</v>
       </c>
       <c r="F62">
-        <v>1018.26</v>
+        <v>1035.231</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6350,45 +6350,45 @@
         <v>198.7</v>
       </c>
       <c r="M62">
-        <v>65.270466</v>
+        <v>74.43310890000001</v>
       </c>
       <c r="N62">
-        <v>133.429534</v>
+        <v>124.2668911</v>
       </c>
       <c r="O62">
-        <v>34.42481977200001</v>
+        <v>32.06085790380001</v>
       </c>
       <c r="P62">
-        <v>99.00471422800001</v>
+        <v>92.2060331962</v>
       </c>
       <c r="Q62">
-        <v>252.104714228</v>
+        <v>245.3060331962</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1112620431579412</v>
+        <v>0.1127356083897539</v>
       </c>
       <c r="T62">
-        <v>1.511825477088713</v>
+        <v>1.545857006691775</v>
       </c>
       <c r="U62">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V62">
         <v>0.258</v>
       </c>
       <c r="W62">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.044255881366007</v>
+        <v>2.669510960061484</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6396,22 +6396,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.076510265272004</v>
+        <v>0.07650583328083152</v>
       </c>
       <c r="C63">
-        <v>664.7059710400335</v>
+        <v>647.7815577836873</v>
       </c>
       <c r="D63">
-        <v>1699.936971040034</v>
+        <v>1699.983557783687</v>
       </c>
       <c r="E63">
-        <v>1035.231</v>
+        <v>1052.202</v>
       </c>
       <c r="F63">
-        <v>1035.231</v>
+        <v>1052.202</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6432,28 +6432,28 @@
         <v>198.7</v>
       </c>
       <c r="M63">
-        <v>74.43310890000001</v>
+        <v>75.65332380000001</v>
       </c>
       <c r="N63">
-        <v>124.2668911</v>
+        <v>123.0466762</v>
       </c>
       <c r="O63">
-        <v>32.06085790380001</v>
+        <v>31.7460424596</v>
       </c>
       <c r="P63">
-        <v>92.2060331962</v>
+        <v>91.3006337404</v>
       </c>
       <c r="Q63">
-        <v>245.3060331962</v>
+        <v>244.4006337404</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1127356083897539</v>
+        <v>0.1142867296863987</v>
       </c>
       <c r="T63">
-        <v>1.545857006691775</v>
+        <v>1.581679669431841</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.669510960061484</v>
+        <v>2.626454331673395</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6478,22 +6478,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07650583328083152</v>
+        <v>0.07650140128965902</v>
       </c>
       <c r="C64">
-        <v>647.7815577836873</v>
+        <v>630.8571470808292</v>
       </c>
       <c r="D64">
-        <v>1699.983557783687</v>
+        <v>1700.030147080829</v>
       </c>
       <c r="E64">
-        <v>1052.202</v>
+        <v>1069.173</v>
       </c>
       <c r="F64">
-        <v>1052.202</v>
+        <v>1069.173</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6514,28 +6514,28 @@
         <v>198.7</v>
       </c>
       <c r="M64">
-        <v>75.65332380000001</v>
+        <v>76.87353870000001</v>
       </c>
       <c r="N64">
-        <v>123.0466762</v>
+        <v>121.8264613</v>
       </c>
       <c r="O64">
-        <v>31.7460424596</v>
+        <v>31.4312270154</v>
       </c>
       <c r="P64">
-        <v>91.3006337404</v>
+        <v>90.39523428460001</v>
       </c>
       <c r="Q64">
-        <v>244.4006337404</v>
+        <v>243.4952342846</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1142867296863987</v>
+        <v>0.1159216953774568</v>
       </c>
       <c r="T64">
-        <v>1.581679669431841</v>
+        <v>1.619438692320018</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6552,7 +6552,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.626454331673395</v>
+        <v>2.584764580376993</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6560,22 +6560,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07650140128965902</v>
+        <v>0.07649696929848651</v>
       </c>
       <c r="C65">
-        <v>630.8571470808292</v>
+        <v>613.9327389316688</v>
       </c>
       <c r="D65">
-        <v>1700.030147080829</v>
+        <v>1700.076738931669</v>
       </c>
       <c r="E65">
-        <v>1069.173</v>
+        <v>1086.144</v>
       </c>
       <c r="F65">
-        <v>1069.173</v>
+        <v>1086.144</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6596,28 +6596,28 @@
         <v>198.7</v>
       </c>
       <c r="M65">
-        <v>76.87353870000001</v>
+        <v>78.0937536</v>
       </c>
       <c r="N65">
-        <v>121.8264613</v>
+        <v>120.6062464</v>
       </c>
       <c r="O65">
-        <v>31.4312270154</v>
+        <v>31.1164115712</v>
       </c>
       <c r="P65">
-        <v>90.39523428460001</v>
+        <v>89.48983482880001</v>
       </c>
       <c r="Q65">
-        <v>243.4952342846</v>
+        <v>242.5898348288</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1159216953774568</v>
+        <v>0.1176474924957959</v>
       </c>
       <c r="T65">
-        <v>1.619438692320018</v>
+        <v>1.659295438701983</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6634,7 +6634,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.584764580376993</v>
+        <v>2.544377633808602</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6642,22 +6642,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07649696929848651</v>
+        <v>0.07649253730731402</v>
       </c>
       <c r="C66">
-        <v>613.9327389316688</v>
+        <v>597.0083333364159</v>
       </c>
       <c r="D66">
-        <v>1700.076738931669</v>
+        <v>1700.123333336416</v>
       </c>
       <c r="E66">
-        <v>1086.144</v>
+        <v>1103.115</v>
       </c>
       <c r="F66">
-        <v>1086.144</v>
+        <v>1103.115</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6678,28 +6678,28 @@
         <v>198.7</v>
       </c>
       <c r="M66">
-        <v>78.0937536</v>
+        <v>79.3139685</v>
       </c>
       <c r="N66">
-        <v>120.6062464</v>
+        <v>119.3860315</v>
       </c>
       <c r="O66">
-        <v>31.1164115712</v>
+        <v>30.801596127</v>
       </c>
       <c r="P66">
-        <v>89.48983482880001</v>
+        <v>88.58443537300002</v>
       </c>
       <c r="Q66">
-        <v>242.5898348288</v>
+        <v>241.684435373</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1176474924957959</v>
+        <v>0.1194719065923258</v>
       </c>
       <c r="T66">
-        <v>1.659295438701983</v>
+        <v>1.701429713448632</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.544377633808602</v>
+        <v>2.505233362519239</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6724,22 +6724,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07649253730731402</v>
+        <v>0.07839801331614152</v>
       </c>
       <c r="C67">
-        <v>597.0083333364159</v>
+        <v>560.2374455835961</v>
       </c>
       <c r="D67">
-        <v>1700.123333336416</v>
+        <v>1680.323445583596</v>
       </c>
       <c r="E67">
-        <v>1103.115</v>
+        <v>1120.086</v>
       </c>
       <c r="F67">
-        <v>1103.115</v>
+        <v>1120.086</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6760,45 +6760,45 @@
         <v>198.7</v>
       </c>
       <c r="M67">
-        <v>79.3139685</v>
+        <v>84.90251880000001</v>
       </c>
       <c r="N67">
-        <v>119.3860315</v>
+        <v>113.7974812</v>
       </c>
       <c r="O67">
-        <v>30.801596127</v>
+        <v>29.3597501496</v>
       </c>
       <c r="P67">
-        <v>88.58443537300002</v>
+        <v>84.4377310504</v>
       </c>
       <c r="Q67">
-        <v>241.684435373</v>
+        <v>237.5377310504</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1194719065923258</v>
+        <v>0.1214036391651221</v>
       </c>
       <c r="T67">
-        <v>1.701429713448632</v>
+        <v>1.746042474945084</v>
       </c>
       <c r="U67">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V67">
         <v>0.258</v>
       </c>
       <c r="W67">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.505233362519239</v>
+        <v>2.340331038565136</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6806,22 +6806,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07839801331614152</v>
+        <v>0.07842251932496902</v>
       </c>
       <c r="C68">
-        <v>560.2374455835961</v>
+        <v>543.0148058338443</v>
       </c>
       <c r="D68">
-        <v>1680.323445583596</v>
+        <v>1680.071805833844</v>
       </c>
       <c r="E68">
-        <v>1120.086</v>
+        <v>1137.057</v>
       </c>
       <c r="F68">
-        <v>1120.086</v>
+        <v>1137.057</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6842,28 +6842,28 @@
         <v>198.7</v>
       </c>
       <c r="M68">
-        <v>84.90251880000001</v>
+        <v>86.1889206</v>
       </c>
       <c r="N68">
-        <v>113.7974812</v>
+        <v>112.5110794</v>
       </c>
       <c r="O68">
-        <v>29.3597501496</v>
+        <v>29.0278584852</v>
       </c>
       <c r="P68">
-        <v>84.4377310504</v>
+        <v>83.48322091480001</v>
       </c>
       <c r="Q68">
-        <v>237.5377310504</v>
+        <v>236.5832209148</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1214036391651221</v>
+        <v>0.1234524464393001</v>
       </c>
       <c r="T68">
-        <v>1.746042474945084</v>
+        <v>1.793359040168593</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.340331038565136</v>
+        <v>2.305400724556701</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6888,22 +6888,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07842251932496902</v>
+        <v>0.07844702533379652</v>
       </c>
       <c r="C69">
-        <v>543.0148058338443</v>
+        <v>525.7922414423008</v>
       </c>
       <c r="D69">
-        <v>1680.071805833844</v>
+        <v>1679.820241442301</v>
       </c>
       <c r="E69">
-        <v>1137.057</v>
+        <v>1154.028</v>
       </c>
       <c r="F69">
-        <v>1137.057</v>
+        <v>1154.028</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6924,28 +6924,28 @@
         <v>198.7</v>
       </c>
       <c r="M69">
-        <v>86.1889206</v>
+        <v>87.47532240000001</v>
       </c>
       <c r="N69">
-        <v>112.5110794</v>
+        <v>111.2246776</v>
       </c>
       <c r="O69">
-        <v>29.0278584852</v>
+        <v>28.6959668208</v>
       </c>
       <c r="P69">
-        <v>83.48322091480001</v>
+        <v>82.5287107792</v>
       </c>
       <c r="Q69">
-        <v>236.5832209148</v>
+        <v>235.6287107792</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1234524464393001</v>
+        <v>0.1256293041681141</v>
       </c>
       <c r="T69">
-        <v>1.793359040168593</v>
+        <v>1.843632890718572</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6962,7 +6962,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.305400724556701</v>
+        <v>2.271497772724985</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6970,22 +6970,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07844702533379652</v>
+        <v>0.07847153134262402</v>
       </c>
       <c r="C70">
-        <v>525.7922414423008</v>
+        <v>508.5697523751196</v>
       </c>
       <c r="D70">
-        <v>1679.820241442301</v>
+        <v>1679.56875237512</v>
       </c>
       <c r="E70">
-        <v>1154.028</v>
+        <v>1170.999</v>
       </c>
       <c r="F70">
-        <v>1154.028</v>
+        <v>1170.999</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7006,28 +7006,28 @@
         <v>198.7</v>
       </c>
       <c r="M70">
-        <v>87.47532240000001</v>
+        <v>88.7617242</v>
       </c>
       <c r="N70">
-        <v>111.2246776</v>
+        <v>109.9382758</v>
       </c>
       <c r="O70">
-        <v>28.6959668208</v>
+        <v>28.36407515640001</v>
       </c>
       <c r="P70">
-        <v>82.5287107792</v>
+        <v>81.57420064360001</v>
       </c>
       <c r="Q70">
-        <v>235.6287107792</v>
+        <v>234.6742006436</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1256293041681141</v>
+        <v>0.1279466043310452</v>
       </c>
       <c r="T70">
-        <v>1.843632890718572</v>
+        <v>1.897150215497581</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.271497772724985</v>
+        <v>2.238577515149261</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7052,22 +7052,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07847153134262402</v>
+        <v>0.07849603735145153</v>
       </c>
       <c r="C71">
-        <v>508.5697523751196</v>
+        <v>491.3473385984748</v>
       </c>
       <c r="D71">
-        <v>1679.56875237512</v>
+        <v>1679.317338598475</v>
       </c>
       <c r="E71">
-        <v>1170.999</v>
+        <v>1187.97</v>
       </c>
       <c r="F71">
-        <v>1170.999</v>
+        <v>1187.97</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7088,28 +7088,28 @@
         <v>198.7</v>
       </c>
       <c r="M71">
-        <v>88.7617242</v>
+        <v>90.04812600000001</v>
       </c>
       <c r="N71">
-        <v>109.9382758</v>
+        <v>108.651874</v>
       </c>
       <c r="O71">
-        <v>28.36407515640001</v>
+        <v>28.032183492</v>
       </c>
       <c r="P71">
-        <v>81.57420064360001</v>
+        <v>80.61969050800001</v>
       </c>
       <c r="Q71">
-        <v>234.6742006436</v>
+        <v>233.719690508</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1279466043310452</v>
+        <v>0.1304183911715051</v>
       </c>
       <c r="T71">
-        <v>1.897150215497581</v>
+        <v>1.954235361928524</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.238577515149261</v>
+        <v>2.206597836361414</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7134,22 +7134,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07849603735145153</v>
+        <v>0.07852054336027903</v>
       </c>
       <c r="C72">
-        <v>491.3473385984748</v>
+        <v>474.125000078561</v>
       </c>
       <c r="D72">
-        <v>1679.317338598475</v>
+        <v>1679.066000078561</v>
       </c>
       <c r="E72">
-        <v>1187.97</v>
+        <v>1204.941</v>
       </c>
       <c r="F72">
-        <v>1187.97</v>
+        <v>1204.941</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7170,28 +7170,28 @@
         <v>198.7</v>
       </c>
       <c r="M72">
-        <v>90.04812600000001</v>
+        <v>91.3345278</v>
       </c>
       <c r="N72">
-        <v>108.651874</v>
+        <v>107.3654722</v>
       </c>
       <c r="O72">
-        <v>28.032183492</v>
+        <v>27.7002918276</v>
       </c>
       <c r="P72">
-        <v>80.61969050800001</v>
+        <v>79.66518037240002</v>
       </c>
       <c r="Q72">
-        <v>233.719690508</v>
+        <v>232.7651803724</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1304183911715051</v>
+        <v>0.1330606460699277</v>
       </c>
       <c r="T72">
-        <v>1.954235361928524</v>
+        <v>2.015257415009878</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7208,7 +7208,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.206597836361414</v>
+        <v>2.175518993595761</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7216,22 +7216,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07852054336027903</v>
+        <v>0.07854504936910653</v>
       </c>
       <c r="C73">
-        <v>474.1250000785612</v>
+        <v>456.9027367815929</v>
       </c>
       <c r="D73">
-        <v>1679.066000078561</v>
+        <v>1678.814736781593</v>
       </c>
       <c r="E73">
-        <v>1204.941</v>
+        <v>1221.912</v>
       </c>
       <c r="F73">
-        <v>1204.941</v>
+        <v>1221.912</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7252,28 +7252,28 @@
         <v>198.7</v>
       </c>
       <c r="M73">
-        <v>91.33452779999999</v>
+        <v>92.6209296</v>
       </c>
       <c r="N73">
-        <v>107.3654722</v>
+        <v>106.0790704</v>
       </c>
       <c r="O73">
-        <v>27.70029182760001</v>
+        <v>27.36840016320001</v>
       </c>
       <c r="P73">
-        <v>79.66518037240002</v>
+        <v>78.71067023680001</v>
       </c>
       <c r="Q73">
-        <v>232.7651803724</v>
+        <v>231.8106702368</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1330606460699277</v>
+        <v>0.1358916334610947</v>
       </c>
       <c r="T73">
-        <v>2.015257415009877</v>
+        <v>2.08063818616847</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.175518993595761</v>
+        <v>2.145303452018042</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7298,22 +7298,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07854504936910653</v>
+        <v>0.07856955537793403</v>
       </c>
       <c r="C74">
-        <v>456.9027367815929</v>
+        <v>439.6805486738051</v>
       </c>
       <c r="D74">
-        <v>1678.814736781593</v>
+        <v>1678.563548673805</v>
       </c>
       <c r="E74">
-        <v>1221.912</v>
+        <v>1238.883</v>
       </c>
       <c r="F74">
-        <v>1221.912</v>
+        <v>1238.883</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7334,28 +7334,28 @@
         <v>198.7</v>
       </c>
       <c r="M74">
-        <v>92.6209296</v>
+        <v>93.90733139999999</v>
       </c>
       <c r="N74">
-        <v>106.0790704</v>
+        <v>104.7926686</v>
       </c>
       <c r="O74">
-        <v>27.36840016320001</v>
+        <v>27.03650849880001</v>
       </c>
       <c r="P74">
-        <v>78.71067023680001</v>
+        <v>77.75616010120002</v>
       </c>
       <c r="Q74">
-        <v>231.8106702368</v>
+        <v>230.8561601012</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1358916334610947</v>
+        <v>0.1389323236219779</v>
       </c>
       <c r="T74">
-        <v>2.08063818616847</v>
+        <v>2.150861977412884</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.145303452018042</v>
+        <v>2.115915733497247</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7380,22 +7380,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07856955537793403</v>
+        <v>0.07859406138676153</v>
       </c>
       <c r="C75">
-        <v>439.6805486738051</v>
+        <v>422.4584357214528</v>
       </c>
       <c r="D75">
-        <v>1678.563548673805</v>
+        <v>1678.312435721453</v>
       </c>
       <c r="E75">
-        <v>1238.883</v>
+        <v>1255.854</v>
       </c>
       <c r="F75">
-        <v>1238.883</v>
+        <v>1255.854</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7416,28 +7416,28 @@
         <v>198.7</v>
       </c>
       <c r="M75">
-        <v>93.90733139999999</v>
+        <v>95.1937332</v>
       </c>
       <c r="N75">
-        <v>104.7926686</v>
+        <v>103.5062668</v>
       </c>
       <c r="O75">
-        <v>27.03650849880001</v>
+        <v>26.70461683440001</v>
       </c>
       <c r="P75">
-        <v>77.75616010120002</v>
+        <v>76.80164996560001</v>
       </c>
       <c r="Q75">
-        <v>230.8561601012</v>
+        <v>229.9016499656</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1389323236219779</v>
+        <v>0.1422069130260059</v>
       </c>
       <c r="T75">
-        <v>2.150861977412884</v>
+        <v>2.226487598753023</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.115915733497247</v>
+        <v>2.087322277639176</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7462,22 +7462,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07859406138676153</v>
+        <v>0.07861856739558903</v>
       </c>
       <c r="C76">
-        <v>422.4584357214528</v>
+        <v>405.2363978908115</v>
       </c>
       <c r="D76">
-        <v>1678.312435721453</v>
+        <v>1678.061397890811</v>
       </c>
       <c r="E76">
-        <v>1255.854</v>
+        <v>1272.825</v>
       </c>
       <c r="F76">
-        <v>1255.854</v>
+        <v>1272.825</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7498,28 +7498,28 @@
         <v>198.7</v>
       </c>
       <c r="M76">
-        <v>95.1937332</v>
+        <v>96.48013499999999</v>
       </c>
       <c r="N76">
-        <v>103.5062668</v>
+        <v>102.219865</v>
       </c>
       <c r="O76">
-        <v>26.70461683440001</v>
+        <v>26.37272517000001</v>
       </c>
       <c r="P76">
-        <v>76.80164996560001</v>
+        <v>75.84713983000002</v>
       </c>
       <c r="Q76">
-        <v>229.9016499656</v>
+        <v>228.94713983</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1422069130260059</v>
+        <v>0.1457434695823561</v>
       </c>
       <c r="T76">
-        <v>2.226487598753023</v>
+        <v>2.308163269800373</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.087322277639176</v>
+        <v>2.05949131393732</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7544,22 +7544,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07861856739558903</v>
+        <v>0.07864307340441654</v>
       </c>
       <c r="C77">
-        <v>405.2363978908115</v>
+        <v>388.0144351481763</v>
       </c>
       <c r="D77">
-        <v>1678.061397890811</v>
+        <v>1677.810435148176</v>
       </c>
       <c r="E77">
-        <v>1272.825</v>
+        <v>1289.796</v>
       </c>
       <c r="F77">
-        <v>1272.825</v>
+        <v>1289.796</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7580,28 +7580,28 @@
         <v>198.7</v>
       </c>
       <c r="M77">
-        <v>96.48013499999999</v>
+        <v>97.76653680000001</v>
       </c>
       <c r="N77">
-        <v>102.219865</v>
+        <v>100.9334632</v>
       </c>
       <c r="O77">
-        <v>26.37272517000001</v>
+        <v>26.0408335056</v>
       </c>
       <c r="P77">
-        <v>75.84713983000002</v>
+        <v>74.8926296944</v>
       </c>
       <c r="Q77">
-        <v>228.94713983</v>
+        <v>227.9926296944</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1457434695823561</v>
+        <v>0.1495747391850689</v>
       </c>
       <c r="T77">
-        <v>2.308163269800373</v>
+        <v>2.396645246768335</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.05949131393732</v>
+        <v>2.032392744017092</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7626,22 +7626,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07864307340441654</v>
+        <v>0.07866757941324404</v>
       </c>
       <c r="C78">
-        <v>388.0144351481763</v>
+        <v>370.7925474598635</v>
       </c>
       <c r="D78">
-        <v>1677.810435148176</v>
+        <v>1677.559547459864</v>
       </c>
       <c r="E78">
-        <v>1289.796</v>
+        <v>1306.767</v>
       </c>
       <c r="F78">
-        <v>1289.796</v>
+        <v>1306.767</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7662,28 +7662,28 @@
         <v>198.7</v>
       </c>
       <c r="M78">
-        <v>97.76653680000001</v>
+        <v>99.05293860000002</v>
       </c>
       <c r="N78">
-        <v>100.9334632</v>
+        <v>99.6470614</v>
       </c>
       <c r="O78">
-        <v>26.0408335056</v>
+        <v>25.7089418412</v>
       </c>
       <c r="P78">
-        <v>74.8926296944</v>
+        <v>73.9381195588</v>
       </c>
       <c r="Q78">
-        <v>227.9926296944</v>
+        <v>227.0381195588</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1495747391850689</v>
+        <v>0.1537391626662784</v>
       </c>
       <c r="T78">
-        <v>2.396645246768335</v>
+        <v>2.492821308690033</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.032392744017092</v>
+        <v>2.005998033055831</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7708,22 +7708,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07866757941324404</v>
+        <v>0.08691047742207153</v>
       </c>
       <c r="C79">
-        <v>370.7925474598635</v>
+        <v>273.4856708108143</v>
       </c>
       <c r="D79">
-        <v>1677.559547459864</v>
+        <v>1597.223670810814</v>
       </c>
       <c r="E79">
-        <v>1306.767</v>
+        <v>1323.738</v>
       </c>
       <c r="F79">
-        <v>1306.767</v>
+        <v>1323.738</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7744,45 +7744,45 @@
         <v>198.7</v>
       </c>
       <c r="M79">
-        <v>99.05293860000002</v>
+        <v>119.13642</v>
       </c>
       <c r="N79">
-        <v>99.6470614</v>
+        <v>79.56358000000002</v>
       </c>
       <c r="O79">
-        <v>25.7089418412</v>
+        <v>20.52740364000001</v>
       </c>
       <c r="P79">
-        <v>73.9381195588</v>
+        <v>59.03617636000001</v>
       </c>
       <c r="Q79">
-        <v>227.0381195588</v>
+        <v>212.13617636</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1537391626662784</v>
+        <v>0.1582821701003252</v>
       </c>
       <c r="T79">
-        <v>2.492821308690033</v>
+        <v>2.597740648968249</v>
       </c>
       <c r="U79">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V79">
         <v>0.258</v>
       </c>
       <c r="W79">
-        <v>0.0562436</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.005998033055831</v>
+        <v>1.667835914491975</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7790,22 +7790,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08691047742207153</v>
+        <v>0.08704034743089903</v>
       </c>
       <c r="C80">
-        <v>273.4856708108143</v>
+        <v>255.3104705383146</v>
       </c>
       <c r="D80">
-        <v>1597.223670810814</v>
+        <v>1596.019470538315</v>
       </c>
       <c r="E80">
-        <v>1323.738</v>
+        <v>1340.709</v>
       </c>
       <c r="F80">
-        <v>1323.738</v>
+        <v>1340.709</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7826,28 +7826,28 @@
         <v>198.7</v>
       </c>
       <c r="M80">
-        <v>119.13642</v>
+        <v>120.66381</v>
       </c>
       <c r="N80">
-        <v>79.56358000000002</v>
+        <v>78.03619000000002</v>
       </c>
       <c r="O80">
-        <v>20.52740364000001</v>
+        <v>20.13333702000001</v>
       </c>
       <c r="P80">
-        <v>59.03617636000001</v>
+        <v>57.90285298000001</v>
       </c>
       <c r="Q80">
-        <v>212.13617636</v>
+        <v>211.00285298</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1582821701003252</v>
+        <v>0.1632578449090431</v>
       </c>
       <c r="T80">
-        <v>2.597740648968249</v>
+        <v>2.712652307368201</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7864,7 +7864,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.667835914491975</v>
+        <v>1.646724067473089</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7872,22 +7872,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08704034743089903</v>
+        <v>0.08717021743972653</v>
       </c>
       <c r="C81">
-        <v>255.3104705383146</v>
+        <v>237.1370846714851</v>
       </c>
       <c r="D81">
-        <v>1596.019470538315</v>
+        <v>1594.817084671485</v>
       </c>
       <c r="E81">
-        <v>1340.709</v>
+        <v>1357.68</v>
       </c>
       <c r="F81">
-        <v>1340.709</v>
+        <v>1357.68</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7908,28 +7908,28 @@
         <v>198.7</v>
       </c>
       <c r="M81">
-        <v>120.66381</v>
+        <v>122.1912</v>
       </c>
       <c r="N81">
-        <v>78.03619000000002</v>
+        <v>76.50880000000002</v>
       </c>
       <c r="O81">
-        <v>20.13333702000001</v>
+        <v>19.73927040000001</v>
       </c>
       <c r="P81">
-        <v>57.90285298000001</v>
+        <v>56.76952960000001</v>
       </c>
       <c r="Q81">
-        <v>211.00285298</v>
+        <v>209.8695296</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1632578449090431</v>
+        <v>0.1687310871986327</v>
       </c>
       <c r="T81">
-        <v>2.712652307368201</v>
+        <v>2.839055131608146</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7946,7 +7946,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.646724067473089</v>
+        <v>1.626140016629676</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7954,22 +7954,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08717021743972653</v>
+        <v>0.08730008744855404</v>
       </c>
       <c r="C82">
-        <v>237.1370846714851</v>
+        <v>218.9655091126808</v>
       </c>
       <c r="D82">
-        <v>1594.817084671485</v>
+        <v>1593.616509112681</v>
       </c>
       <c r="E82">
-        <v>1357.68</v>
+        <v>1374.651</v>
       </c>
       <c r="F82">
-        <v>1357.68</v>
+        <v>1374.651</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -7990,28 +7990,28 @@
         <v>198.7</v>
       </c>
       <c r="M82">
-        <v>122.1912</v>
+        <v>123.71859</v>
       </c>
       <c r="N82">
-        <v>76.50880000000002</v>
+        <v>74.98141000000001</v>
       </c>
       <c r="O82">
-        <v>19.73927040000001</v>
+        <v>19.34520378</v>
       </c>
       <c r="P82">
-        <v>56.76952960000001</v>
+        <v>55.63620622000001</v>
       </c>
       <c r="Q82">
-        <v>209.8695296</v>
+        <v>208.73620622</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1687310871986327</v>
+        <v>0.1747804602555476</v>
       </c>
       <c r="T82">
-        <v>2.839055131608146</v>
+        <v>2.978763516294403</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.626140016629676</v>
+        <v>1.606064213955235</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8036,22 +8036,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08730008744855404</v>
+        <v>0.08742995745738154</v>
       </c>
       <c r="C83">
-        <v>218.9655091126808</v>
+        <v>200.7957397765879</v>
       </c>
       <c r="D83">
-        <v>1593.616509112681</v>
+        <v>1592.417739776588</v>
       </c>
       <c r="E83">
-        <v>1374.651</v>
+        <v>1391.622</v>
       </c>
       <c r="F83">
-        <v>1374.651</v>
+        <v>1391.622</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8072,28 +8072,28 @@
         <v>198.7</v>
       </c>
       <c r="M83">
-        <v>123.71859</v>
+        <v>125.24598</v>
       </c>
       <c r="N83">
-        <v>74.98141000000001</v>
+        <v>73.45402000000001</v>
       </c>
       <c r="O83">
-        <v>19.34520378</v>
+        <v>18.95113716000001</v>
       </c>
       <c r="P83">
-        <v>55.63620622000001</v>
+        <v>54.50288284000001</v>
       </c>
       <c r="Q83">
-        <v>208.73620622</v>
+        <v>207.60288284</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1747804602555476</v>
+        <v>0.181501985874342</v>
       </c>
       <c r="T83">
-        <v>2.978763516294403</v>
+        <v>3.133995054834688</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.606064213955235</v>
+        <v>1.586478065004562</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8118,22 +8118,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08742995745738154</v>
+        <v>0.08755982746620905</v>
       </c>
       <c r="C84">
-        <v>200.7957397765879</v>
+        <v>182.6277725901737</v>
       </c>
       <c r="D84">
-        <v>1592.417739776588</v>
+        <v>1591.220772590174</v>
       </c>
       <c r="E84">
-        <v>1391.622</v>
+        <v>1408.593</v>
       </c>
       <c r="F84">
-        <v>1391.622</v>
+        <v>1408.593</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8154,28 +8154,28 @@
         <v>198.7</v>
       </c>
       <c r="M84">
-        <v>125.24598</v>
+        <v>126.77337</v>
       </c>
       <c r="N84">
-        <v>73.45402000000001</v>
+        <v>71.92663000000002</v>
       </c>
       <c r="O84">
-        <v>18.95113716000001</v>
+        <v>18.55707054000001</v>
       </c>
       <c r="P84">
-        <v>54.50288284000001</v>
+        <v>53.36955946000001</v>
       </c>
       <c r="Q84">
-        <v>207.60288284</v>
+        <v>206.46955946</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.181501985874342</v>
+        <v>0.1890142792129945</v>
       </c>
       <c r="T84">
-        <v>3.133995054834688</v>
+        <v>3.307489127320888</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.586478065004562</v>
+        <v>1.56736387145029</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8200,22 +8200,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08755982746620905</v>
+        <v>0.08768969747503655</v>
       </c>
       <c r="C85">
-        <v>182.6277725901737</v>
+        <v>164.4616034926441</v>
       </c>
       <c r="D85">
-        <v>1591.220772590174</v>
+        <v>1590.025603492644</v>
       </c>
       <c r="E85">
-        <v>1408.593</v>
+        <v>1425.564</v>
       </c>
       <c r="F85">
-        <v>1408.593</v>
+        <v>1425.564</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8236,28 +8236,28 @@
         <v>198.7</v>
       </c>
       <c r="M85">
-        <v>126.77337</v>
+        <v>128.30076</v>
       </c>
       <c r="N85">
-        <v>71.92663000000002</v>
+        <v>70.39924000000002</v>
       </c>
       <c r="O85">
-        <v>18.55707054000001</v>
+        <v>18.16300392</v>
       </c>
       <c r="P85">
-        <v>53.36955946000001</v>
+        <v>52.23623608000001</v>
       </c>
       <c r="Q85">
-        <v>206.46955946</v>
+        <v>205.33623608</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1890142792129945</v>
+        <v>0.1974656092189785</v>
       </c>
       <c r="T85">
-        <v>3.307489127320888</v>
+        <v>3.502669958867864</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8274,7 +8274,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.56736387145029</v>
+        <v>1.548704777742548</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8282,22 +8282,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08768969747503655</v>
+        <v>0.08781956748386405</v>
       </c>
       <c r="C86">
-        <v>164.4616034926444</v>
+        <v>146.2972284353957</v>
       </c>
       <c r="D86">
-        <v>1590.025603492644</v>
+        <v>1588.832228435396</v>
       </c>
       <c r="E86">
-        <v>1425.564</v>
+        <v>1442.535</v>
       </c>
       <c r="F86">
-        <v>1425.564</v>
+        <v>1442.535</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8318,28 +8318,28 @@
         <v>198.7</v>
       </c>
       <c r="M86">
-        <v>128.30076</v>
+        <v>129.82815</v>
       </c>
       <c r="N86">
-        <v>70.39924000000005</v>
+        <v>68.87185000000002</v>
       </c>
       <c r="O86">
-        <v>18.16300392000001</v>
+        <v>17.76893730000001</v>
       </c>
       <c r="P86">
-        <v>52.23623608000004</v>
+        <v>51.10291270000002</v>
       </c>
       <c r="Q86">
-        <v>205.33623608</v>
+        <v>204.2029127</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1974656092189784</v>
+        <v>0.2070437832257603</v>
       </c>
       <c r="T86">
-        <v>3.502669958867862</v>
+        <v>3.723874901287768</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8356,7 +8356,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.548704777742548</v>
+        <v>1.530484721533812</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8364,22 +8364,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08781956748386405</v>
+        <v>0.08794943749269155</v>
       </c>
       <c r="C87">
-        <v>146.2972284353957</v>
+        <v>128.1346433819699</v>
       </c>
       <c r="D87">
-        <v>1588.832228435396</v>
+        <v>1587.64064338197</v>
       </c>
       <c r="E87">
-        <v>1442.535</v>
+        <v>1459.506</v>
       </c>
       <c r="F87">
-        <v>1442.535</v>
+        <v>1459.506</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8400,28 +8400,28 @@
         <v>198.7</v>
       </c>
       <c r="M87">
-        <v>129.82815</v>
+        <v>131.35554</v>
       </c>
       <c r="N87">
-        <v>68.87185000000002</v>
+        <v>67.34446000000003</v>
       </c>
       <c r="O87">
-        <v>17.76893730000001</v>
+        <v>17.37487068000001</v>
       </c>
       <c r="P87">
-        <v>51.10291270000002</v>
+        <v>49.96958932000002</v>
       </c>
       <c r="Q87">
-        <v>204.2029127</v>
+        <v>203.06958932</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2070437832257603</v>
+        <v>0.2179902678049397</v>
       </c>
       <c r="T87">
-        <v>3.723874901287768</v>
+        <v>3.97668054976766</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.530484721533812</v>
+        <v>1.512688387562489</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8446,22 +8446,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08794943749269155</v>
+        <v>0.1280685285335503</v>
       </c>
       <c r="C88">
-        <v>128.1346433819699</v>
+        <v>-187.4732181227787</v>
       </c>
       <c r="D88">
-        <v>1587.64064338197</v>
+        <v>1289.003781877221</v>
       </c>
       <c r="E88">
-        <v>1459.506</v>
+        <v>1476.477</v>
       </c>
       <c r="F88">
-        <v>1459.506</v>
+        <v>1476.477</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8482,45 +8482,45 @@
         <v>198.7</v>
       </c>
       <c r="M88">
-        <v>131.35554</v>
+        <v>216.7468236</v>
       </c>
       <c r="N88">
-        <v>67.34446000000003</v>
+        <v>-18.04682359999998</v>
       </c>
       <c r="O88">
-        <v>17.37487068000001</v>
+        <v>-4.656080488799995</v>
       </c>
       <c r="P88">
-        <v>49.96958932000002</v>
+        <v>-13.39074311119999</v>
       </c>
       <c r="Q88">
-        <v>203.06958932</v>
+        <v>139.7092568888</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2179902678049397</v>
+        <v>0.2350746575574089</v>
       </c>
       <c r="T88">
-        <v>3.97668054976766</v>
+        <v>4.371239204559097</v>
       </c>
       <c r="U88">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.258</v>
+        <v>0.2365183449913312</v>
       </c>
       <c r="W88">
-        <v>0.06677999999999999</v>
+        <v>0.1120791069552726</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>1.512688387562489</v>
+        <v>0.9167377712842294</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8528,22 +8528,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1280685285335503</v>
+        <v>0.1290785285335503</v>
       </c>
       <c r="C89">
-        <v>-187.4732181227787</v>
+        <v>-210.5194653817982</v>
       </c>
       <c r="D89">
-        <v>1289.003781877221</v>
+        <v>1282.928534618202</v>
       </c>
       <c r="E89">
-        <v>1476.477</v>
+        <v>1493.448</v>
       </c>
       <c r="F89">
-        <v>1476.477</v>
+        <v>1493.448</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8564,37 +8564,37 @@
         <v>198.7</v>
       </c>
       <c r="M89">
-        <v>216.7468236</v>
+        <v>219.2381664</v>
       </c>
       <c r="N89">
-        <v>-18.04682359999998</v>
+        <v>-20.53816639999999</v>
       </c>
       <c r="O89">
-        <v>-4.656080488799995</v>
+        <v>-5.298846931199999</v>
       </c>
       <c r="P89">
-        <v>-13.39074311119999</v>
+        <v>-15.23931946879999</v>
       </c>
       <c r="Q89">
-        <v>139.7092568888</v>
+        <v>137.8606805312</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2350746575574089</v>
+        <v>0.250847545687193</v>
       </c>
       <c r="T89">
-        <v>4.371239204559097</v>
+        <v>4.735509138272356</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2365183449913312</v>
+        <v>0.2338306365255206</v>
       </c>
       <c r="W89">
-        <v>0.1120791069552726</v>
+        <v>0.1124736625580536</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9167377712842294</v>
+        <v>0.9063202966105449</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8610,22 +8610,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1290785285335503</v>
+        <v>0.1300885285335503</v>
       </c>
       <c r="C90">
-        <v>-210.5194653817982</v>
+        <v>-233.5087143751862</v>
       </c>
       <c r="D90">
-        <v>1282.928534618202</v>
+        <v>1276.910285624814</v>
       </c>
       <c r="E90">
-        <v>1493.448</v>
+        <v>1510.419</v>
       </c>
       <c r="F90">
-        <v>1493.448</v>
+        <v>1510.419</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8646,37 +8646,37 @@
         <v>198.7</v>
       </c>
       <c r="M90">
-        <v>219.2381664</v>
+        <v>221.7295092</v>
       </c>
       <c r="N90">
-        <v>-20.53816639999999</v>
+        <v>-23.02950919999998</v>
       </c>
       <c r="O90">
-        <v>-5.298846931199999</v>
+        <v>-5.941613373599995</v>
       </c>
       <c r="P90">
-        <v>-15.23931946879999</v>
+        <v>-17.08789582639998</v>
       </c>
       <c r="Q90">
-        <v>137.8606805312</v>
+        <v>136.0121041736</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.250847545687193</v>
+        <v>0.269488231658756</v>
       </c>
       <c r="T90">
-        <v>4.735509138272356</v>
+        <v>5.166009969024389</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2338306365255206</v>
+        <v>0.2312033260027619</v>
       </c>
       <c r="W90">
-        <v>0.1124736625580536</v>
+        <v>0.1128593517427946</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9063202966105449</v>
+        <v>0.8961369224913254</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8692,22 +8692,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1300885285335503</v>
+        <v>0.1310985285335503</v>
       </c>
       <c r="C91">
-        <v>-233.5087143751862</v>
+        <v>-256.4417634984059</v>
       </c>
       <c r="D91">
-        <v>1276.910285624814</v>
+        <v>1270.948236501594</v>
       </c>
       <c r="E91">
-        <v>1510.419</v>
+        <v>1527.39</v>
       </c>
       <c r="F91">
-        <v>1510.419</v>
+        <v>1527.39</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8728,37 +8728,37 @@
         <v>198.7</v>
       </c>
       <c r="M91">
-        <v>221.7295092</v>
+        <v>224.220852</v>
       </c>
       <c r="N91">
-        <v>-23.02950919999998</v>
+        <v>-25.52085199999999</v>
       </c>
       <c r="O91">
-        <v>-5.941613373599995</v>
+        <v>-6.584379815999998</v>
       </c>
       <c r="P91">
-        <v>-17.08789582639998</v>
+        <v>-18.93647218399999</v>
       </c>
       <c r="Q91">
-        <v>136.0121041736</v>
+        <v>134.163527816</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.269488231658756</v>
+        <v>0.2918570548246316</v>
       </c>
       <c r="T91">
-        <v>5.166009969024389</v>
+        <v>5.682610965926828</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2312033260027619</v>
+        <v>0.2286344001582868</v>
       </c>
       <c r="W91">
-        <v>0.1128593517427946</v>
+        <v>0.1132364700567635</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8961369224913254</v>
+        <v>0.886179845574755</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8774,22 +8774,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1310985285335503</v>
+        <v>0.1321085285335503</v>
       </c>
       <c r="C92">
-        <v>-256.4417634984059</v>
+        <v>-279.319396304998</v>
       </c>
       <c r="D92">
-        <v>1270.948236501594</v>
+        <v>1265.041603695002</v>
       </c>
       <c r="E92">
-        <v>1527.39</v>
+        <v>1544.361</v>
       </c>
       <c r="F92">
-        <v>1527.39</v>
+        <v>1544.361</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8810,37 +8810,37 @@
         <v>198.7</v>
       </c>
       <c r="M92">
-        <v>224.220852</v>
+        <v>226.7121948</v>
       </c>
       <c r="N92">
-        <v>-25.52085199999999</v>
+        <v>-28.01219479999997</v>
       </c>
       <c r="O92">
-        <v>-6.584379815999998</v>
+        <v>-7.227146258399993</v>
       </c>
       <c r="P92">
-        <v>-18.93647218399999</v>
+        <v>-20.78504854159998</v>
       </c>
       <c r="Q92">
-        <v>134.163527816</v>
+        <v>132.3149514584</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2918570548246316</v>
+        <v>0.3191967275829241</v>
       </c>
       <c r="T92">
-        <v>5.682610965926828</v>
+        <v>6.314012184363142</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2286344001582868</v>
+        <v>0.2261219342224815</v>
       </c>
       <c r="W92">
-        <v>0.1132364700567635</v>
+        <v>0.1136053000561397</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.886179845574755</v>
+        <v>0.876441605513494</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8856,22 +8856,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1321085285335503</v>
+        <v>0.1331185285335503</v>
       </c>
       <c r="C93">
-        <v>-279.319396304998</v>
+        <v>-302.1423818498681</v>
       </c>
       <c r="D93">
-        <v>1265.041603695002</v>
+        <v>1259.189618150132</v>
       </c>
       <c r="E93">
-        <v>1544.361</v>
+        <v>1561.332</v>
       </c>
       <c r="F93">
-        <v>1544.361</v>
+        <v>1561.332</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8892,37 +8892,37 @@
         <v>198.7</v>
       </c>
       <c r="M93">
-        <v>226.7121948</v>
+        <v>229.2035376</v>
       </c>
       <c r="N93">
-        <v>-28.01219479999997</v>
+        <v>-30.50353759999999</v>
       </c>
       <c r="O93">
-        <v>-7.227146258399993</v>
+        <v>-7.869912700799997</v>
       </c>
       <c r="P93">
-        <v>-20.78504854159998</v>
+        <v>-22.63362489919999</v>
       </c>
       <c r="Q93">
-        <v>132.3149514584</v>
+        <v>130.4663751008</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3191967275829241</v>
+        <v>0.3533713185307897</v>
       </c>
       <c r="T93">
-        <v>6.314012184363142</v>
+        <v>7.103263707408537</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2261219342224815</v>
+        <v>0.2236640871113675</v>
       </c>
       <c r="W93">
-        <v>0.1136053000561397</v>
+        <v>0.1139661120120513</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.876441605513494</v>
+        <v>0.86691506632313</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8938,22 +8938,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1331185285335503</v>
+        <v>0.1341285285335503</v>
       </c>
       <c r="C94">
-        <v>-302.1423818498681</v>
+        <v>-324.9114750230917</v>
       </c>
       <c r="D94">
-        <v>1259.189618150132</v>
+        <v>1253.391524976908</v>
       </c>
       <c r="E94">
-        <v>1561.332</v>
+        <v>1578.303</v>
       </c>
       <c r="F94">
-        <v>1561.332</v>
+        <v>1578.303</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8974,37 +8974,37 @@
         <v>198.7</v>
       </c>
       <c r="M94">
-        <v>229.2035376</v>
+        <v>231.6948804</v>
       </c>
       <c r="N94">
-        <v>-30.50353759999999</v>
+        <v>-32.99488040000003</v>
       </c>
       <c r="O94">
-        <v>-7.869912700799997</v>
+        <v>-8.512679143200007</v>
       </c>
       <c r="P94">
-        <v>-22.63362489919999</v>
+        <v>-24.48220125680002</v>
       </c>
       <c r="Q94">
-        <v>130.4663751008</v>
+        <v>128.6177987432</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3533713185307897</v>
+        <v>0.3973100783209025</v>
       </c>
       <c r="T94">
-        <v>7.103263707408537</v>
+        <v>8.118015665609757</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2236640871113675</v>
+        <v>0.2212590969273743</v>
       </c>
       <c r="W94">
-        <v>0.1139661120120513</v>
+        <v>0.1143191645710615</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.86691506632313</v>
+        <v>0.8575933989433112</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9020,22 +9020,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1341285285335503</v>
+        <v>0.1351385285335503</v>
       </c>
       <c r="C95">
-        <v>-324.9114750230917</v>
+        <v>-347.6274168745363</v>
       </c>
       <c r="D95">
-        <v>1253.391524976908</v>
+        <v>1247.646583125464</v>
       </c>
       <c r="E95">
-        <v>1578.303</v>
+        <v>1595.274</v>
       </c>
       <c r="F95">
-        <v>1578.303</v>
+        <v>1595.274</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9056,37 +9056,37 @@
         <v>198.7</v>
       </c>
       <c r="M95">
-        <v>231.6948804</v>
+        <v>234.1862232</v>
       </c>
       <c r="N95">
-        <v>-32.99488040000003</v>
+        <v>-35.48622320000001</v>
       </c>
       <c r="O95">
-        <v>-8.512679143200007</v>
+        <v>-9.155445585600003</v>
       </c>
       <c r="P95">
-        <v>-24.48220125680002</v>
+        <v>-26.33077761440001</v>
       </c>
       <c r="Q95">
-        <v>128.6177987432</v>
+        <v>126.7692223856</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3973100783209025</v>
+        <v>0.4558950913743864</v>
       </c>
       <c r="T95">
-        <v>8.118015665609757</v>
+        <v>9.47101827654472</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2212590969273743</v>
+        <v>0.2189052767472959</v>
       </c>
       <c r="W95">
-        <v>0.1143191645710615</v>
+        <v>0.114664705373497</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8575933989433112</v>
+        <v>0.8484700649119994</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9102,22 +9102,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1351385285335503</v>
+        <v>0.1361485285335503</v>
       </c>
       <c r="C96">
-        <v>-347.6274168745363</v>
+        <v>-370.2909349296001</v>
       </c>
       <c r="D96">
-        <v>1247.646583125464</v>
+        <v>1241.9540650704</v>
       </c>
       <c r="E96">
-        <v>1595.274</v>
+        <v>1612.245</v>
       </c>
       <c r="F96">
-        <v>1595.274</v>
+        <v>1612.245</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9138,37 +9138,37 @@
         <v>198.7</v>
       </c>
       <c r="M96">
-        <v>234.1862232</v>
+        <v>236.677566</v>
       </c>
       <c r="N96">
-        <v>-35.48622320000001</v>
+        <v>-37.97756600000002</v>
       </c>
       <c r="O96">
-        <v>-9.155445585600003</v>
+        <v>-9.798212028000007</v>
       </c>
       <c r="P96">
-        <v>-26.33077761440001</v>
+        <v>-28.17935397200002</v>
       </c>
       <c r="Q96">
-        <v>126.7692223856</v>
+        <v>124.920646028</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4558950913743864</v>
+        <v>0.5379141096492639</v>
       </c>
       <c r="T96">
-        <v>9.47101827654472</v>
+        <v>11.36522193185367</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2189052767472959</v>
+        <v>0.2166010106762717</v>
       </c>
       <c r="W96">
-        <v>0.114664705373497</v>
+        <v>0.1150029716327233</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8484700649119994</v>
+        <v>0.8395388010708205</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9184,22 +9184,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1361485285335503</v>
+        <v>0.1371585285335503</v>
       </c>
       <c r="C97">
-        <v>-370.2909349296001</v>
+        <v>-392.9027434963427</v>
       </c>
       <c r="D97">
-        <v>1241.9540650704</v>
+        <v>1236.313256503657</v>
       </c>
       <c r="E97">
-        <v>1612.245</v>
+        <v>1629.216</v>
       </c>
       <c r="F97">
-        <v>1612.245</v>
+        <v>1629.216</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9220,37 +9220,37 @@
         <v>198.7</v>
       </c>
       <c r="M97">
-        <v>236.677566</v>
+        <v>239.1689088000001</v>
       </c>
       <c r="N97">
-        <v>-37.97756600000002</v>
+        <v>-40.46890880000004</v>
       </c>
       <c r="O97">
-        <v>-9.798212028000007</v>
+        <v>-10.44097847040001</v>
       </c>
       <c r="P97">
-        <v>-28.17935397200002</v>
+        <v>-30.02793032960003</v>
       </c>
       <c r="Q97">
-        <v>124.920646028</v>
+        <v>123.0720696704</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5379141096492639</v>
+        <v>0.66094263706158</v>
       </c>
       <c r="T97">
-        <v>11.36522193185367</v>
+        <v>14.20652741481709</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2166010106762717</v>
+        <v>0.2143447501483939</v>
       </c>
       <c r="W97">
-        <v>0.1150029716327233</v>
+        <v>0.1153341906782158</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8395388010708205</v>
+        <v>0.8307936052263327</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9266,22 +9266,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1371585285335503</v>
+        <v>0.1381685285335503</v>
       </c>
       <c r="C98">
-        <v>-392.9027434963425</v>
+        <v>-415.4635439642882</v>
       </c>
       <c r="D98">
-        <v>1236.313256503657</v>
+        <v>1230.723456035712</v>
       </c>
       <c r="E98">
-        <v>1629.216</v>
+        <v>1646.187</v>
       </c>
       <c r="F98">
-        <v>1629.216</v>
+        <v>1646.187</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9302,37 +9302,37 @@
         <v>198.7</v>
       </c>
       <c r="M98">
-        <v>239.1689088</v>
+        <v>241.6602516</v>
       </c>
       <c r="N98">
-        <v>-40.46890879999998</v>
+        <v>-42.96025159999999</v>
       </c>
       <c r="O98">
-        <v>-10.4409784704</v>
+        <v>-11.0837449128</v>
       </c>
       <c r="P98">
-        <v>-30.02793032959998</v>
+        <v>-31.87650668719999</v>
       </c>
       <c r="Q98">
-        <v>123.0720696704</v>
+        <v>121.2234933128</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6609426370615784</v>
+        <v>0.8659901827487713</v>
       </c>
       <c r="T98">
-        <v>14.20652741481705</v>
+        <v>18.94203655308941</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2143447501483939</v>
+        <v>0.2121350104561424</v>
       </c>
       <c r="W98">
-        <v>0.1153341906782158</v>
+        <v>0.1156585804650383</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8307936052263329</v>
+        <v>0.8222287226982263</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9348,22 +9348,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1381685285335503</v>
+        <v>0.1391785285335503</v>
       </c>
       <c r="C99">
-        <v>-415.4635439642882</v>
+        <v>-437.9740250951552</v>
       </c>
       <c r="D99">
-        <v>1230.723456035712</v>
+        <v>1225.183974904845</v>
       </c>
       <c r="E99">
-        <v>1646.187</v>
+        <v>1663.158</v>
       </c>
       <c r="F99">
-        <v>1646.187</v>
+        <v>1663.158</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9384,37 +9384,37 @@
         <v>198.7</v>
       </c>
       <c r="M99">
-        <v>241.6602516</v>
+        <v>244.1515944</v>
       </c>
       <c r="N99">
-        <v>-42.96025159999999</v>
+        <v>-45.4515944</v>
       </c>
       <c r="O99">
-        <v>-11.0837449128</v>
+        <v>-11.7265113552</v>
       </c>
       <c r="P99">
-        <v>-31.87650668719999</v>
+        <v>-33.7250830448</v>
       </c>
       <c r="Q99">
-        <v>121.2234933128</v>
+        <v>119.3749169552</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8659901827487713</v>
+        <v>1.276085274123157</v>
       </c>
       <c r="T99">
-        <v>18.94203655308941</v>
+        <v>28.41305482963411</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2121350104561424</v>
+        <v>0.2099703674923042</v>
       </c>
       <c r="W99">
-        <v>0.1156585804650383</v>
+        <v>0.1159763500521298</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8222287226982263</v>
+        <v>0.8138386336911015</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9430,22 +9430,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1391785285335503</v>
+        <v>0.1401885285335503</v>
       </c>
       <c r="C100">
-        <v>-437.9740250951552</v>
+        <v>-460.4348633057714</v>
       </c>
       <c r="D100">
-        <v>1225.183974904845</v>
+        <v>1219.694136694229</v>
       </c>
       <c r="E100">
-        <v>1663.158</v>
+        <v>1680.129</v>
       </c>
       <c r="F100">
-        <v>1663.158</v>
+        <v>1680.129</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9466,37 +9466,37 @@
         <v>198.7</v>
       </c>
       <c r="M100">
-        <v>244.1515944</v>
+        <v>246.6429372</v>
       </c>
       <c r="N100">
-        <v>-45.4515944</v>
+        <v>-47.94293719999999</v>
       </c>
       <c r="O100">
-        <v>-11.7265113552</v>
+        <v>-12.3692777976</v>
       </c>
       <c r="P100">
-        <v>-33.7250830448</v>
+        <v>-35.57365940239999</v>
       </c>
       <c r="Q100">
-        <v>119.3749169552</v>
+        <v>117.5263405976</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.276085274123157</v>
+        <v>2.506370548246314</v>
       </c>
       <c r="T100">
-        <v>28.41305482963411</v>
+        <v>56.82610965926822</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2099703674923042</v>
+        <v>0.2078494546893516</v>
       </c>
       <c r="W100">
-        <v>0.1159763500521298</v>
+        <v>0.1162877000516032</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9504,91 +9504,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8138386336911015</v>
+        <v>0.8056180414315955</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1401885285335503</v>
-      </c>
-      <c r="C101">
-        <v>-460.4348633057714</v>
-      </c>
-      <c r="D101">
-        <v>1219.694136694229</v>
-      </c>
-      <c r="E101">
-        <v>1680.129</v>
-      </c>
-      <c r="F101">
-        <v>1680.129</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>1697.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>351.8</v>
-      </c>
-      <c r="K101">
-        <v>153.1</v>
-      </c>
-      <c r="L101">
-        <v>198.7</v>
-      </c>
-      <c r="M101">
-        <v>246.6429372</v>
-      </c>
-      <c r="N101">
-        <v>-47.94293719999999</v>
-      </c>
-      <c r="O101">
-        <v>-12.3692777976</v>
-      </c>
-      <c r="P101">
-        <v>-35.57365940239999</v>
-      </c>
-      <c r="Q101">
-        <v>117.5263405976</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.506370548246314</v>
-      </c>
-      <c r="T101">
-        <v>56.82610965926822</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2078494546893516</v>
-      </c>
-      <c r="W101">
-        <v>0.1162877000516032</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8056180414315955</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
